--- a/materialy/материалы-по-комнатам.xlsx
+++ b/materialy/материалы-по-комнатам.xlsx
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Розетка для роутера рядом с сетевым подключением в прихожей.</t>
+          <t>Обычная розетка в прихожей; роутер находится на балконе.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Розетка в зале у края дивана со стороны спальни.</t>
+          <t>Розетка под телевизором на восточной стене зала.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Розетка в зале на свободном участке стены вне дверного проёма.</t>
+          <t>Розетка над северной спинкой углового дивана, доступная сидя.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Розетка в зале по центру стены с телевизором.</t>
+          <t>Розетка у южного торца углового дивана на западной стене зала.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -7438,7 +7438,7 @@
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
     </row>
-    <row r="19" ht="40" customHeight="1">
+    <row r="19" ht="56" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Розетка на балконе на свободной части стены рядом с дверью.</t>
+          <t>Розетка питания роутера на внутреннем простенке балкона рядом с интернет-розеткой.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -10941,7 +10941,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -11136,7 +11136,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
       <c r="I74" s="5" t="n"/>
       <c r="J74" s="5" t="n"/>
     </row>
-    <row r="75" ht="56" customHeight="1">
+    <row r="75" ht="72" customHeight="1">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
@@ -11360,12 +11360,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Сетевые и телевизионные подключения для роутера и телевизора.</t>
+          <t>Интернет-розетка для роутера на балконе и антенная розетка за ТВ в зале.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>H1/TH, RJ45/TV; состав уточнить
+          <t>BS — RJ45 на балконе; TH — антенна, без RJ45; H1 — обычная розетка
 Общее</t>
         </is>
       </c>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Сетевой кабель для роутера и телевизионной зоны квартиры.</t>
+          <t>Сетевой кабель от ввода до роутера на балконе; ТВ по Wi-Fi.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>

--- a/materialy/материалы-по-комнатам.xlsx
+++ b/materialy/материалы-по-комнатам.xlsx
@@ -20,21 +20,21 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Сводка'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Сводка'!$A$1:$C$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Прихожая'!$A$1:$J$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Прихожая'!$A$1:$J$29</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Прихожая'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Прихожая'!$A$1:$J$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Прихожая'!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ванная'!$A$1:$J$62</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Ванная'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Ванная'!$A$1:$J$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Кухня'!$A$1:$J$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Кухня'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Кухня'!$A$1:$J$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Зал'!$A$1:$J$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Зал'!$A$1:$J$40</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Зал'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Зал'!$A$1:$J$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Балкон'!$A$1:$J$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Зал'!$A$1:$J$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Балкон'!$A$1:$J$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Балкон'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Балкон'!$A$1:$J$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Балкон'!$A$1:$J$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Туалет'!$A$1:$J$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Туалет'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Туалет'!$A$1:$J$8</definedName>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
     </row>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
     </row>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
     </row>
@@ -695,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1288,17 +1288,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Двойная розетка</t>
+          <t>Двойная розетка, ориентир одинарная ×1,6</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Общая розетка в прихожей на стене без зеркала.</t>
+          <t>Пылесос у зеркала прихожей; зеркало не сверлить.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>H2, QF3</t>
+          <t>HM2; двойная</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Обычная розетка в прихожей; роутер находится на балконе.</t>
+          <t>Общая розетка в прихожей на стене без зеркала.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>H1, QF3</t>
+          <t>H2, QF3</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -1364,21 +1364,21 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Споты прихожей</t>
+          <t>Двойная розетка</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Споты для освещения прихожей.</t>
+          <t>Обычная розетка в прихожей; роутер находится на балконе.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>HL1/HL2; комплектность ламп проверить</t>
+          <t>H1, QF3</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1402,21 +1402,21 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Крепления / закладные под споты</t>
+          <t>Двойная розетка, ориентир одинарная ×1,6</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Закладные для крепления спотов прихожей до закрытия потолка.</t>
+          <t>Временный прибор у зеркала прихожей; розетка ниже зеркала.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>HL1/HL2</t>
+          <t>HM1; двойная</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -1434,27 +1434,27 @@
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
     </row>
-    <row r="20" ht="32" customHeight="1">
+    <row r="20" ht="40" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Обычный выключатель</t>
+          <t>Споты прихожей</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Выключатель освещения прихожей.</t>
+          <t>Споты для освещения прихожей.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>S1, L1</t>
+          <t>HL1/HL2; комплектность ламп проверить</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1472,27 +1472,31 @@
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="40" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Дюбель-гвоздь 6×60</t>
+          <t>Крепления / закладные под споты</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="3" t="n">
-        <v>0.06</v>
+          <t>Закладные для крепления спотов прихожей до закрытия потолка.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>HL1/HL2</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G21" s="4" t="n">
@@ -1500,41 +1504,45 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="32" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Саморезы-семечки</t>
+          <t>Обычный выключатель</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="3" t="n">
-        <v>0.06</v>
+          <t>Выключатель освещения прихожей.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>S1, L1</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I22" s="5" t="n"/>
@@ -1546,29 +1554,29 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ПВХ панели потолочные и балкон</t>
+          <t>Дюбель-гвоздь 6×60</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.</t>
+          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="3" t="n">
-        <v>3.08</v>
+        <v>0.06</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>шт. по 1 м²</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>шт. по 1 м²</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="I23" s="5" t="n"/>
@@ -1580,71 +1588,63 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Направляющие для ПВХ</t>
+          <t>Саморезы-семечки</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>UD 3 м; совместимость подтвердить</t>
-        </is>
-      </c>
+          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" s="3" t="n">
-        <v>2.47</v>
+        <v>0.06</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
     </row>
-    <row r="25" ht="40" customHeight="1">
+    <row r="25" ht="56" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Профиль для ПВХ</t>
+          <t>ПВХ панели потолочные и балкон</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>CD 3 м; совместимость подтвердить</t>
-        </is>
-      </c>
+          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
       <c r="E25" s="3" t="n">
-        <v>2.47</v>
+        <v>3.08</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
+          <t>шт. по 1 м²</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
+          <t>шт. по 1 м²</t>
         </is>
       </c>
       <c r="I25" s="5" t="n"/>
@@ -1656,17 +1656,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Пластиковые уголки</t>
+          <t>Направляющие для ПВХ</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Длина 3 м</t>
+          <t>UD 3 м; совместимость подтвердить</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
@@ -1682,52 +1682,128 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="40" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Обувница отдельная, зеркало на противоположной стене</t>
+          <t>Профиль для ПВХ</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Обувница у входа в прихожей, зеркало на противоположной стене.</t>
+          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>900×250×950 мм; не закрывать H1/H2 и проход</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>1</v>
+          <t>CD 3 м; совместимость подтвердить</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>2.47</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
     </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Пластиковые уголки</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Длина 3 м</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Обувница отдельная, зеркало на противоположной стене</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Обувница у входа в прихожей, зеркало на противоположной стене.</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>900×250×950 мм; не закрывать H1/H2 и проход</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J27"/>
+  <autoFilter ref="A1:J29"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -2958,7 +3034,7 @@
       <c r="I33" s="5" t="n"/>
       <c r="J33" s="5" t="n"/>
     </row>
-    <row r="34" ht="40" customHeight="1">
+    <row r="34" ht="56" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -2969,7 +3045,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Розетка с крышкой для фена рядом с раковиной ванной.</t>
+          <t>Две двойные розетки SH и SH2 для фена и зубной щётки у раковины; IP44 с крышками, УЗО.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2978,7 +3054,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2986,7 +3062,7 @@
         </is>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -3398,7 +3474,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -3406,7 +3482,7 @@
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -5693,7 +5769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6314,39 +6390,39 @@
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
     </row>
-    <row r="17" ht="40" customHeight="1">
+    <row r="17" ht="56" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Двойная розетка</t>
+          <t>ВВГнг(А)-LS 3×2,5</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Розетка под телевизором на восточной стене зала.</t>
+          <t>Кондиционер зала: отдельная линия QF10; длина с запасом 15%, купить один раз.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>LE1, QF3</t>
+          <t>QF10; запас 15%</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I17" s="5" t="n"/>
@@ -6358,17 +6434,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Двойная розетка</t>
+          <t>Двойная розетка, ориентир одинарная ×1,6</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Розетка в зале на простенке у окна.</t>
+          <t>Питание для уборки под кондиционером зала.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>LW2, QF3</t>
+          <t>LW3; двойная</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -6396,17 +6472,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Двойная розетка</t>
+          <t>Двойная розетка, ориентир одинарная ×1,6</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Розетка и подключения за телевизором в зале.</t>
+          <t>Отдельное питание кондиционера зала, QF10.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>TH, QF3</t>
+          <t>LAC; двойная</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
@@ -6439,12 +6515,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Розетка над северной спинкой углового дивана, доступная сидя.</t>
+          <t>Розетка под телевизором на восточной стене зала.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>LE2, QF3</t>
+          <t>LE1, QF3</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -6472,17 +6548,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Двойная розетка</t>
+          <t>Двойная розетка, ориентир одинарная ×1,6</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Розетка у южного торца углового дивана на западной стене зала.</t>
+          <t>Зарядка у северной спинки дивана; розетка доступна сидя.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>TL, QF3</t>
+          <t>LN2; двойная</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
@@ -6510,21 +6586,21 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Крепления / закладные под споты</t>
+          <t>Двойная розетка</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Закладные для крепления спотов зала до закрытия потолка.</t>
+          <t>Розетка в зале на простенке у окна.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>LW2, QF3</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -6532,7 +6608,7 @@
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -6548,21 +6624,21 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Споты зала</t>
+          <t>Двойная розетка, ориентир одинарная ×1,6</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Споты для освещения зала с разделением на две группы.</t>
+          <t>Питание на простенке окна зала выше радиатора.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>LC, 9 точек; комплектность ламп проверить</t>
+          <t>LS2; двойная</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -6570,7 +6646,7 @@
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -6580,23 +6656,23 @@
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="40" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Проходной выключатель</t>
+          <t>Двойная розетка</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Проходной выключатель для управления светом зала со второго места.</t>
+          <t>Розетка и подключения за телевизором в зале.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>S6, L1; схему согласовать</t>
+          <t>TH, QF3</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -6618,23 +6694,23 @@
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="40" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Двухклавишный выключатель</t>
+          <t>Двойная розетка</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Выключатель двух групп спотов зала, проходную схему согласовать с электриком.</t>
+          <t>Розетка над северной спинкой углового дивана, доступная сидя.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>S5, L1; A — 6 спотов, B — 3; связь с S6 согласовать</t>
+          <t>LE2, QF3</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
@@ -6662,21 +6738,25 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Дверной блок в зал 800 мм</t>
+          <t>Двойная розетка</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Новая дверь между залом и прихожей.</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
+          <t>Розетка у южного торца углового дивана на западной стене зала.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>TL, QF3</t>
+        </is>
+      </c>
       <c r="E26" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
@@ -6684,48 +6764,538 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="40" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Натяжной потолок зала</t>
+          <t>Крепления / закладные под споты</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Натяжной потолок для зала с местами под споты.</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
+          <t>Закладные для крепления спотов зала до закрытия потолка.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
       <c r="E27" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>комплект на 16,86 м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>комплект на 16,86 м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
     </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Споты зала</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Споты для освещения зала с разделением на две группы.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>LC, 9 точек; комплектность ламп проверить</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Проходной выключатель</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Проходной выключатель для управления светом зала со второго места.</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>S6, L1; схему согласовать</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="56" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Двухклавишный выключатель</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Выключатель двух групп спотов зала, проходную схему согласовать с электриком.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>S5, L1; A — 6 спотов, B — 3; связь с S6 согласовать</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Дверной блок в зал 800 мм</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Новая дверь между залом и прихожей.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="56" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Натяжной потолок зала</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Натяжной потолок для зала с местами под споты.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>комплект на 16,86 м²</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>комплект на 16,86 м²</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="88" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Кронштейны наружного блока зала</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Крепление наружного блока зала под решёткой балкона; анкеры после осмотра парапета.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="88" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Защитная клетка наружного блока зала</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Защита наружного блока зала под балконной решёткой; размеры и крепление уточнить у мастера.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="88" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Медная трасса 1/4 + 3/8 с изоляцией, первые 5 м</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Первые 5 м медной трассы с изоляцией; медь сверх 5 м входит в дополнительный метр. Уточнить у мастера.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="88" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Дренаж кондиционера зала</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Отвод конденсата наружу по трассе 7,62 м с постоянным уклоном; слив согласовать на месте.</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="88" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Дополнительный метр трассы с медью и монтажом</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Дополнительные 1,83 м трассы сверх 5 м; медь и монтаж уже включены в эту строку, медь повторно не покупать.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="88" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Монтаж кондиционера зала, до 5 м</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Монтаж и пуск кондиционера зала; базовая работа до 5 м, материалы отдельно.</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="88" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Гильза прохода трассы кондиционера зала</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Две гильзы: через стену зала и через глухой парапет ниже остекления; стекло не сверлить.</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+    </row>
+    <row r="40" ht="88" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Кондиционер зала инверторный 9000 BTU</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Кондиционер охлаждает зал; инвертор 9000 BTU, этап 4.</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J27"/>
+  <autoFilter ref="A1:J40"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -6737,7 +7307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7400,7 +7970,7 @@
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
     </row>
-    <row r="18" ht="40" customHeight="1">
+    <row r="18" ht="56" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -7411,12 +7981,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Розетка на балконе на стене со стороны кухни.</t>
+          <t>Розетка питания роутера на внутреннем простенке балкона рядом с интернет-розеткой.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>BS4, QF3; IP44</t>
+          <t>BS, QF3; IP44</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -7438,7 +8008,7 @@
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="40" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -7449,12 +8019,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Розетка питания роутера на внутреннем простенке балкона рядом с интернет-розеткой.</t>
+          <t>Питание для уборки под окном зала со стороны балкона.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>BS, QF3; IP44</t>
+          <t>BN2; IP44 с крышкой</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
@@ -7487,12 +8057,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Розетка на балконе на стене со стороны зала.</t>
+          <t>Зарядка над откидным столом балкона.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>BS2, QF3; IP44</t>
+          <t>BW2; IP44 с крышкой</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -7520,21 +8090,21 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Споты балкона IP44</t>
+          <t>Двойная розетка IP44 с крышкой</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Влагозащищённые споты для освещения балкона.</t>
+          <t>Розетка на балконе на стене со стороны зала.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>BLL/BLL2, IP44; класс защиты подтвердить</t>
+          <t>BS2, QF3; IP44</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -7542,7 +8112,7 @@
         </is>
       </c>
       <c r="G21" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -7558,21 +8128,21 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Крепления / закладные под споты</t>
+          <t>Двойная розетка IP44 с крышкой</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Закладные для крепления спотов балкона до закрытия потолка.</t>
+          <t>Питание на парапете балкона, вне шкафа.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>BLL/BLL2</t>
+          <t>BS5; IP44 с крышкой</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -7580,7 +8150,7 @@
         </is>
       </c>
       <c r="G22" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -7596,21 +8166,21 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Двухклавишный выключатель IP44</t>
+          <t>Споты балкона IP44</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Выключатель двух зон освещения балкона рядом с дверью.</t>
+          <t>Влагозащищённые споты для освещения балкона.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>BLS, L2, IP44; зоны A/B</t>
+          <t>BLL/BLL2, IP44; класс защиты подтвердить</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -7618,7 +8188,7 @@
         </is>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -7628,69 +8198,77 @@
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="40" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Дюбель-гвоздь 6×60</t>
+          <t>Крепления / закладные под споты</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="3" t="n">
-        <v>0.5600000000000001</v>
+          <t>Закладные для крепления спотов балкона до закрытия потолка.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>BLL/BLL2</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>8</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="40" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Саморезы-семечки</t>
+          <t>Двухклавишный выключатель IP44</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="3" t="n">
-        <v>0.5600000000000001</v>
+          <t>Выключатель двух зон освещения балкона рядом с дверью.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>BLS, L2, IP44; зоны A/B</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I25" s="5" t="n"/>
@@ -7702,29 +8280,29 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ПВХ панели потолочные и балкон</t>
+          <t>Дюбель-гвоздь 6×60</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.</t>
+          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="3" t="n">
-        <v>27.83</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>шт. по 1 м²</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G26" s="4" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>шт. по 1 м²</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="I26" s="5" t="n"/>
@@ -7736,71 +8314,63 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Направляющие для ПВХ</t>
+          <t>Саморезы-семечки</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>UD 3 м; совместимость подтвердить</t>
-        </is>
-      </c>
+          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="3" t="n">
-        <v>4.33</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G27" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
     </row>
-    <row r="28" ht="40" customHeight="1">
+    <row r="28" ht="56" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Профиль для ПВХ</t>
+          <t>ПВХ панели потолочные и балкон</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>CD 3 м; совместимость подтвердить</t>
-        </is>
-      </c>
+          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="3" t="n">
-        <v>4.33</v>
+        <v>27.83</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
+          <t>шт. по 1 м²</t>
         </is>
       </c>
       <c r="G28" s="4" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
+          <t>шт. по 1 м²</t>
         </is>
       </c>
       <c r="I28" s="5" t="n"/>
@@ -7812,17 +8382,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Пластиковые уголки</t>
+          <t>Направляющие для ПВХ</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Длина 3 м</t>
+          <t>UD 3 м; совместимость подтвердить</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
@@ -7830,7 +8400,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="G29" s="4" t="n">
@@ -7838,7 +8408,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="I29" s="5" t="n"/>
@@ -7850,29 +8420,33 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Козырёк балкона наружный, материал и монтаж</t>
+          <t>Профиль для ПВХ</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Наружный козырёк для защиты балкона от осадков.</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="4" t="n">
-        <v>1</v>
+          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>CD 3 м; совместимость подтвердить</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>4.33</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="G30" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="I30" s="5" t="n"/>
@@ -7884,33 +8458,33 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Шкаф балконный</t>
+          <t>Пластиковые уголки</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Узкий шкаф на балконе с проходом канала вытяжки через верх.</t>
+          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1250×240×2700 мм; канал Ø150 через верх; не перекрывать окно</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>1</v>
+          <t>Длина 3 м</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>4.33</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I31" s="5" t="n"/>
@@ -7922,12 +8496,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Стол складной и 2 стула</t>
+          <t>Козырёк балкона наружный, материал и монтаж</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Складной стол и стулья для балкона с сохранением прохода.</t>
+          <t>Наружный козырёк для защиты балкона от осадков.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -7950,8 +8524,80 @@
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
     </row>
+    <row r="33" ht="56" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Шкаф балконный</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Узкий шкаф на балконе с проходом канала вытяжки через верх.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>1250×240×2700 мм; канал Ø150 через верх; не перекрывать окно</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Стол складной и 2 стула</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Складной стол и стулья для балкона с сохранением прохода.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J32"/>
+  <autoFilter ref="A1:J34"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -10941,7 +11587,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -10949,7 +11595,7 @@
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -11136,7 +11782,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -11144,7 +11790,7 @@
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -11292,7 +11938,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -11300,7 +11946,7 @@
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>

--- a/materialy/материалы-по-комнатам.xlsx
+++ b/materialy/материалы-по-комнатам.xlsx
@@ -11587,7 +11587,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>

--- a/materialy/материалы-по-комнатам.xlsx
+++ b/materialy/материалы-по-комнатам.xlsx
@@ -29,9 +29,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Кухня'!$A$1:$J$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Кухня'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Кухня'!$A$1:$J$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Зал'!$A$1:$J$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Зал'!$A$1:$J$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Зал'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Зал'!$A$1:$J$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Зал'!$A$1:$J$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Балкон'!$A$1:$J$34</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Балкон'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Балкон'!$A$1:$J$34</definedName>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
     </row>
@@ -5769,7 +5769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+          <t>Фреоновая трасса 4,24 м; дренаж 5,03 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+          <t>Фреоновая трасса 4,24 м; дренаж 5,03 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
@@ -7082,19 +7082,19 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>5</v>
+          <t>Фреоновая трасса 4,24 м; дренаж 5,03 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>4.24</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
-        <v>5</v>
+      <c r="G35" s="3" t="n">
+        <v>4.24</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -7115,16 +7115,16 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Отвод конденсата наружу по трассе 7,62 м с постоянным уклоном; слив согласовать на месте.</t>
+          <t>Отвод конденсата наружу по трассе 5,03 м с постоянным уклоном; слив согласовать на месте.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+          <t>Фреоновая трасса 4,24 м; дренаж 5,03 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>7.62</v>
+        <v>5.03</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>7.62</v>
+        <v>5.03</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -7148,33 +7148,33 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Дополнительный метр трассы с медью и монтажом</t>
+          <t>Монтаж кондиционера зала, до 5 м</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Дополнительные 1,83 м трассы сверх 5 м; медь и монтаж уже включены в эту строку, медь повторно не покупать.</t>
+          <t>Монтаж и пуск кондиционера зала; базовая работа до 5 м, материалы отдельно.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>1.83</v>
+          <t>Фреоновая трасса 4,24 м; дренаж 5,03 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>1.83</v>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="I37" s="5" t="n"/>
@@ -7186,33 +7186,33 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Монтаж кондиционера зала, до 5 м</t>
+          <t>Гильза прохода трассы кондиционера зала</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Монтаж и пуск кондиционера зала; базовая работа до 5 м, материалы отдельно.</t>
+          <t>Две гильзы: через стену зала и через глухой парапет ниже остекления; стекло не сверлить.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+          <t>Фреоновая трасса 4,24 м; дренаж 5,03 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I38" s="5" t="n"/>
@@ -7224,21 +7224,21 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Гильза прохода трассы кондиционера зала</t>
+          <t>Кондиционер зала инверторный 9000 BTU</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Две гильзы: через стену зала и через глухой парапет ниже остекления; стекло не сверлить.</t>
+          <t>Кондиционер охлаждает зал; инвертор 9000 BTU, этап 4.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+          <t>Фреоновая трасса 4,24 м; дренаж 5,03 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -7256,46 +7256,8 @@
       <c r="I39" s="5" t="n"/>
       <c r="J39" s="5" t="n"/>
     </row>
-    <row r="40" ht="88" customHeight="1">
-      <c r="A40" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Кондиционер зала инверторный 9000 BTU</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Кондиционер охлаждает зал; инвертор 9000 BTU, этап 4.</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Фреоновая трасса 6,83 м; дренаж 7,62 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="n"/>
-      <c r="J40" s="5" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J40"/>
+  <autoFilter ref="A1:J39"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/materialy/материалы-по-комнатам.xlsx
+++ b/materialy/материалы-по-комнатам.xlsx
@@ -41,9 +41,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Спальня'!$A$1:$J$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Спальня'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Спальня'!$A$1:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'На всю квартиру'!$A$1:$J$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'На всю квартиру'!$A$1:$J$97</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'На всю квартиру'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'На всю квартиру'!$A$1:$J$92</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'На всю квартиру'!$A$1:$J$97</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="0"/>
 </workbook>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
     </row>
@@ -762,7 +762,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="88" customHeight="1">
+    <row r="2" ht="104" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -773,7 +773,8 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.</t>
+          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.
+Даҳлиз, Зал, Ошхона, Ваннахона ва Балкон полига бир хил рангли плитка.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -811,7 +812,8 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.</t>
+          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда пол ва девор плиткасини ётқизиш учун клей.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -838,7 +840,7 @@
       <c r="I3" s="5" t="n"/>
       <c r="J3" s="5" t="n"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="88" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -849,7 +851,8 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Грунт, чтобы штукатурка и стяжка держались на старом основании.</t>
+          <t>Грунт, чтобы штукатурка и стяжка держались на старом основании.
+Штукатурка ва стяжка эски асосга яхши ёпишиши учун грунт.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
@@ -872,7 +875,7 @@
       <c r="I4" s="5" t="n"/>
       <c r="J4" s="5" t="n"/>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="72" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -883,7 +886,8 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Цемент для новой стяжки полов в ремонтируемых комнатах.</t>
+          <t>Цемент для новой стяжки полов в ремонтируемых комнатах.
+Таъмирланадиган хоналарда янги пол стяжкаси учун цемент.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -910,7 +914,7 @@
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="72" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -921,7 +925,8 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Плёнка как разделительный слой под новой стяжкой полов.</t>
+          <t>Плёнка как разделительный слой под новой стяжкой полов.
+Янги пол стяжкаси остида ажратувчи қатлам учун плёнка.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -948,7 +953,7 @@
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="104" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -959,7 +964,8 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Грунтовка для старых оснований и новых поверхностей гипсокартона перед отделкой.</t>
+          <t>Грунтовка для старых оснований и новых поверхностей гипсокартона перед отделкой.
+Отделкадан олдин эски асослар ва янги гипсокартон юзалари учун грунтовка.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
@@ -982,7 +988,7 @@
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
     </row>
-    <row r="8" ht="40" customHeight="1">
+    <row r="8" ht="72" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -993,7 +999,8 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Песок для раствора новой стяжки полов.</t>
+          <t>Песок для раствора новой стяжки полов.
+Янги пол стяжкаси раствори учун песок.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -1016,7 +1023,7 @@
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="72" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -1027,7 +1034,8 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Лента по краям стяжки, чтобы пол не упирался жёстко в стены.</t>
+          <t>Лента по краям стяжки, чтобы пол не упирался жёстко в стены.
+Стяжка деворларга қаттиқ тиралмаслиги учун четларига лента.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1065,7 +1073,8 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Затирка для швов плитки на полах и стенах.</t>
+          <t>Затирка для швов плитки на полах и стенах.
+Пол ва девор плиткаси чоклари учун затирка.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1092,7 +1101,7 @@
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
     </row>
-    <row r="11" ht="40" customHeight="1">
+    <row r="11" ht="72" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -1103,7 +1112,8 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Маяки, чтобы вывести стяжку полов на общий уровень.</t>
+          <t>Маяки, чтобы вывести стяжку полов на общий уровень.
+Пол стяжкасини умумий баландликка текислаш учун маяклар.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1130,7 +1140,7 @@
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
     </row>
-    <row r="12" ht="40" customHeight="1">
+    <row r="12" ht="72" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -1141,7 +1151,8 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона прихожей.</t>
+          <t>Шпаклёвка для заделки швов гипсокартона прихожей.
+Даҳлиз гипсокартони чокларини ёпиш учун шпаклёвка.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1168,7 +1179,7 @@
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
     </row>
-    <row r="13" ht="40" customHeight="1">
+    <row r="13" ht="72" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -1179,7 +1190,8 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стенам прихожей.</t>
+          <t>Клей, чтобы приклеить гипсокартон к стенам прихожей.
+Даҳлиз деворларига гипсокартонни ёпиштириш учун клей.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1206,7 +1218,7 @@
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
     </row>
-    <row r="14" ht="40" customHeight="1">
+    <row r="14" ht="72" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -1217,7 +1229,8 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона прихожей.</t>
+          <t>Серпянка для укрепления швов гипсокартона прихожей.
+Даҳлиз гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1244,7 +1257,7 @@
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
     </row>
-    <row r="15" ht="40" customHeight="1">
+    <row r="15" ht="72" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -1255,7 +1268,8 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стен прихожей перед отделкой.</t>
+          <t>Листы для выравнивания стен прихожей перед отделкой.
+Отделкадан олдин Даҳлиз деворларини текислаш учун листлар.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1282,7 +1296,7 @@
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
     </row>
-    <row r="16" ht="40" customHeight="1">
+    <row r="16" ht="72" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -1293,7 +1307,8 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Пылесос у зеркала прихожей; зеркало не сверлить.</t>
+          <t>Пылесос у зеркала прихожей; зеркало не сверлить.
+Даҳлиз кўзгуси ёнида чангютгич учун; кўзгуни тешманг.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1320,7 +1335,7 @@
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
     </row>
-    <row r="17" ht="40" customHeight="1">
+    <row r="17" ht="72" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -1331,7 +1346,8 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Общая розетка в прихожей на стене без зеркала.</t>
+          <t>Общая розетка в прихожей на стене без зеркала.
+Даҳлизда ойнасиз деворда умумий розетка.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1358,7 +1374,7 @@
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
     </row>
-    <row r="18" ht="40" customHeight="1">
+    <row r="18" ht="72" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -1369,7 +1385,8 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Обычная розетка в прихожей; роутер находится на балконе.</t>
+          <t>Обычная розетка в прихожей; роутер находится на балконе.
+Йўлакдаги оддий розетка; роутер Балконда.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1396,7 +1413,7 @@
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
     </row>
-    <row r="19" ht="40" customHeight="1">
+    <row r="19" ht="88" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -1407,7 +1424,8 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Временный прибор у зеркала прихожей; розетка ниже зеркала.</t>
+          <t>Временный прибор у зеркала прихожей; розетка ниже зеркала.
+Даҳлиз кўзгуси ёнидаги вақтинча жиҳоз учун; розетка кўзгу остида.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1445,7 +1463,8 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Споты для освещения прихожей.</t>
+          <t>Споты для освещения прихожей.
+Даҳлизни ёритиш учун спотлар.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1472,7 +1491,7 @@
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
     </row>
-    <row r="21" ht="40" customHeight="1">
+    <row r="21" ht="88" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -1483,7 +1502,8 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Закладные для крепления спотов прихожей до закрытия потолка.</t>
+          <t>Закладные для крепления спотов прихожей до закрытия потолка.
+Потолок ёпилгунча Даҳлиз спотларини маҳкамлаш учун закладнойлар.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1510,7 +1530,7 @@
       <c r="I21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
     </row>
-    <row r="22" ht="32" customHeight="1">
+    <row r="22" ht="40" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -1521,7 +1541,8 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Выключатель освещения прихожей.</t>
+          <t>Выключатель освещения прихожей.
+Даҳлиз чироғи выключатели.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1548,7 +1569,7 @@
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="104" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -1559,7 +1580,8 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркасини маҳкамлаш учун дюбель-гвоздлар.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1582,7 +1604,7 @@
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="104" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -1593,7 +1615,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.</t>
+          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХни каркасга маҳкамлаш учун саморезлар.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -1616,7 +1639,7 @@
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="104" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -1627,7 +1650,8 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.</t>
+          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.
+Ваннахона, Ошхона, Даҳлиз потолоклари ҳамда Балкон деворлари ва потолоки учун панеллар.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -1650,7 +1674,7 @@
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="104" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -1661,7 +1685,8 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси направляющийлари.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1688,7 +1713,7 @@
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
     </row>
-    <row r="27" ht="40" customHeight="1">
+    <row r="27" ht="72" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
@@ -1699,7 +1724,8 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси профили.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1726,7 +1752,7 @@
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="104" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
@@ -1737,7 +1763,8 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ туташган жойларини ёпиш учун уголоклар.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1764,7 +1791,7 @@
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="72" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
@@ -1775,7 +1802,8 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Обувница у входа в прихожей, зеркало на противоположной стене.</t>
+          <t>Обувница у входа в прихожей, зеркало на противоположной стене.
+Даҳлиз киришида обувница, ойна қарама-қарши деворда.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1882,7 +1910,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="88" customHeight="1">
+    <row r="2" ht="104" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -1893,7 +1921,8 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.</t>
+          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.
+Даҳлиз, Зал, Ошхона, Ваннахона ва Балкон полига бир хил рангли плитка.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1931,7 +1960,8 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Плитка для всех стен ванной и двух рабочих стен кухни.</t>
+          <t>Плитка для всех стен ванной и двух рабочих стен кухни.
+Ваннахонанинг барча деворлари ва Ошхонанинг икки иш девори учун плитка.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1969,7 +1999,8 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.</t>
+          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда пол ва девор плиткасини ётқизиш учун клей.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1996,7 +2027,7 @@
       <c r="I4" s="5" t="n"/>
       <c r="J4" s="5" t="n"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="88" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -2007,7 +2038,8 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Грунт, чтобы штукатурка и стяжка держались на старом основании.</t>
+          <t>Грунт, чтобы штукатурка и стяжка держались на старом основании.
+Штукатурка ва стяжка эски асосга яхши ёпишиши учун грунт.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
@@ -2030,7 +2062,7 @@
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="72" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -2041,7 +2073,8 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Цемент для новой стяжки полов в ремонтируемых комнатах.</t>
+          <t>Цемент для новой стяжки полов в ремонтируемых комнатах.
+Таъмирланадиган хоналарда янги пол стяжкаси учун цемент.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2068,7 +2101,7 @@
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="72" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -2079,7 +2112,8 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Плёнка как разделительный слой под новой стяжкой полов.</t>
+          <t>Плёнка как разделительный слой под новой стяжкой полов.
+Янги пол стяжкаси остида ажратувчи қатлам учун плёнка.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2106,7 +2140,7 @@
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="104" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -2117,7 +2151,8 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Грунтовка для старых оснований и новых поверхностей гипсокартона перед отделкой.</t>
+          <t>Грунтовка для старых оснований и новых поверхностей гипсокартона перед отделкой.
+Отделкадан олдин эски асослар ва янги гипсокартон юзалари учун грунтовка.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -2140,7 +2175,7 @@
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="72" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -2151,7 +2186,8 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Песок для раствора новой стяжки полов.</t>
+          <t>Песок для раствора новой стяжки полов.
+Янги пол стяжкаси раствори учун песок.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
@@ -2174,7 +2210,7 @@
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="72" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -2185,7 +2221,8 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Лента по краям стяжки, чтобы пол не упирался жёстко в стены.</t>
+          <t>Лента по краям стяжки, чтобы пол не упирался жёстко в стены.
+Стяжка деворларга қаттиқ тиралмаслиги учун четларига лента.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2223,7 +2260,8 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Затирка для швов плитки на полах и стенах.</t>
+          <t>Затирка для швов плитки на полах и стенах.
+Пол ва девор плиткаси чоклари учун затирка.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2250,7 +2288,7 @@
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
     </row>
-    <row r="12" ht="40" customHeight="1">
+    <row r="12" ht="72" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -2261,7 +2299,8 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Маяки, чтобы вывести стяжку полов на общий уровень.</t>
+          <t>Маяки, чтобы вывести стяжку полов на общий уровень.
+Пол стяжкасини умумий баландликка текислаш учун маяклар.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2288,7 +2327,7 @@
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
     </row>
-    <row r="13" ht="40" customHeight="1">
+    <row r="13" ht="72" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -2299,7 +2338,8 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона ванной.</t>
+          <t>Шпаклёвка для заделки швов гипсокартона ванной.
+Ваннахона гипсокартони чокларини ёпиш учун шпаклёвка.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2326,7 +2366,7 @@
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
     </row>
-    <row r="14" ht="40" customHeight="1">
+    <row r="14" ht="72" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -2337,7 +2377,8 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стенам ванной.</t>
+          <t>Клей, чтобы приклеить гипсокартон к стенам ванной.
+Ваннахона деворларига гипсокартонни ёпиштириш учун клей.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2364,7 +2405,7 @@
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="120" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -2375,7 +2416,8 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для второго слоя гипсокартона ванной; крепление согласовать с изготовителем системы.</t>
+          <t>Саморезы для второго слоя гипсокартона ванной; крепление согласовать с изготовителем системы.
+Ваннахона гипсокартонининг иккинчи қатлами учун саморезлар; маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2402,7 +2444,7 @@
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
     </row>
-    <row r="16" ht="40" customHeight="1">
+    <row r="16" ht="72" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -2413,7 +2455,8 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона ванной.</t>
+          <t>Серпянка для укрепления швов гипсокартона ванной.
+Ваннахона гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2440,7 +2483,7 @@
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="72" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -2451,7 +2494,8 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стен ванной перед отделкой.</t>
+          <t>Листы для выравнивания стен ванной перед отделкой.
+Отделкадан олдин Ваннахона деворларини текислаш учун листлар.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2478,7 +2522,7 @@
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
     </row>
-    <row r="18" ht="40" customHeight="1">
+    <row r="18" ht="72" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -2489,7 +2533,8 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Сифон для отвода воды от подвесной раковины в ванной.</t>
+          <t>Сифон для отвода воды от подвесной раковины в ванной.
+Ваннахонадаги осма раковинадан сувни чиқариш учун сифон.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2516,7 +2561,7 @@
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="72" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -2527,7 +2572,8 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Раковина для умывания на стене ванной со стороны кухни.</t>
+          <t>Раковина для умывания на стене ванной со стороны кухни.
+Ваннахонанинг Ошхона томонидаги деворида ювиниш учун раковина.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
@@ -2550,7 +2596,7 @@
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
     </row>
-    <row r="20" ht="40" customHeight="1">
+    <row r="20" ht="72" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -2561,7 +2607,8 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Зеркало и полка для мелочей над раковиной ванной.</t>
+          <t>Зеркало и полка для мелочей над раковиной ванной.
+Ваннахона раковинаси устига ойна ва майда буюмлар учун полка.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -2584,7 +2631,7 @@
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="72" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -2595,7 +2642,8 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Ванна для купания вдоль стены со стороны туалета.</t>
+          <t>Ванна для купания вдоль стены со стороны туалета.
+Ҳожатхона томонидаги девор бўйлаб чўмилиш учун ванна.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2622,7 +2670,7 @@
       <c r="I21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
     </row>
-    <row r="22" ht="40" customHeight="1">
+    <row r="22" ht="72" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -2633,7 +2681,8 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Лента для герметичного стыка ванны со стеной.</t>
+          <t>Лента для герметичного стыка ванны со стеной.
+Ванна билан девор туташган жойни герметик ёпиш учун лента.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -2656,7 +2705,7 @@
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="88" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -2667,7 +2716,8 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Опора для акриловой ванны, только если каркас не входит в её комплект.</t>
+          <t>Опора для акриловой ванны, только если каркас не входит в её комплект.
+Акриловая ванна таянчи, фақат каркас комплектга кирмаса.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2694,7 +2744,7 @@
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
     </row>
-    <row r="24" ht="40" customHeight="1">
+    <row r="24" ht="72" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -2705,7 +2755,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Смеситель для набора воды в ванну и ручного душа.</t>
+          <t>Смеситель для набора воды в ванну и ручного душа.
+Ваннага сув тўлдириш ва қўл души учун смеситель.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -2728,7 +2779,7 @@
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
     </row>
-    <row r="25" ht="40" customHeight="1">
+    <row r="25" ht="72" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -2739,7 +2790,8 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Сифон для слива ванны с защитой от перелива.</t>
+          <t>Сифон для слива ванны с защитой от перелива.
+Ванна сувини чиқариш ва переливдан ҳимоя қилиш учун сифон.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -2762,7 +2814,7 @@
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
     </row>
-    <row r="26" ht="40" customHeight="1">
+    <row r="26" ht="72" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -2773,7 +2825,8 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Штанга для полотенца ног на стене ванной со стороны зала.</t>
+          <t>Штанга для полотенца ног на стене ванной со стороны зала.
+Ваннахонанинг Зал томонидаги деворида оёқ сочиғи учун штанга.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -2796,7 +2849,7 @@
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
     </row>
-    <row r="27" ht="40" customHeight="1">
+    <row r="27" ht="72" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
@@ -2807,7 +2860,8 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Вентили для перекрытия воды к сантехнике ванной.</t>
+          <t>Вентили для перекрытия воды к сантехнике ванной.
+Ваннахона сантехникаси сувини ёпиш учун вентиллар.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -2830,7 +2884,7 @@
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
     </row>
-    <row r="28" ht="40" customHeight="1">
+    <row r="28" ht="72" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
@@ -2841,7 +2895,8 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Вентилятор для удаления влажного воздуха из ванной.</t>
+          <t>Вентилятор для удаления влажного воздуха из ванной.
+Ваннахонадан нам ҳавони чиқариш учун вентилятор.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -2864,7 +2919,7 @@
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
     </row>
-    <row r="29" ht="40" customHeight="1">
+    <row r="29" ht="72" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
@@ -2875,7 +2930,8 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Влагозащищённые споты для освещения ванной.</t>
+          <t>Влагозащищённые споты для освещения ванной.
+Ваннахонани ёритиш учун намликдан ҳимояланган спотлар.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -2898,7 +2954,7 @@
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="88" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
@@ -2909,7 +2965,8 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Экран, чтобы закрыть пространство под ванной и сохранить доступ к сливу.</t>
+          <t>Экран, чтобы закрыть пространство под ванной и сохранить доступ к сливу.
+Ванна остини ёпиш ва сливга киришни сақлаш учун экран.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -2932,7 +2989,7 @@
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
     </row>
-    <row r="31" ht="40" customHeight="1">
+    <row r="31" ht="72" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
@@ -2943,7 +3000,8 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Крючки для одежды на внутренней стороне двери ванной.</t>
+          <t>Крючки для одежды на внутренней стороне двери ванной.
+Ваннахона эшигининг ички томонига кийим учун крючкалар.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
@@ -2966,7 +3024,7 @@
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="5" t="n"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="88" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -2977,7 +3035,8 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Подключение варочной панели на кухне лицензированной газовой службой.</t>
+          <t>Подключение варочной панели на кухне лицензированной газовой службой.
+Ошхона варочная панелини лицензияли газ хизмати улайди.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -3000,7 +3059,7 @@
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
     </row>
-    <row r="33" ht="40" customHeight="1">
+    <row r="33" ht="88" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
@@ -3011,7 +3070,8 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Гидроизоляция под плиткой для защиты ванной от протечек.</t>
+          <t>Гидроизоляция под плиткой для защиты ванной от протечек.
+Ваннахонани сув сизишидан ҳимоя қилиш учун плитка остига гидроизоляция.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -3034,7 +3094,7 @@
       <c r="I33" s="5" t="n"/>
       <c r="J33" s="5" t="n"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="120" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -3045,7 +3105,8 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Две двойные розетки SH и SH2 для фена и зубной щётки у раковины; IP44 с крышками, УЗО.</t>
+          <t>Две двойные розетки SH и SH2 для фена и зубной щётки у раковины; IP44 с крышками, УЗО.
+Раковина ёнида фен ва тиш чўткаси учун SH ва SH2 икки кишилик иккита розетка; қопқоқли IP44, УЗО.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3072,7 +3133,7 @@
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
     </row>
-    <row r="35" ht="40" customHeight="1">
+    <row r="35" ht="72" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
@@ -3083,7 +3144,8 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Полка для шампуня в углу над ванной.</t>
+          <t>Полка для шампуня в углу над ванной.
+Ванна устидаги бурчакда шампунь учун полка.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
@@ -3106,7 +3168,7 @@
       <c r="I35" s="5" t="n"/>
       <c r="J35" s="5" t="n"/>
     </row>
-    <row r="36" ht="40" customHeight="1">
+    <row r="36" ht="72" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
@@ -3117,7 +3179,8 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Клинья СВП для выравнивания соседних плиток.</t>
+          <t>Клинья СВП для выравнивания соседних плиток.
+Ёнма-ён плиткаларни текислаш учун СВП клинлари.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -3140,7 +3203,7 @@
       <c r="I36" s="5" t="n"/>
       <c r="J36" s="5" t="n"/>
     </row>
-    <row r="37" ht="40" customHeight="1">
+    <row r="37" ht="88" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
@@ -3151,7 +3214,8 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Лента для герметизации углов и примыканий ванной под плиткой.</t>
+          <t>Лента для герметизации углов и примыканий ванной под плиткой.
+Ваннахонада плитка остида бурчак ва туташган жойларни герметик ёпиш учун лента.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -3174,7 +3238,7 @@
       <c r="I37" s="5" t="n"/>
       <c r="J37" s="5" t="n"/>
     </row>
-    <row r="38" ht="40" customHeight="1">
+    <row r="38" ht="88" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
@@ -3185,7 +3249,8 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Воздухоотводчик для удаления воздуха из отопления ванной.</t>
+          <t>Воздухоотводчик для удаления воздуха из отопления ванной.
+Ваннахона иситиш системасидан ҳавони чиқариш учун воздухоотводчик.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
@@ -3208,7 +3273,7 @@
       <c r="I38" s="5" t="n"/>
       <c r="J38" s="5" t="n"/>
     </row>
-    <row r="39" ht="40" customHeight="1">
+    <row r="39" ht="88" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
@@ -3219,7 +3284,8 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Полотенцесушитель над радиатором ванной для сушки полотенец.</t>
+          <t>Полотенцесушитель над радиатором ванной для сушки полотенец.
+Ваннахона радиатори устида сочиқларни қуритиш учун полотенцесушитель.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
@@ -3242,7 +3308,7 @@
       <c r="I39" s="5" t="n"/>
       <c r="J39" s="5" t="n"/>
     </row>
-    <row r="40" ht="40" customHeight="1">
+    <row r="40" ht="72" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
@@ -3253,7 +3319,8 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Подводка для подключения сантехники к воде в ванной.</t>
+          <t>Подводка для подключения сантехники к воде в ванной.
+Ваннахона сантехникасини сувга улаш учун подводка.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
@@ -3276,7 +3343,7 @@
       <c r="I40" s="5" t="n"/>
       <c r="J40" s="5" t="n"/>
     </row>
-    <row r="41" ht="40" customHeight="1">
+    <row r="41" ht="72" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
@@ -3287,7 +3354,8 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Зажимы СВП для ровных швов при укладке плитки.</t>
+          <t>Зажимы СВП для ровных швов при укладке плитки.
+Плитка ётқизишда текис чоклар учун СВП зажимлари.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -3310,7 +3378,7 @@
       <c r="I41" s="5" t="n"/>
       <c r="J41" s="5" t="n"/>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="104" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
@@ -3321,7 +3389,8 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Защитное отключение линий ванной при утечке тока, схему согласовать с электриком.</t>
+          <t>Защитное отключение линий ванной при утечке тока, схему согласовать с электриком.
+Ваннахона линияларида ток сизганда ҳимоя ўчириши учун, схемани электрик билан келишиш.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3348,7 +3417,7 @@
       <c r="I42" s="5" t="n"/>
       <c r="J42" s="5" t="n"/>
     </row>
-    <row r="43" ht="40" customHeight="1">
+    <row r="43" ht="72" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
@@ -3359,7 +3428,8 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Краны для подключения радиатора ванной к отоплению.</t>
+          <t>Краны для подключения радиатора ванной к отоплению.
+Ваннахона радиаторини иситишга улаш учун кранлар.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -3382,7 +3452,7 @@
       <c r="I43" s="5" t="n"/>
       <c r="J43" s="5" t="n"/>
     </row>
-    <row r="44" ht="40" customHeight="1">
+    <row r="44" ht="72" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
@@ -3393,7 +3463,8 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Прямой карниз для тканевой шторки вдоль ванны.</t>
+          <t>Прямой карниз для тканевой шторки вдоль ванны.
+Ванна бўйлаб матоли шторка учун тўғри карниз.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -3416,7 +3487,7 @@
       <c r="I44" s="5" t="n"/>
       <c r="J44" s="5" t="n"/>
     </row>
-    <row r="45" ht="56" customHeight="1">
+    <row r="45" ht="104" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
@@ -3427,7 +3498,8 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Коробка для соединений проводов ванной с доступом для обслуживания.</t>
+          <t>Коробка для соединений проводов ванной с доступом для обслуживания.
+Ваннахона симларини улаш ва хизмат кўрсатишга кириш учун коробка.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3454,7 +3526,7 @@
       <c r="I45" s="5" t="n"/>
       <c r="J45" s="5" t="n"/>
     </row>
-    <row r="46" ht="40" customHeight="1">
+    <row r="46" ht="72" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
@@ -3465,7 +3537,8 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Кабель для питания розетки ванной.</t>
+          <t>Кабель для питания розетки ванной.
+Ваннахона розеткасига ток келтириш учун кабель.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3492,7 +3565,7 @@
       <c r="I46" s="5" t="n"/>
       <c r="J46" s="5" t="n"/>
     </row>
-    <row r="47" ht="40" customHeight="1">
+    <row r="47" ht="72" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
@@ -3503,7 +3576,8 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Краны для подключения полотенцесушителя ванной.</t>
+          <t>Краны для подключения полотенцесушителя ванной.
+Ваннахона полотенцесушителини улаш учун кранлар.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -3526,7 +3600,7 @@
       <c r="I47" s="5" t="n"/>
       <c r="J47" s="5" t="n"/>
     </row>
-    <row r="48" ht="40" customHeight="1">
+    <row r="48" ht="88" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
@@ -3537,7 +3611,8 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Выключатель света и вентилятора ванной в прихожей у двери.</t>
+          <t>Выключатель света и вентилятора ванной в прихожей у двери.
+Ваннахона чироғи ва вентилятори учун Даҳлизда эшик ёнида выключатель.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3564,7 +3639,7 @@
       <c r="I48" s="5" t="n"/>
       <c r="J48" s="5" t="n"/>
     </row>
-    <row r="49" ht="40" customHeight="1">
+    <row r="49" ht="72" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
@@ -3575,7 +3650,8 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Кабель для освещения и вентилятора ванной.</t>
+          <t>Кабель для освещения и вентилятора ванной.
+Ваннахона чироқлари ва вентилятори учун кабель.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3602,7 +3678,7 @@
       <c r="I49" s="5" t="n"/>
       <c r="J49" s="5" t="n"/>
     </row>
-    <row r="50" ht="40" customHeight="1">
+    <row r="50" ht="72" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
@@ -3613,7 +3689,8 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Радиатор под полотенцесушителем для отопления ванной.</t>
+          <t>Радиатор под полотенцесушителем для отопления ванной.
+Ваннахонани иситиш учун полотенцесушитель остида радиатор.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -3636,7 +3713,7 @@
       <c r="I50" s="5" t="n"/>
       <c r="J50" s="5" t="n"/>
     </row>
-    <row r="51" ht="40" customHeight="1">
+    <row r="51" ht="72" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
@@ -3647,7 +3724,8 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Тканевая шторка, чтобы вода из ванны не попадала в проход.</t>
+          <t>Тканевая шторка, чтобы вода из ванны не попадала в проход.
+Ванна суви йўлакка сачрамаслиги учун матоли шторка.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -3670,7 +3748,7 @@
       <c r="I51" s="5" t="n"/>
       <c r="J51" s="5" t="n"/>
     </row>
-    <row r="52" ht="40" customHeight="1">
+    <row r="52" ht="88" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
@@ -3681,7 +3759,8 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Силикон для герметизации стыков сантехники ванной.</t>
+          <t>Силикон для герметизации стыков сантехники ванной.
+Ваннахона сантехникаси туташган жойларини герметик ёпиш учун силикон.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -3704,7 +3783,7 @@
       <c r="I52" s="5" t="n"/>
       <c r="J52" s="5" t="n"/>
     </row>
-    <row r="53" ht="40" customHeight="1">
+    <row r="53" ht="72" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
@@ -3715,7 +3794,8 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Крючки для полотенец на стене ванной со стороны зала.</t>
+          <t>Крючки для полотенец на стене ванной со стороны зала.
+Ваннахонанинг Зал томонидаги деворига сочиқ учун крючкалар.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -3738,7 +3818,7 @@
       <c r="I53" s="5" t="n"/>
       <c r="J53" s="5" t="n"/>
     </row>
-    <row r="54" ht="40" customHeight="1">
+    <row r="54" ht="72" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
@@ -3749,7 +3829,8 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Трубы для подачи воды к сантехнике ванной и кухни.</t>
+          <t>Трубы для подачи воды к сантехнике ванной и кухни.
+Ваннахона ва Ошхона сантехникасига сув келтириш учун трубалар.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -3772,7 +3853,7 @@
       <c r="I54" s="5" t="n"/>
       <c r="J54" s="5" t="n"/>
     </row>
-    <row r="55" ht="40" customHeight="1">
+    <row r="55" ht="88" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
@@ -3783,7 +3864,8 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Трубы для отвода стоков ванной и кухни к стояку.</t>
+          <t>Трубы для отвода стоков ванной и кухни к стояку.
+Ваннахона ва Ошхона оқова сувини стоякка олиб бориш учун трубалар.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
@@ -3806,7 +3888,7 @@
       <c r="I55" s="5" t="n"/>
       <c r="J55" s="5" t="n"/>
     </row>
-    <row r="56" ht="56" customHeight="1">
+    <row r="56" ht="104" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
@@ -3817,7 +3899,8 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркасини маҳкамлаш учун дюбель-гвоздлар.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -3840,7 +3923,7 @@
       <c r="I56" s="5" t="n"/>
       <c r="J56" s="5" t="n"/>
     </row>
-    <row r="57" ht="56" customHeight="1">
+    <row r="57" ht="104" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
@@ -3851,7 +3934,8 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.</t>
+          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХни каркасга маҳкамлаш учун саморезлар.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -3874,7 +3958,7 @@
       <c r="I57" s="5" t="n"/>
       <c r="J57" s="5" t="n"/>
     </row>
-    <row r="58" ht="56" customHeight="1">
+    <row r="58" ht="104" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
@@ -3885,7 +3969,8 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.</t>
+          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.
+Ваннахона, Ошхона, Даҳлиз потолоклари ҳамда Балкон деворлари ва потолоки учун панеллар.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -3908,7 +3993,7 @@
       <c r="I58" s="5" t="n"/>
       <c r="J58" s="5" t="n"/>
     </row>
-    <row r="59" ht="56" customHeight="1">
+    <row r="59" ht="104" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
@@ -3919,7 +4004,8 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси направляющийлари.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3946,7 +4032,7 @@
       <c r="I59" s="5" t="n"/>
       <c r="J59" s="5" t="n"/>
     </row>
-    <row r="60" ht="40" customHeight="1">
+    <row r="60" ht="72" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
@@ -3957,7 +4043,8 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси профили.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3984,7 +4071,7 @@
       <c r="I60" s="5" t="n"/>
       <c r="J60" s="5" t="n"/>
     </row>
-    <row r="61" ht="56" customHeight="1">
+    <row r="61" ht="104" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
@@ -3995,7 +4082,8 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ туташган жойларини ёпиш учун уголоклар.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -4022,7 +4110,7 @@
       <c r="I61" s="5" t="n"/>
       <c r="J61" s="5" t="n"/>
     </row>
-    <row r="62" ht="40" customHeight="1">
+    <row r="62" ht="72" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
@@ -4033,7 +4121,8 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Новая дверь ванной, открывается наружу в прихожую.</t>
+          <t>Новая дверь ванной, открывается наружу в прихожую.
+Ваннахонанинг янги эшиги, Даҳлизга ташқарига очилади.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -4136,7 +4225,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="88" customHeight="1">
+    <row r="2" ht="104" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -4147,7 +4236,8 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.</t>
+          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.
+Даҳлиз, Зал, Ошхона, Ваннахона ва Балкон полига бир хил рангли плитка.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4185,7 +4275,8 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Плитка для всех стен ванной и двух рабочих стен кухни.</t>
+          <t>Плитка для всех стен ванной и двух рабочих стен кухни.
+Ваннахонанинг барча деворлари ва Ошхонанинг икки иш девори учун плитка.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -4223,7 +4314,8 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.</t>
+          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда пол ва девор плиткасини ётқизиш учун клей.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -4250,7 +4342,7 @@
       <c r="I4" s="5" t="n"/>
       <c r="J4" s="5" t="n"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="88" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -4261,7 +4353,8 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Грунт, чтобы штукатурка и стяжка держались на старом основании.</t>
+          <t>Грунт, чтобы штукатурка и стяжка держались на старом основании.
+Штукатурка ва стяжка эски асосга яхши ёпишиши учун грунт.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
@@ -4284,7 +4377,7 @@
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="72" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -4295,7 +4388,8 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Цемент для новой стяжки полов в ремонтируемых комнатах.</t>
+          <t>Цемент для новой стяжки полов в ремонтируемых комнатах.
+Таъмирланадиган хоналарда янги пол стяжкаси учун цемент.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -4322,7 +4416,7 @@
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="72" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -4333,7 +4427,8 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Плёнка как разделительный слой под новой стяжкой полов.</t>
+          <t>Плёнка как разделительный слой под новой стяжкой полов.
+Янги пол стяжкаси остида ажратувчи қатлам учун плёнка.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -4360,7 +4455,7 @@
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="104" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -4371,7 +4466,8 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Грунтовка для старых оснований и новых поверхностей гипсокартона перед отделкой.</t>
+          <t>Грунтовка для старых оснований и новых поверхностей гипсокартона перед отделкой.
+Отделкадан олдин эски асослар ва янги гипсокартон юзалари учун грунтовка.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -4394,7 +4490,7 @@
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="72" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -4405,7 +4501,8 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Песок для раствора новой стяжки полов.</t>
+          <t>Песок для раствора новой стяжки полов.
+Янги пол стяжкаси раствори учун песок.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
@@ -4428,7 +4525,7 @@
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="72" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -4439,7 +4536,8 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Лента по краям стяжки, чтобы пол не упирался жёстко в стены.</t>
+          <t>Лента по краям стяжки, чтобы пол не упирался жёстко в стены.
+Стяжка деворларга қаттиқ тиралмаслиги учун четларига лента.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -4477,7 +4575,8 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Затирка для швов плитки на полах и стенах.</t>
+          <t>Затирка для швов плитки на полах и стенах.
+Пол ва девор плиткаси чоклари учун затирка.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -4504,7 +4603,7 @@
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
     </row>
-    <row r="12" ht="40" customHeight="1">
+    <row r="12" ht="72" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -4515,7 +4614,8 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Маяки, чтобы вывести стяжку полов на общий уровень.</t>
+          <t>Маяки, чтобы вывести стяжку полов на общий уровень.
+Пол стяжкасини умумий баландликка текислаш учун маяклар.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -4542,7 +4642,7 @@
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
     </row>
-    <row r="13" ht="40" customHeight="1">
+    <row r="13" ht="72" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -4553,7 +4653,8 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона кухни.</t>
+          <t>Шпаклёвка для заделки швов гипсокартона кухни.
+Ошхона гипсокартони чокларини ёпиш учун шпаклёвка.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -4580,7 +4681,7 @@
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
     </row>
-    <row r="14" ht="40" customHeight="1">
+    <row r="14" ht="72" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -4591,7 +4692,8 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стенам кухни.</t>
+          <t>Клей, чтобы приклеить гипсокартон к стенам кухни.
+Ошхона деворларига гипсокартонни ёпиштириш учун клей.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4618,7 +4720,7 @@
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="120" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -4629,7 +4731,8 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для второго слоя гипсокартона кухни; крепление согласовать с изготовителем системы.</t>
+          <t>Саморезы для второго слоя гипсокартона кухни; крепление согласовать с изготовителем системы.
+Ошхона гипсокартонининг иккинчи қатлами учун саморезлар; маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4656,7 +4759,7 @@
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
     </row>
-    <row r="16" ht="40" customHeight="1">
+    <row r="16" ht="72" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -4667,7 +4770,8 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона кухни.</t>
+          <t>Серпянка для укрепления швов гипсокартона кухни.
+Ошхона гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4694,7 +4798,7 @@
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="72" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -4705,7 +4809,8 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стен кухни перед отделкой.</t>
+          <t>Листы для выравнивания стен кухни перед отделкой.
+Отделкадан олдин Ошхона деворларини текислаш учун листлар.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4732,7 +4837,7 @@
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="104" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -4743,7 +4848,8 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Патрубок, чтобы подключить слив стиральной машины к сифону кухонной мойки.</t>
+          <t>Патрубок, чтобы подключить слив стиральной машины к сифону кухонной мойки.
+Стиральная машина сливини Ошхона мойкаси сифонига улаш учун патрубок.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -4766,7 +4872,7 @@
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
     </row>
-    <row r="19" ht="40" customHeight="1">
+    <row r="19" ht="72" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -4777,7 +4883,8 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Радиатор для отопления кухни под окном.</t>
+          <t>Радиатор для отопления кухни под окном.
+Ошхонани иситиш учун дераза остида радиатор.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
@@ -4800,7 +4907,7 @@
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
     </row>
-    <row r="20" ht="40" customHeight="1">
+    <row r="20" ht="72" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -4811,7 +4918,8 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Кран для перекрытия воды стиральной машине в кухне.</t>
+          <t>Кран для перекрытия воды стиральной машине в кухне.
+Ошхонадаги стиральная машина сувини ёпиш учун кран.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4838,7 +4946,7 @@
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="104" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -4849,7 +4957,8 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Заглушка для кухонного канализационного вывода до подключения мойки.</t>
+          <t>Заглушка для кухонного канализационного вывода до подключения мойки.
+Мойкани улагунча Ошхона канализация чиқишини ёпиш учун заглушка.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -4872,7 +4981,7 @@
       <c r="I21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
     </row>
-    <row r="22" ht="40" customHeight="1">
+    <row r="22" ht="72" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -4883,7 +4992,8 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Трубы для подачи воды к сантехнике ванной и кухни.</t>
+          <t>Трубы для подачи воды к сантехнике ванной и кухни.
+Ваннахона ва Ошхона сантехникасига сув келтириш учун трубалар.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -4906,7 +5016,7 @@
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
     </row>
-    <row r="23" ht="40" customHeight="1">
+    <row r="23" ht="88" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -4917,7 +5027,8 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Трубы для отвода стоков ванной и кухни к стояку.</t>
+          <t>Трубы для отвода стоков ванной и кухни к стояку.
+Ваннахона ва Ошхона оқова сувини стоякка олиб бориш учун трубалар.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -4940,7 +5051,7 @@
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
     </row>
-    <row r="24" ht="40" customHeight="1">
+    <row r="24" ht="72" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -4951,7 +5062,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Кабель линии QF5 для холодильника и вытяжки кухни.</t>
+          <t>Кабель линии QF5 для холодильника и вытяжки кухни.
+Ошхона холодильниги ва вытяжкаси QF5 линияси учун кабель.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -4978,7 +5090,7 @@
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
     </row>
-    <row r="25" ht="40" customHeight="1">
+    <row r="25" ht="72" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -4989,7 +5101,8 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Кабель линии QF4 для приборов кухни.</t>
+          <t>Кабель линии QF4 для приборов кухни.
+Ошхона жиҳозлари QF4 линияси учун кабель.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5016,7 +5129,7 @@
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
     </row>
-    <row r="26" ht="40" customHeight="1">
+    <row r="26" ht="72" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -5027,7 +5140,8 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Кабель отдельной линии стиральной машины в кухне.</t>
+          <t>Кабель отдельной линии стиральной машины в кухне.
+Ошхона стиральная машинасининг алоҳида линияси учун кабель.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5054,7 +5168,7 @@
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
     </row>
-    <row r="27" ht="32" customHeight="1">
+    <row r="27" ht="56" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
@@ -5065,7 +5179,8 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Розетка за холодильником кухни.</t>
+          <t>Розетка за холодильником кухни.
+Ошхона холодильниги орқасидаги розетка.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -5092,7 +5207,7 @@
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
     </row>
-    <row r="28" ht="40" customHeight="1">
+    <row r="28" ht="72" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
@@ -5103,7 +5218,8 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Розетка для вытяжки кухни за коробом воздуховода.</t>
+          <t>Розетка для вытяжки кухни за коробом воздуховода.
+Ошхона вытяжкаси учун воздуховод короби орқасида розетка.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -5130,7 +5246,7 @@
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="104" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
@@ -5141,7 +5257,8 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Розетки для чайника и приборов над свободной столешницей кухни.</t>
+          <t>Розетки для чайника и приборов над свободной столешницей кухни.
+Ошхонанинг бўш столешницаси устида чойнак ва жиҳозлар учун розеткалар.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -5168,7 +5285,7 @@
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
     </row>
-    <row r="30" ht="40" customHeight="1">
+    <row r="30" ht="72" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
@@ -5179,7 +5296,8 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Розетка для микроволновки на тумбе рядом с холодильником.</t>
+          <t>Розетка для микроволновки на тумбе рядом с холодильником.
+Холодильник ёнидаги тумбада микроволновка учун розетка.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -5206,7 +5324,7 @@
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="72" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
@@ -5217,7 +5335,8 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Розетка стиральной машины внутри тумбы мойки кухни.</t>
+          <t>Розетка стиральной машины внутри тумбы мойки кухни.
+Ошхона мойкаси тумбаси ичида стиральная машина розеткаси.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -5244,7 +5363,7 @@
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="5" t="n"/>
     </row>
-    <row r="32" ht="40" customHeight="1">
+    <row r="32" ht="72" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -5255,7 +5374,8 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Розетка поджига газовой панели в соседней кухонной тумбе.</t>
+          <t>Розетка поджига газовой панели в соседней кухонной тумбе.
+Ошхонанинг қўшни тумбасида газ панели поджиги учун розетка.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -5293,7 +5413,8 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Споты для освещения кухни.</t>
+          <t>Споты для освещения кухни.
+Ошхонани ёритиш учун спотлар.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -5320,7 +5441,7 @@
       <c r="I33" s="5" t="n"/>
       <c r="J33" s="5" t="n"/>
     </row>
-    <row r="34" ht="40" customHeight="1">
+    <row r="34" ht="88" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -5331,7 +5452,8 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Закладные для крепления спотов кухни до закрытия потолка.</t>
+          <t>Закладные для крепления спотов кухни до закрытия потолка.
+Потолок ёпилгунча Ошхона спотларини маҳкамлаш учун закладнойлар.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -5358,7 +5480,7 @@
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
     </row>
-    <row r="35" ht="40" customHeight="1">
+    <row r="35" ht="72" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
@@ -5369,7 +5491,8 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Выключатель света кухни со стороны ручки двери.</t>
+          <t>Выключатель света кухни со стороны ручки двери.
+Ошхона эшиги тутқичи томонида чироқ выключатели.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -5396,7 +5519,7 @@
       <c r="I35" s="5" t="n"/>
       <c r="J35" s="5" t="n"/>
     </row>
-    <row r="36" ht="56" customHeight="1">
+    <row r="36" ht="104" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
@@ -5407,7 +5530,8 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркасини маҳкамлаш учун дюбель-гвоздлар.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -5430,7 +5554,7 @@
       <c r="I36" s="5" t="n"/>
       <c r="J36" s="5" t="n"/>
     </row>
-    <row r="37" ht="56" customHeight="1">
+    <row r="37" ht="104" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
@@ -5441,7 +5565,8 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.</t>
+          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХни каркасга маҳкамлаш учун саморезлар.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -5464,7 +5589,7 @@
       <c r="I37" s="5" t="n"/>
       <c r="J37" s="5" t="n"/>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="104" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
@@ -5475,7 +5600,8 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.</t>
+          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.
+Ваннахона, Ошхона, Даҳлиз потолоклари ҳамда Балкон деворлари ва потолоки учун панеллар.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
@@ -5498,7 +5624,7 @@
       <c r="I38" s="5" t="n"/>
       <c r="J38" s="5" t="n"/>
     </row>
-    <row r="39" ht="56" customHeight="1">
+    <row r="39" ht="104" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
@@ -5509,7 +5635,8 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси направляющийлари.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5536,7 +5663,7 @@
       <c r="I39" s="5" t="n"/>
       <c r="J39" s="5" t="n"/>
     </row>
-    <row r="40" ht="40" customHeight="1">
+    <row r="40" ht="72" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
@@ -5547,7 +5674,8 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси профили.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5574,7 +5702,7 @@
       <c r="I40" s="5" t="n"/>
       <c r="J40" s="5" t="n"/>
     </row>
-    <row r="41" ht="56" customHeight="1">
+    <row r="41" ht="104" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
@@ -5585,7 +5713,8 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ туташган жойларини ёпиш учун уголоклар.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5612,7 +5741,7 @@
       <c r="I41" s="5" t="n"/>
       <c r="J41" s="5" t="n"/>
     </row>
-    <row r="42" ht="56" customHeight="1">
+    <row r="42" ht="104" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
@@ -5623,7 +5752,8 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Панель для готовки в кухонной столешнице, подключает газовая служба.</t>
+          <t>Панель для готовки в кухонной столешнице, подключает газовая служба.
+Ошхона столешницасида овқат тайёрлаш панели, газ хизмати улайди.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -5657,7 +5787,8 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Кухонные шкафы и столешница с местом для мойки, стиральной машины и панели.</t>
+          <t>Кухонные шкафы и столешница с местом для мойки, стиральной машины и панели.
+Мойка, стиральная машина ва панель учун жойли Ошхона шкафлари ва столешница.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5684,7 +5815,7 @@
       <c r="I43" s="5" t="n"/>
       <c r="J43" s="5" t="n"/>
     </row>
-    <row r="44" ht="40" customHeight="1">
+    <row r="44" ht="72" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
@@ -5695,7 +5826,8 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Микроволновка на отдельной тумбе рядом с холодильником кухни.</t>
+          <t>Микроволновка на отдельной тумбе рядом с холодильником кухни.
+Ошхона холодильниги ёнида алоҳида тумбага микроволновка.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -5718,7 +5850,7 @@
       <c r="I44" s="5" t="n"/>
       <c r="J44" s="5" t="n"/>
     </row>
-    <row r="45" ht="72" customHeight="1">
+    <row r="45" ht="104" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
@@ -5729,7 +5861,8 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Тумба для микроволновки рядом с холодильником, с вырезом под угол подоконника.</t>
+          <t>Тумба для микроволновки рядом с холодильником, с вырезом под угол подоконника.
+Холодильник ёнида микроволновка учун подоконник бурчагига ўйиқли тумба.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5836,7 +5969,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="88" customHeight="1">
+    <row r="2" ht="104" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -5847,7 +5980,8 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.</t>
+          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.
+Даҳлиз, Зал, Ошхона, Ваннахона ва Балкон полига бир хил рангли плитка.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -5885,7 +6019,8 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.</t>
+          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда пол ва девор плиткасини ётқизиш учун клей.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -5912,7 +6047,7 @@
       <c r="I3" s="5" t="n"/>
       <c r="J3" s="5" t="n"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="88" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -5923,7 +6058,8 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Грунт, чтобы штукатурка и стяжка держались на старом основании.</t>
+          <t>Грунт, чтобы штукатурка и стяжка держались на старом основании.
+Штукатурка ва стяжка эски асосга яхши ёпишиши учун грунт.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
@@ -5946,7 +6082,7 @@
       <c r="I4" s="5" t="n"/>
       <c r="J4" s="5" t="n"/>
     </row>
-    <row r="5" ht="40" customHeight="1">
+    <row r="5" ht="72" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -5957,7 +6093,8 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Цемент для новой стяжки полов в ремонтируемых комнатах.</t>
+          <t>Цемент для новой стяжки полов в ремонтируемых комнатах.
+Таъмирланадиган хоналарда янги пол стяжкаси учун цемент.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -5984,7 +6121,7 @@
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="72" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -5995,7 +6132,8 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Плёнка как разделительный слой под новой стяжкой полов.</t>
+          <t>Плёнка как разделительный слой под новой стяжкой полов.
+Янги пол стяжкаси остида ажратувчи қатлам учун плёнка.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -6022,7 +6160,7 @@
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="104" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -6033,7 +6171,8 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Штукатурка для выравнивания стен зала, которые не закрываются гипсокартоном.</t>
+          <t>Штукатурка для выравнивания стен зала, которые не закрываются гипсокартоном.
+Залда гипсокартон билан ёпилмайдиган деворларни текислаш учун штукатурка.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
@@ -6056,7 +6195,7 @@
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="104" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -6067,7 +6206,8 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Грунтовка для старых оснований и новых поверхностей гипсокартона перед отделкой.</t>
+          <t>Грунтовка для старых оснований и новых поверхностей гипсокартона перед отделкой.
+Отделкадан олдин эски асослар ва янги гипсокартон юзалари учун грунтовка.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -6090,7 +6230,7 @@
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="72" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -6101,7 +6241,8 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Песок для раствора новой стяжки полов.</t>
+          <t>Песок для раствора новой стяжки полов.
+Янги пол стяжкаси раствори учун песок.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
@@ -6124,7 +6265,7 @@
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="72" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -6135,7 +6276,8 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Лента по краям стяжки, чтобы пол не упирался жёстко в стены.</t>
+          <t>Лента по краям стяжки, чтобы пол не упирался жёстко в стены.
+Стяжка деворларга қаттиқ тиралмаслиги учун четларига лента.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -6173,7 +6315,8 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Затирка для швов плитки на полах и стенах.</t>
+          <t>Затирка для швов плитки на полах и стенах.
+Пол ва девор плиткаси чоклари учун затирка.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -6200,7 +6343,7 @@
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
     </row>
-    <row r="12" ht="40" customHeight="1">
+    <row r="12" ht="72" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -6211,7 +6354,8 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Маяки, чтобы вывести стяжку полов на общий уровень.</t>
+          <t>Маяки, чтобы вывести стяжку полов на общий уровень.
+Пол стяжкасини умумий баландликка текислаш учун маяклар.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -6238,7 +6382,7 @@
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="104" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -6249,7 +6393,8 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона на стене под ТВ в зале.</t>
+          <t>Шпаклёвка для заделки швов гипсокартона на стене под ТВ в зале.
+Залда ТВ ортидаги девор гипсокартони чокларини ёпиш учун шпаклёвка.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -6276,7 +6421,7 @@
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
     </row>
-    <row r="14" ht="40" customHeight="1">
+    <row r="14" ht="72" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -6287,7 +6432,8 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стене под ТВ в зале.</t>
+          <t>Клей, чтобы приклеить гипсокартон к стене под ТВ в зале.
+Залда ТВ ортидаги деворга гипсокартонни ёпиштириш учун клей.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -6314,7 +6460,7 @@
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="104" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -6325,7 +6471,8 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона на стене под ТВ в зале.</t>
+          <t>Серпянка для укрепления швов гипсокартона на стене под ТВ в зале.
+Залда ТВ ортидаги девор гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -6352,7 +6499,7 @@
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
     </row>
-    <row r="16" ht="40" customHeight="1">
+    <row r="16" ht="72" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -6363,7 +6510,8 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стены под ТВ в зале перед отделкой.</t>
+          <t>Листы для выравнивания стены под ТВ в зале перед отделкой.
+Отделкадан олдин Залдаги ТВ деворини текислаш учун листлар.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -6390,7 +6538,7 @@
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="104" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -6401,7 +6549,8 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Кондиционер зала: отдельная линия QF10; длина с запасом 15%, купить один раз.</t>
+          <t>Кондиционер зала: отдельная линия QF10; длина с запасом 15%, купить один раз.
+Зал кондиционери: алоҳида QF10 линияси; узунлик 15% захира билан, бир марта сотиб олинг.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -6428,7 +6577,7 @@
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
     </row>
-    <row r="18" ht="40" customHeight="1">
+    <row r="18" ht="72" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -6439,7 +6588,8 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Питание для уборки под кондиционером зала.</t>
+          <t>Питание для уборки под кондиционером зала.
+Зал кондиционери остида тозалаш жиҳози учун ток.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -6466,7 +6616,7 @@
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
     </row>
-    <row r="19" ht="40" customHeight="1">
+    <row r="19" ht="72" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -6477,7 +6627,8 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Отдельное питание кондиционера зала, QF10.</t>
+          <t>Отдельное питание кондиционера зала, QF10.
+Зал кондиционери учун алоҳида ток, QF10.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -6504,7 +6655,7 @@
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
     </row>
-    <row r="20" ht="40" customHeight="1">
+    <row r="20" ht="72" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -6515,7 +6666,8 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Розетка под телевизором на восточной стене зала.</t>
+          <t>Розетка под телевизором на восточной стене зала.
+Залнинг шарқий деворида телевизор остидаги розетка.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -6542,7 +6694,7 @@
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
     </row>
-    <row r="21" ht="40" customHeight="1">
+    <row r="21" ht="88" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -6553,7 +6705,8 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Зарядка у северной спинки дивана; розетка доступна сидя.</t>
+          <t>Зарядка у северной спинки дивана; розетка доступна сидя.
+Диваннинг шимолий суянчиғи ёнида зарядлаш; ўтириб фойдаланиш мумкин.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -6580,7 +6733,7 @@
       <c r="I21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
     </row>
-    <row r="22" ht="40" customHeight="1">
+    <row r="22" ht="72" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -6591,7 +6744,8 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Розетка в зале на простенке у окна.</t>
+          <t>Розетка в зале на простенке у окна.
+Залда дераза ёнидаги простенокда розетка.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6618,7 +6772,7 @@
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
     </row>
-    <row r="23" ht="40" customHeight="1">
+    <row r="23" ht="72" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -6629,7 +6783,8 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Питание на простенке окна зала выше радиатора.</t>
+          <t>Питание на простенке окна зала выше радиатора.
+Зал ойнаси ёнида, радиатордан юқорида ток олиш.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6656,7 +6811,7 @@
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
     </row>
-    <row r="24" ht="40" customHeight="1">
+    <row r="24" ht="72" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -6667,7 +6822,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Розетка и подключения за телевизором в зале.</t>
+          <t>Розетка и подключения за телевизором в зале.
+Залда телевизор орқасида розетка ва уланишлар.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6694,7 +6850,7 @@
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
     </row>
-    <row r="25" ht="40" customHeight="1">
+    <row r="25" ht="88" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -6705,7 +6861,8 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Розетка над северной спинкой углового дивана, доступная сидя.</t>
+          <t>Розетка над северной спинкой углового дивана, доступная сидя.
+Бурчакли диваннинг шимолий суянчиғи устида, ўтирган ҳолда фойдаланиш мумкин бўлган розетка.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6732,7 +6889,7 @@
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
     </row>
-    <row r="26" ht="40" customHeight="1">
+    <row r="26" ht="88" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -6743,7 +6900,8 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Розетка у южного торца углового дивана на западной стене зала.</t>
+          <t>Розетка у южного торца углового дивана на западной стене зала.
+Залнинг ғарбий деворида бурчакли диваннинг жанубий учидаги розетка.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -6770,7 +6928,7 @@
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
     </row>
-    <row r="27" ht="40" customHeight="1">
+    <row r="27" ht="72" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
@@ -6781,7 +6939,8 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Закладные для крепления спотов зала до закрытия потолка.</t>
+          <t>Закладные для крепления спотов зала до закрытия потолка.
+Потолок ёпилгунча Зал спотларини маҳкамлаш учун закладнойлар.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6808,7 +6967,7 @@
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
     </row>
-    <row r="28" ht="40" customHeight="1">
+    <row r="28" ht="72" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
@@ -6819,7 +6978,8 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Споты для освещения зала с разделением на две группы.</t>
+          <t>Споты для освещения зала с разделением на две группы.
+Зални икки гуруҳга ажратиб ёритиш учун спотлар.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6846,7 +7006,7 @@
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="104" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
@@ -6857,7 +7017,8 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Проходной выключатель для управления светом зала со второго места.</t>
+          <t>Проходной выключатель для управления светом зала со второго места.
+Зал чироғини иккинчи жойдан бошқариш учун проходной выключатель.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6884,7 +7045,7 @@
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
     </row>
-    <row r="30" ht="56" customHeight="1">
+    <row r="30" ht="104" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
@@ -6895,7 +7056,8 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Выключатель двух групп спотов зала, проходную схему согласовать с электриком.</t>
+          <t>Выключатель двух групп спотов зала, проходную схему согласовать с электриком.
+Зал спотларининг икки гуруҳи учун выключатель, проходной схемани электрик билан келишиш.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6922,7 +7084,7 @@
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
     </row>
-    <row r="31" ht="40" customHeight="1">
+    <row r="31" ht="72" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
@@ -6933,7 +7095,8 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Новая дверь между залом и прихожей.</t>
+          <t>Новая дверь между залом и прихожей.
+Зал билан Даҳлиз орасидаги янги эшик.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
@@ -6956,7 +7119,7 @@
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="5" t="n"/>
     </row>
-    <row r="32" ht="56" customHeight="1">
+    <row r="32" ht="72" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -6967,7 +7130,8 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Натяжной потолок для зала с местами под споты.</t>
+          <t>Натяжной потолок для зала с местами под споты.
+Зал учун спотлар жойи билан натяжной потолок.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -6990,7 +7154,7 @@
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
     </row>
-    <row r="33" ht="88" customHeight="1">
+    <row r="33" ht="104" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
@@ -7001,7 +7165,8 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Крепление наружного блока зала под решёткой балкона; анкеры после осмотра парапета.</t>
+          <t>Крепление наружного блока зала под решёткой балкона; анкеры после осмотра парапета.
+Зал ташқи блокини Балкон панжараси остига маҳкамлаш; парапет кўрилгач анкер танланади.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -7028,7 +7193,7 @@
       <c r="I33" s="5" t="n"/>
       <c r="J33" s="5" t="n"/>
     </row>
-    <row r="34" ht="88" customHeight="1">
+    <row r="34" ht="104" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -7039,7 +7204,8 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Защита наружного блока зала под балконной решёткой; размеры и крепление уточнить у мастера.</t>
+          <t>Защита наружного блока зала под балконной решёткой; размеры и крепление уточнить у мастера.
+Балкон панжараси остида Зал ташқи блокини ҳимоялаш; ўлчам ва маҳкамлашни устадан аниқланг.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7066,7 +7232,7 @@
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
     </row>
-    <row r="35" ht="88" customHeight="1">
+    <row r="35" ht="136" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
@@ -7077,7 +7243,8 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Первые 5 м медной трассы с изоляцией; медь сверх 5 м входит в дополнительный метр. Уточнить у мастера.</t>
+          <t>Первые 5 м медной трассы с изоляцией; медь сверх 5 м входит в дополнительный метр. Уточнить у мастера.
+Изоляцияли мис трассанинг дастлабки 5 м қисми; 5 м дан ортиқ мис қўшимча метр нархига кирган. Устадан аниқланг.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7104,7 +7271,7 @@
       <c r="I35" s="5" t="n"/>
       <c r="J35" s="5" t="n"/>
     </row>
-    <row r="36" ht="88" customHeight="1">
+    <row r="36" ht="120" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
@@ -7115,7 +7282,8 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Отвод конденсата наружу по трассе 5,03 м с постоянным уклоном; слив согласовать на месте.</t>
+          <t>Отвод конденсата наружу по трассе 5,03 м с постоянным уклоном; слив согласовать на месте.
+Конденсатни 5,03 м трасса бўйлаб доимий нишаб билан ташқарига чиқариш; оқизиш жойини келишинг.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7142,7 +7310,7 @@
       <c r="I36" s="5" t="n"/>
       <c r="J36" s="5" t="n"/>
     </row>
-    <row r="37" ht="88" customHeight="1">
+    <row r="37" ht="104" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
@@ -7153,7 +7321,8 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Монтаж и пуск кондиционера зала; базовая работа до 5 м, материалы отдельно.</t>
+          <t>Монтаж и пуск кондиционера зала; базовая работа до 5 м, материалы отдельно.
+Зал кондиционерини ўрнатиш ва ишга тушириш; 5 м гача асосий иш, материаллар алоҳида.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -7180,7 +7349,7 @@
       <c r="I37" s="5" t="n"/>
       <c r="J37" s="5" t="n"/>
     </row>
-    <row r="38" ht="88" customHeight="1">
+    <row r="38" ht="104" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
@@ -7191,12 +7360,13 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Две гильзы: через стену зала и через глухой парапет ниже остекления; стекло не сверлить.</t>
+          <t>Две гильзы: через стену зала и через глухой парапет ниже остекления; стекло не сверлить.
+Иккита гильза: Зал девори ва ойналашдан пастдаги ёпиқ парапет орқали; ойнани тешманг.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Фреоновая трасса 4,24 м; дренаж 5,03 м; первые 5 м отдельно, превышение с медью и монтажом; уточнить у мастера</t>
+          <t>Замена гильзы: труба ПВХ Ø75 × 0,5 м, 2 шт.; подрезать по стене</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
@@ -7229,7 +7399,8 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Кондиционер охлаждает зал; инвертор 9000 BTU, этап 4.</t>
+          <t>Кондиционер охлаждает зал; инвертор 9000 BTU, этап 4.
+Зални совитиш учун кондиционер; инвертор 9000 BTU, 4-босқич.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -7336,7 +7507,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="88" customHeight="1">
+    <row r="2" ht="104" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -7347,7 +7518,8 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.</t>
+          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.
+Даҳлиз, Зал, Ошхона, Ваннахона ва Балкон полига бир хил рангли плитка.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -7385,7 +7557,8 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.</t>
+          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда пол ва девор плиткасини ётқизиш учун клей.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -7412,7 +7585,7 @@
       <c r="I3" s="5" t="n"/>
       <c r="J3" s="5" t="n"/>
     </row>
-    <row r="4" ht="40" customHeight="1">
+    <row r="4" ht="88" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -7423,7 +7596,8 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Лёгкая засыпка, чтобы поднять пол балкона до нужного уровня.</t>
+          <t>Лёгкая засыпка, чтобы поднять пол балкона до нужного уровня.
+Балкон полини керакли баландликка кўтариш учун енгил тўлдиргич.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -7450,7 +7624,7 @@
       <c r="I4" s="5" t="n"/>
       <c r="J4" s="5" t="n"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="88" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -7461,7 +7635,8 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Грунт, чтобы штукатурка и стяжка держались на старом основании.</t>
+          <t>Грунт, чтобы штукатурка и стяжка держались на старом основании.
+Штукатурка ва стяжка эски асосга яхши ёпишиши учун грунт.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
@@ -7484,7 +7659,7 @@
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="88" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -7495,7 +7670,8 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Кирпич для закладки проёмов под балконом и перегородки внизу.</t>
+          <t>Кирпич для закладки проёмов под балконом и перегородки внизу.
+Балкон остидаги очиқ жойларни ёпиш ва пастда перегородка қилиш учун кирпич.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -7522,7 +7698,7 @@
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="72" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -7533,7 +7709,8 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Цемент для новой стяжки полов в ремонтируемых комнатах.</t>
+          <t>Цемент для новой стяжки полов в ремонтируемых комнатах.
+Таъмирланадиган хоналарда янги пол стяжкаси учун цемент.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -7560,7 +7737,7 @@
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
     </row>
-    <row r="8" ht="40" customHeight="1">
+    <row r="8" ht="72" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -7571,7 +7748,8 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Плёнка как разделительный слой под новой стяжкой полов.</t>
+          <t>Плёнка как разделительный слой под новой стяжкой полов.
+Янги пол стяжкаси остида ажратувчи қатлам учун плёнка.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -7598,7 +7776,7 @@
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
     </row>
-    <row r="9" ht="40" customHeight="1">
+    <row r="9" ht="72" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -7609,7 +7787,8 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Цемент для раствора при кладке под балконом.</t>
+          <t>Цемент для раствора при кладке под балконом.
+Балкон остидаги кладка раствори учун цемент.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -7636,7 +7815,7 @@
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
     </row>
-    <row r="10" ht="40" customHeight="1">
+    <row r="10" ht="72" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -7647,7 +7826,8 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Песок для раствора при кладке под балконом.</t>
+          <t>Песок для раствора при кладке под балконом.
+Балкон остидаги кладка раствори учун песок.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -7674,7 +7854,7 @@
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="104" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -7685,7 +7865,8 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Грунтовка для старых оснований и новых поверхностей гипсокартона перед отделкой.</t>
+          <t>Грунтовка для старых оснований и новых поверхностей гипсокартона перед отделкой.
+Отделкадан олдин эски асослар ва янги гипсокартон юзалари учун грунтовка.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
@@ -7708,7 +7889,7 @@
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
     </row>
-    <row r="12" ht="40" customHeight="1">
+    <row r="12" ht="72" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -7719,7 +7900,8 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Песок для раствора новой стяжки полов.</t>
+          <t>Песок для раствора новой стяжки полов.
+Янги пол стяжкаси раствори учун песок.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
@@ -7742,7 +7924,7 @@
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
     </row>
-    <row r="13" ht="40" customHeight="1">
+    <row r="13" ht="72" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -7753,7 +7935,8 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Лента по краям стяжки, чтобы пол не упирался жёстко в стены.</t>
+          <t>Лента по краям стяжки, чтобы пол не упирался жёстко в стены.
+Стяжка деворларга қаттиқ тиралмаслиги учун четларига лента.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -7791,7 +7974,8 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Затирка для швов плитки на полах и стенах.</t>
+          <t>Затирка для швов плитки на полах и стенах.
+Пол ва девор плиткаси чоклари учун затирка.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -7818,7 +8002,7 @@
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
     </row>
-    <row r="15" ht="40" customHeight="1">
+    <row r="15" ht="72" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -7829,7 +8013,8 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Маяки, чтобы вывести стяжку полов на общий уровень.</t>
+          <t>Маяки, чтобы вывести стяжку полов на общий уровень.
+Пол стяжкасини умумий баландликка текислаш учун маяклар.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -7856,7 +8041,7 @@
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="104" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -7867,7 +8052,8 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Решётки, чтобы оставить вентиляцию под балконом и закрыть вход грызунам.</t>
+          <t>Решётки, чтобы оставить вентиляцию под балконом и закрыть вход грызунам.
+Балкон остида вентиляцияни сақлаш ва кемирувчилар киришини тўсиш учун решёткалар.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -7894,7 +8080,7 @@
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
     </row>
-    <row r="17" ht="40" customHeight="1">
+    <row r="17" ht="72" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -7905,7 +8091,8 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Розетка на балконе у края окна, чтобы её не закрывала штора.</t>
+          <t>Розетка на балконе у края окна, чтобы её не закрывала штора.
+Балконда штора ёпиб қўймаслиги учун дераза четида розетка.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -7932,7 +8119,7 @@
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="104" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -7943,7 +8130,8 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Розетка питания роутера на внутреннем простенке балкона рядом с интернет-розеткой.</t>
+          <t>Розетка питания роутера на внутреннем простенке балкона рядом с интернет-розеткой.
+Балконнинг ички деворида интернет розеткаси ёнида роутерни қувватлаш розеткаси.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -7970,7 +8158,7 @@
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
     </row>
-    <row r="19" ht="40" customHeight="1">
+    <row r="19" ht="72" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -7981,7 +8169,8 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Питание для уборки под окном зала со стороны балкона.</t>
+          <t>Питание для уборки под окном зала со стороны балкона.
+Балкон томонида Зал ойнаси остида тозалаш жиҳози учун ток.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -8008,7 +8197,7 @@
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
     </row>
-    <row r="20" ht="40" customHeight="1">
+    <row r="20" ht="72" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -8019,7 +8208,8 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Зарядка над откидным столом балкона.</t>
+          <t>Зарядка над откидным столом балкона.
+Балконнинг йиғма столи устида зарядлаш.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -8046,7 +8236,7 @@
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
     </row>
-    <row r="21" ht="40" customHeight="1">
+    <row r="21" ht="72" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -8057,7 +8247,8 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Розетка на балконе на стене со стороны зала.</t>
+          <t>Розетка на балконе на стене со стороны зала.
+Балконнинг Зал томонидаги деворида розетка.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -8084,7 +8275,7 @@
       <c r="I21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
     </row>
-    <row r="22" ht="40" customHeight="1">
+    <row r="22" ht="72" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -8095,7 +8286,8 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Питание на парапете балкона, вне шкафа.</t>
+          <t>Питание на парапете балкона, вне шкафа.
+Балкон парапетида, шкафдан ташқарида ток олиш.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -8122,7 +8314,7 @@
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
     </row>
-    <row r="23" ht="40" customHeight="1">
+    <row r="23" ht="72" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -8133,7 +8325,8 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Влагозащищённые споты для освещения балкона.</t>
+          <t>Влагозащищённые споты для освещения балкона.
+Балконни ёритиш учун намликдан ҳимояланган спотлар.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -8160,7 +8353,7 @@
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
     </row>
-    <row r="24" ht="40" customHeight="1">
+    <row r="24" ht="88" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -8171,7 +8364,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Закладные для крепления спотов балкона до закрытия потолка.</t>
+          <t>Закладные для крепления спотов балкона до закрытия потолка.
+Потолок ёпилгунча Балкон спотларини маҳкамлаш учун закладнойлар.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -8198,7 +8392,7 @@
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
     </row>
-    <row r="25" ht="40" customHeight="1">
+    <row r="25" ht="72" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -8209,7 +8403,8 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Выключатель двух зон освещения балкона рядом с дверью.</t>
+          <t>Выключатель двух зон освещения балкона рядом с дверью.
+Балкон эшиги ёнида икки ёритиш зонаси выключатели.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -8236,7 +8431,7 @@
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="104" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
@@ -8247,7 +8442,8 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркасини маҳкамлаш учун дюбель-гвоздлар.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -8270,7 +8466,7 @@
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
     </row>
-    <row r="27" ht="56" customHeight="1">
+    <row r="27" ht="104" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
@@ -8281,7 +8477,8 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.</t>
+          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХни каркасга маҳкамлаш учун саморезлар.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -8304,7 +8501,7 @@
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
     </row>
-    <row r="28" ht="56" customHeight="1">
+    <row r="28" ht="104" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
@@ -8315,7 +8512,8 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.</t>
+          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.
+Ваннахона, Ошхона, Даҳлиз потолоклари ҳамда Балкон деворлари ва потолоки учун панеллар.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -8338,7 +8536,7 @@
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
     </row>
-    <row r="29" ht="56" customHeight="1">
+    <row r="29" ht="104" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
@@ -8349,7 +8547,8 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси направляющийлари.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -8376,7 +8575,7 @@
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
     </row>
-    <row r="30" ht="40" customHeight="1">
+    <row r="30" ht="72" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
@@ -8387,7 +8586,8 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси профили.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8414,7 +8614,7 @@
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
     </row>
-    <row r="31" ht="56" customHeight="1">
+    <row r="31" ht="104" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
@@ -8425,7 +8625,8 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.</t>
+          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ туташган жойларини ёпиш учун уголоклар.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8452,7 +8653,7 @@
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="5" t="n"/>
     </row>
-    <row r="32" ht="40" customHeight="1">
+    <row r="32" ht="72" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -8463,7 +8664,8 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Наружный козырёк для защиты балкона от осадков.</t>
+          <t>Наружный козырёк для защиты балкона от осадков.
+Балконни ёғиндан ҳимоя қилиш учун ташқи козырёк.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -8486,7 +8688,7 @@
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="72" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
@@ -8497,7 +8699,8 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Узкий шкаф на балконе с проходом канала вытяжки через верх.</t>
+          <t>Узкий шкаф на балконе с проходом канала вытяжки через верх.
+Балконда тепасидан вытяжка канали ўтадиган энсиз шкаф.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8524,7 +8727,7 @@
       <c r="I33" s="5" t="n"/>
       <c r="J33" s="5" t="n"/>
     </row>
-    <row r="34" ht="40" customHeight="1">
+    <row r="34" ht="72" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -8535,7 +8738,8 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Складной стол и стулья для балкона с сохранением прохода.</t>
+          <t>Складной стол и стулья для балкона с сохранением прохода.
+Балкон учун йўлакни сақлайдиган йиғма стол ва стуллар.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
@@ -8638,7 +8842,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
+    <row r="2" ht="72" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -8649,7 +8853,8 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Вентиль, чтобы перекрывать воду гигиеническому душу в туалете.</t>
+          <t>Вентиль, чтобы перекрывать воду гигиеническому душу в туалете.
+Ҳожатхонада гигиенический душ сувини ёпиш учун вентиль.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
@@ -8672,7 +8877,7 @@
       <c r="I2" s="5" t="n"/>
       <c r="J2" s="5" t="n"/>
     </row>
-    <row r="3" ht="40" customHeight="1">
+    <row r="3" ht="72" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -8683,7 +8888,8 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Гигиенический душ рядом с унитазом в готовом туалете.</t>
+          <t>Гигиенический душ рядом с унитазом в готовом туалете.
+Тайёр Ҳожатхонада унитаз ёнига гигиенический душ.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
@@ -8706,7 +8912,7 @@
       <c r="I3" s="5" t="n"/>
       <c r="J3" s="5" t="n"/>
     </row>
-    <row r="4" ht="40" customHeight="1">
+    <row r="4" ht="72" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -8717,7 +8923,8 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Держатель бумаги у унитаза в готовом туалете.</t>
+          <t>Держатель бумаги у унитаза в готовом туалете.
+Тайёр Ҳожатхонада унитаз ёнига қоғоз тутқич.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
@@ -8740,7 +8947,7 @@
       <c r="I4" s="5" t="n"/>
       <c r="J4" s="5" t="n"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="72" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -8751,7 +8958,8 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Водорозетки для крепления гигиенического душа в туалете.</t>
+          <t>Водорозетки для крепления гигиенического душа в туалете.
+Ҳожатхонада гигиенический душни маҳкамлаш учун водорозеткалар.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
@@ -8774,7 +8982,7 @@
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
     </row>
-    <row r="6" ht="40" customHeight="1">
+    <row r="6" ht="72" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -8785,7 +8993,8 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Тройники для ответвления воды к гигиеническому душу туалета.</t>
+          <t>Тройники для ответвления воды к гигиеническому душу туалета.
+Ҳожатхона гигиенический души учун сув тармоғига тройниклар.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
@@ -8808,7 +9017,7 @@
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="72" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -8819,7 +9028,8 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Отводы для поворотов труб гигиенического душа в туалете.</t>
+          <t>Отводы для поворотов труб гигиенического душа в туалете.
+Ҳожатхона гигиенический души трубаларини буриш учун отводлар.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
@@ -8842,7 +9052,7 @@
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
     </row>
-    <row r="8" ht="40" customHeight="1">
+    <row r="8" ht="72" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -8853,7 +9063,8 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Труба для подачи воды к гигиеническому душу туалета.</t>
+          <t>Труба для подачи воды к гигиеническому душу туалета.
+Ҳожатхона гигиенический душига сув келтириш учун труба.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -8956,7 +9167,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
+    <row r="2" ht="72" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -8967,7 +9178,8 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Кабель отдельной линии QF9 для кондиционера спальни.</t>
+          <t>Кабель отдельной линии QF9 для кондиционера спальни.
+Ётоқхона кондиционери алоҳида QF9 линияси учун кабель.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -8994,7 +9206,7 @@
       <c r="I2" s="5" t="n"/>
       <c r="J2" s="5" t="n"/>
     </row>
-    <row r="3" ht="40" customHeight="1">
+    <row r="3" ht="72" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -9005,7 +9217,8 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Розетка для кондиционера в готовой спальне.</t>
+          <t>Розетка для кондиционера в готовой спальне.
+Тайёр Ётоқхонада кондиционер учун розетка.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -9045,7 +9258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9123,7 +9336,8 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.</t>
+          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.
+Даҳлиз, Зал, Ошхона, Ваннахона ва Балкон полига бир хил рангли плитка.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -9162,7 +9376,8 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.</t>
+          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.
+Даҳлиз, Зал, Ошхона, Ваннахона ва Балкон полига бир хил рангли плитка.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -9201,7 +9416,8 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.</t>
+          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.
+Даҳлиз, Зал, Ошхона, Ваннахона ва Балкон полига бир хил рангли плитка.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9240,7 +9456,8 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.</t>
+          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.
+Даҳлиз, Зал, Ошхона, Ваннахона ва Балкон полига бир хил рангли плитка.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -9279,7 +9496,8 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.</t>
+          <t>Плитка для пола прихожей, зала, кухни, ванной и балкона в одном цвете.
+Даҳлиз, Зал, Ошхона, Ваннахона ва Балкон полига бир хил рангли плитка.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -9318,7 +9536,8 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Плитка для всех стен ванной и двух рабочих стен кухни.</t>
+          <t>Плитка для всех стен ванной и двух рабочих стен кухни.
+Ваннахонанинг барча деворлари ва Ошхонанинг икки иш девори учун плитка.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -9357,7 +9576,8 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Плитка для всех стен ванной и двух рабочих стен кухни.</t>
+          <t>Плитка для всех стен ванной и двух рабочих стен кухни.
+Ваннахонанинг барча деворлари ва Ошхонанинг икки иш девори учун плитка.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -9396,7 +9616,8 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.</t>
+          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда пол ва девор плиткасини ётқизиш учун клей.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -9435,7 +9656,8 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.</t>
+          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда пол ва девор плиткасини ётқизиш учун клей.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -9474,7 +9696,8 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.</t>
+          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда пол ва девор плиткасини ётқизиш учун клей.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -9513,7 +9736,8 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.</t>
+          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда пол ва девор плиткасини ётқизиш учун клей.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -9552,7 +9776,8 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.</t>
+          <t>Клей для укладки напольной и настенной плитки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда пол ва девор плиткасини ётқизиш учун клей.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -9580,7 +9805,7 @@
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="88" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -9591,7 +9816,8 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Грунт, чтобы штукатурка и стяжка держались на старом основании.</t>
+          <t>Грунт, чтобы штукатурка и стяжка держались на старом основании.
+Штукатурка ва стяжка эски асосга яхши ёпишиши учун грунт.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -9618,7 +9844,7 @@
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -9629,7 +9855,8 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Кирпич для закладки проёмов под балконом и перегородки внизу.</t>
+          <t>Кирпич для закладки проёмов под балконом и перегородки внизу.
+Балкон остидаги очиқ жойларни ёпиш ва пастда перегородка қилиш учун кирпич.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -9657,7 +9884,7 @@
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="72" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -9668,7 +9895,8 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Цемент для новой стяжки полов в ремонтируемых комнатах.</t>
+          <t>Цемент для новой стяжки полов в ремонтируемых комнатах.
+Таъмирланадиган хоналарда янги пол стяжкаси учун цемент.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -9696,7 +9924,7 @@
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="72" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -9707,7 +9935,8 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Плёнка как разделительный слой под новой стяжкой полов.</t>
+          <t>Плёнка как разделительный слой под новой стяжкой полов.
+Янги пол стяжкаси остида ажратувчи қатлам учун плёнка.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -9735,7 +9964,7 @@
       <c r="I17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
     </row>
-    <row r="18" ht="40" customHeight="1">
+    <row r="18" ht="72" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -9746,7 +9975,8 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Цемент для раствора при кладке под балконом.</t>
+          <t>Цемент для раствора при кладке под балконом.
+Балкон остидаги кладка раствори учун цемент.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -9774,7 +10004,7 @@
       <c r="I18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
     </row>
-    <row r="19" ht="40" customHeight="1">
+    <row r="19" ht="72" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -9785,7 +10015,8 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Песок для раствора при кладке под балконом.</t>
+          <t>Песок для раствора при кладке под балконом.
+Балкон остидаги кладка раствори учун песок.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -9813,7 +10044,7 @@
       <c r="I19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="104" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
@@ -9824,7 +10055,8 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Штукатурка для выравнивания стен зала, которые не закрываются гипсокартоном.</t>
+          <t>Штукатурка для выравнивания стен зала, которые не закрываются гипсокартоном.
+Залда гипсокартон билан ёпилмайдиган деворларни текислаш учун штукатурка.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -9851,7 +10083,7 @@
       <c r="I20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="104" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
@@ -9862,7 +10094,8 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Штукатурка для подготовки стен ванной и кухни под плитку, если понадобится на месте.</t>
+          <t>Штукатурка для подготовки стен ванной и кухни под плитку, если понадобится на месте.
+Керак бўлса, Ваннахона ва Ошхона деворларини плиткага тайёрлаш учун штукатурка.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -9889,7 +10122,7 @@
       <c r="I21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="104" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
@@ -9900,7 +10133,8 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Грунтовка для старых оснований и новых поверхностей гипсокартона перед отделкой.</t>
+          <t>Грунтовка для старых оснований и новых поверхностей гипсокартона перед отделкой.
+Отделкадан олдин эски асослар ва янги гипсокартон юзалари учун грунтовка.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -9927,7 +10161,7 @@
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
     </row>
-    <row r="23" ht="40" customHeight="1">
+    <row r="23" ht="72" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
@@ -9938,7 +10172,8 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Песок для раствора новой стяжки полов.</t>
+          <t>Песок для раствора новой стяжки полов.
+Янги пол стяжкаси раствори учун песок.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -9965,7 +10200,7 @@
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="104" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
@@ -9976,7 +10211,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Дополнительный песок для верхней стяжки балкона после замера уровня.</t>
+          <t>Дополнительный песок для верхней стяжки балкона после замера уровня.
+Баландлик ўлчангач, Балконнинг устки стяжкаси учун қўшимча песок.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -10007,7 +10243,7 @@
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
     </row>
-    <row r="25" ht="40" customHeight="1">
+    <row r="25" ht="72" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
@@ -10018,7 +10254,8 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Лента по краям стяжки, чтобы пол не упирался жёстко в стены.</t>
+          <t>Лента по краям стяжки, чтобы пол не упирался жёстко в стены.
+Стяжка деворларга қаттиқ тиралмаслиги учун четларига лента.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -10057,7 +10294,8 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Затирка для швов плитки на полах и стенах.</t>
+          <t>Затирка для швов плитки на полах и стенах.
+Пол ва девор плиткаси чоклари учун затирка.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -10096,7 +10334,8 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Затирка для швов плитки на полах и стенах.</t>
+          <t>Затирка для швов плитки на полах и стенах.
+Пол ва девор плиткаси чоклари учун затирка.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -10135,7 +10374,8 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Затирка для швов плитки на полах и стенах.</t>
+          <t>Затирка для швов плитки на полах и стенах.
+Пол ва девор плиткаси чоклари учун затирка.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -10174,7 +10414,8 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Затирка для швов плитки на полах и стенах.</t>
+          <t>Затирка для швов плитки на полах и стенах.
+Пол ва девор плиткаси чоклари учун затирка.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -10213,7 +10454,8 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Затирка для швов плитки на полах и стенах.</t>
+          <t>Затирка для швов плитки на полах и стенах.
+Пол ва девор плиткаси чоклари учун затирка.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -10241,7 +10483,7 @@
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
     </row>
-    <row r="31" ht="40" customHeight="1">
+    <row r="31" ht="72" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
@@ -10252,7 +10494,8 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Маяки, чтобы вывести стяжку полов на общий уровень.</t>
+          <t>Маяки, чтобы вывести стяжку полов на общий уровень.
+Пол стяжкасини умумий баландликка текислаш учун маяклар.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -10280,7 +10523,7 @@
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="5" t="n"/>
     </row>
-    <row r="32" ht="40" customHeight="1">
+    <row r="32" ht="72" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
@@ -10291,7 +10534,8 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>СВП для ровной укладки плитки на полах и стенах.</t>
+          <t>СВП для ровной укладки плитки на полах и стенах.
+Пол ва деворга плиткани текис ётқизиш учун СВП.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -10322,7 +10566,7 @@
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="72" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
@@ -10333,7 +10577,8 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для гладкой подготовки стен под краску.</t>
+          <t>Шпаклёвка для гладкой подготовки стен под краску.
+Деворларни краскага силлиқ тайёрлаш учун шпаклёвка.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -10365,7 +10610,7 @@
       <c r="I33" s="5" t="n"/>
       <c r="J33" s="5" t="n"/>
     </row>
-    <row r="34" ht="56" customHeight="1">
+    <row r="34" ht="104" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
@@ -10376,7 +10621,8 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Дополнительный цемент для верхней стяжки балкона после замера уровня.</t>
+          <t>Дополнительный цемент для верхней стяжки балкона после замера уровня.
+Баландлик ўлчангач, Балконнинг устки стяжкаси учун қўшимча цемент.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -10407,7 +10653,7 @@
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
     </row>
-    <row r="35" ht="40" customHeight="1">
+    <row r="35" ht="72" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
@@ -10418,7 +10664,8 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона ванной.</t>
+          <t>Шпаклёвка для заделки швов гипсокартона ванной.
+Ваннахона гипсокартони чокларини ёпиш учун шпаклёвка.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -10446,7 +10693,7 @@
       <c r="I35" s="5" t="n"/>
       <c r="J35" s="5" t="n"/>
     </row>
-    <row r="36" ht="40" customHeight="1">
+    <row r="36" ht="72" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
@@ -10457,7 +10704,8 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона прихожей.</t>
+          <t>Шпаклёвка для заделки швов гипсокартона прихожей.
+Даҳлиз гипсокартони чокларини ёпиш учун шпаклёвка.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -10485,7 +10733,7 @@
       <c r="I36" s="5" t="n"/>
       <c r="J36" s="5" t="n"/>
     </row>
-    <row r="37" ht="40" customHeight="1">
+    <row r="37" ht="72" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
@@ -10496,7 +10744,8 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона кухни.</t>
+          <t>Шпаклёвка для заделки швов гипсокартона кухни.
+Ошхона гипсокартони чокларини ёпиш учун шпаклёвка.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -10524,7 +10773,7 @@
       <c r="I37" s="5" t="n"/>
       <c r="J37" s="5" t="n"/>
     </row>
-    <row r="38" ht="56" customHeight="1">
+    <row r="38" ht="104" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
@@ -10535,7 +10784,8 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона на стене под ТВ в зале.</t>
+          <t>Шпаклёвка для заделки швов гипсокартона на стене под ТВ в зале.
+Залда ТВ ортидаги девор гипсокартони чокларини ёпиш учун шпаклёвка.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10563,7 +10813,7 @@
       <c r="I38" s="5" t="n"/>
       <c r="J38" s="5" t="n"/>
     </row>
-    <row r="39" ht="40" customHeight="1">
+    <row r="39" ht="72" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
@@ -10574,7 +10824,8 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стенам ванной.</t>
+          <t>Клей, чтобы приклеить гипсокартон к стенам ванной.
+Ваннахона деворларига гипсокартонни ёпиштириш учун клей.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10602,7 +10853,7 @@
       <c r="I39" s="5" t="n"/>
       <c r="J39" s="5" t="n"/>
     </row>
-    <row r="40" ht="40" customHeight="1">
+    <row r="40" ht="72" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
@@ -10613,7 +10864,8 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стенам прихожей.</t>
+          <t>Клей, чтобы приклеить гипсокартон к стенам прихожей.
+Даҳлиз деворларига гипсокартонни ёпиштириш учун клей.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10641,7 +10893,7 @@
       <c r="I40" s="5" t="n"/>
       <c r="J40" s="5" t="n"/>
     </row>
-    <row r="41" ht="40" customHeight="1">
+    <row r="41" ht="72" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
@@ -10652,7 +10904,8 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стенам кухни.</t>
+          <t>Клей, чтобы приклеить гипсокартон к стенам кухни.
+Ошхона деворларига гипсокартонни ёпиштириш учун клей.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10680,7 +10933,7 @@
       <c r="I41" s="5" t="n"/>
       <c r="J41" s="5" t="n"/>
     </row>
-    <row r="42" ht="40" customHeight="1">
+    <row r="42" ht="72" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
@@ -10691,7 +10944,8 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стене под ТВ в зале.</t>
+          <t>Клей, чтобы приклеить гипсокартон к стене под ТВ в зале.
+Залда ТВ ортидаги деворга гипсокартонни ёпиштириш учун клей.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -10719,7 +10973,7 @@
       <c r="I42" s="5" t="n"/>
       <c r="J42" s="5" t="n"/>
     </row>
-    <row r="43" ht="56" customHeight="1">
+    <row r="43" ht="120" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
@@ -10730,7 +10984,8 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для второго слоя гипсокартона ванной; крепление согласовать с изготовителем системы.</t>
+          <t>Саморезы для второго слоя гипсокартона ванной; крепление согласовать с изготовителем системы.
+Ваннахона гипсокартонининг иккинчи қатлами учун саморезлар; маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -10758,7 +11013,7 @@
       <c r="I43" s="5" t="n"/>
       <c r="J43" s="5" t="n"/>
     </row>
-    <row r="44" ht="56" customHeight="1">
+    <row r="44" ht="120" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
@@ -10769,7 +11024,8 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для второго слоя гипсокартона кухни; крепление согласовать с изготовителем системы.</t>
+          <t>Саморезы для второго слоя гипсокартона кухни; крепление согласовать с изготовителем системы.
+Ошхона гипсокартонининг иккинчи қатлами учун саморезлар; маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -10797,7 +11053,7 @@
       <c r="I44" s="5" t="n"/>
       <c r="J44" s="5" t="n"/>
     </row>
-    <row r="45" ht="40" customHeight="1">
+    <row r="45" ht="72" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
@@ -10808,7 +11064,8 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона ванной.</t>
+          <t>Серпянка для укрепления швов гипсокартона ванной.
+Ваннахона гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -10836,7 +11093,7 @@
       <c r="I45" s="5" t="n"/>
       <c r="J45" s="5" t="n"/>
     </row>
-    <row r="46" ht="40" customHeight="1">
+    <row r="46" ht="72" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
@@ -10847,7 +11104,8 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона прихожей.</t>
+          <t>Серпянка для укрепления швов гипсокартона прихожей.
+Даҳлиз гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -10875,7 +11133,7 @@
       <c r="I46" s="5" t="n"/>
       <c r="J46" s="5" t="n"/>
     </row>
-    <row r="47" ht="40" customHeight="1">
+    <row r="47" ht="72" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
@@ -10886,7 +11144,8 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона кухни.</t>
+          <t>Серпянка для укрепления швов гипсокартона кухни.
+Ошхона гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -10914,7 +11173,7 @@
       <c r="I47" s="5" t="n"/>
       <c r="J47" s="5" t="n"/>
     </row>
-    <row r="48" ht="56" customHeight="1">
+    <row r="48" ht="104" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
@@ -10925,7 +11184,8 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона на стене под ТВ в зале.</t>
+          <t>Серпянка для укрепления швов гипсокартона на стене под ТВ в зале.
+Залда ТВ ортидаги девор гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -10953,7 +11213,7 @@
       <c r="I48" s="5" t="n"/>
       <c r="J48" s="5" t="n"/>
     </row>
-    <row r="49" ht="56" customHeight="1">
+    <row r="49" ht="72" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
@@ -10964,7 +11224,8 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стен прихожей перед отделкой.</t>
+          <t>Листы для выравнивания стен прихожей перед отделкой.
+Отделкадан олдин Даҳлиз деворларини текислаш учун листлар.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -10992,7 +11253,7 @@
       <c r="I49" s="5" t="n"/>
       <c r="J49" s="5" t="n"/>
     </row>
-    <row r="50" ht="56" customHeight="1">
+    <row r="50" ht="72" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
@@ -11003,7 +11264,8 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стены под ТВ в зале перед отделкой.</t>
+          <t>Листы для выравнивания стены под ТВ в зале перед отделкой.
+Отделкадан олдин Залдаги ТВ деворини текислаш учун листлар.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -11042,7 +11304,8 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стен ванной перед отделкой.</t>
+          <t>Листы для выравнивания стен ванной перед отделкой.
+Отделкадан олдин Ваннахона деворларини текислаш учун листлар.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -11081,7 +11344,8 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стен кухни перед отделкой.</t>
+          <t>Листы для выравнивания стен кухни перед отделкой.
+Отделкадан олдин Ошхона деворларини текислаш учун листлар.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -11109,7 +11373,7 @@
       <c r="I52" s="5" t="n"/>
       <c r="J52" s="5" t="n"/>
     </row>
-    <row r="53" ht="40" customHeight="1">
+    <row r="53" ht="72" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
@@ -11120,7 +11384,8 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Трубы для подачи воды к сантехнике ванной и кухни.</t>
+          <t>Трубы для подачи воды к сантехнике ванной и кухни.
+Ваннахона ва Ошхона сантехникасига сув келтириш учун трубалар.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -11147,7 +11412,7 @@
       <c r="I53" s="5" t="n"/>
       <c r="J53" s="5" t="n"/>
     </row>
-    <row r="54" ht="40" customHeight="1">
+    <row r="54" ht="72" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
@@ -11158,7 +11423,8 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Отводы для поворотов канализации ванной и кухни.</t>
+          <t>Отводы для поворотов канализации ванной и кухни.
+Ваннахона ва Ошхона канализациясини буриш учун отводлар.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11185,7 +11451,7 @@
       <c r="I54" s="5" t="n"/>
       <c r="J54" s="5" t="n"/>
     </row>
-    <row r="55" ht="40" customHeight="1">
+    <row r="55" ht="88" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
@@ -11196,7 +11462,8 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Тройники для ответвлений воды к сантехнике ванной и кухни.</t>
+          <t>Тройники для ответвлений воды к сантехнике ванной и кухни.
+Ваннахона ва Ошхона сантехникасига сув тармоқлари учун тройниклар.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -11223,7 +11490,7 @@
       <c r="I55" s="5" t="n"/>
       <c r="J55" s="5" t="n"/>
     </row>
-    <row r="56" ht="40" customHeight="1">
+    <row r="56" ht="72" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
@@ -11234,7 +11501,8 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Тройники для объединения сливов ванной и кухни.</t>
+          <t>Тройники для объединения сливов ванной и кухни.
+Ваннахона ва Ошхона сливларини бирлаштириш учун тройниклар.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -11261,7 +11529,7 @@
       <c r="I56" s="5" t="n"/>
       <c r="J56" s="5" t="n"/>
     </row>
-    <row r="57" ht="40" customHeight="1">
+    <row r="57" ht="72" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
@@ -11272,7 +11540,8 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Угольники для поворотов водопроводных труб ванной и кухни.</t>
+          <t>Угольники для поворотов водопроводных труб ванной и кухни.
+Ваннахона ва Ошхона сув трубаларини буриш учун угольниклар.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -11299,7 +11568,7 @@
       <c r="I57" s="5" t="n"/>
       <c r="J57" s="5" t="n"/>
     </row>
-    <row r="58" ht="40" customHeight="1">
+    <row r="58" ht="88" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
@@ -11310,7 +11579,8 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Трубы для отвода стоков ванной и кухни к стояку.</t>
+          <t>Трубы для отвода стоков ванной и кухни к стояку.
+Ваннахона ва Ошхона оқова сувини стоякка олиб бориш учун трубалар.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -11337,7 +11607,7 @@
       <c r="I58" s="5" t="n"/>
       <c r="J58" s="5" t="n"/>
     </row>
-    <row r="59" ht="40" customHeight="1">
+    <row r="59" ht="72" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
@@ -11348,7 +11618,8 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Переходы для соединения труб с резьбовой сантехникой.</t>
+          <t>Переходы для соединения труб с резьбовой сантехникой.
+Трубаларни резьбали сантехникага улаш учун переходлар.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -11375,7 +11646,7 @@
       <c r="I59" s="5" t="n"/>
       <c r="J59" s="5" t="n"/>
     </row>
-    <row r="60" ht="40" customHeight="1">
+    <row r="60" ht="72" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
@@ -11386,7 +11657,8 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Труба для подачи воды к гигиеническому душу туалета.</t>
+          <t>Труба для подачи воды к гигиеническому душу туалета.
+Ҳожатхона гигиенический душига сув келтириш учун труба.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -11413,7 +11685,7 @@
       <c r="I60" s="5" t="n"/>
       <c r="J60" s="5" t="n"/>
     </row>
-    <row r="61" ht="40" customHeight="1">
+    <row r="61" ht="72" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
@@ -11424,7 +11696,8 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Муфты для соединения участков канализации ванной и кухни.</t>
+          <t>Муфты для соединения участков канализации ванной и кухни.
+Ваннахона ва Ошхона канализация қисмларини улаш учун муфталар.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -11451,7 +11724,7 @@
       <c r="I61" s="5" t="n"/>
       <c r="J61" s="5" t="n"/>
     </row>
-    <row r="62" ht="40" customHeight="1">
+    <row r="62" ht="72" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
@@ -11462,7 +11735,8 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Муфты для соединения водопроводных труб ванной и кухни.</t>
+          <t>Муфты для соединения водопроводных труб ванной и кухни.
+Ваннахона ва Ошхона сув трубаларини улаш учун муфталар.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -11489,7 +11763,7 @@
       <c r="I62" s="5" t="n"/>
       <c r="J62" s="5" t="n"/>
     </row>
-    <row r="63" ht="56" customHeight="1">
+    <row r="63" ht="104" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
@@ -11500,7 +11774,8 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Кабель-канал для отдельной линии кондиционера в готовой спальне.</t>
+          <t>Кабель-канал для отдельной линии кондиционера в готовой спальне.
+Тайёр Ётоқхонада кондиционернинг алоҳида линияси учун кабель-канал.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -11528,7 +11803,7 @@
       <c r="I63" s="5" t="n"/>
       <c r="J63" s="5" t="n"/>
     </row>
-    <row r="64" ht="40" customHeight="1">
+    <row r="64" ht="72" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
@@ -11539,7 +11814,8 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Кабель розеточной линии QF3 для зала, прихожей и балкона.</t>
+          <t>Кабель розеточной линии QF3 для зала, прихожей и балкона.
+Зал, Даҳлиз ва Балкон розеткалари QF3 линияси учун кабель.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -11567,7 +11843,7 @@
       <c r="I64" s="5" t="n"/>
       <c r="J64" s="5" t="n"/>
     </row>
-    <row r="65" ht="40" customHeight="1">
+    <row r="65" ht="72" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
@@ -11578,7 +11854,8 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Кабель для линий освещения ремонтируемых комнат.</t>
+          <t>Кабель для линий освещения ремонтируемых комнат.
+Таъмирланадиган хоналар чироқлари линиялари учун кабель.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -11606,7 +11883,7 @@
       <c r="I65" s="5" t="n"/>
       <c r="J65" s="5" t="n"/>
     </row>
-    <row r="66" ht="40" customHeight="1">
+    <row r="66" ht="72" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
@@ -11617,7 +11894,8 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Вводной кабель от счётчика на площадке к щиту в прихожей.</t>
+          <t>Вводной кабель от счётчика на площадке к щиту в прихожей.
+Майдонча счётчигидан Даҳлиз щитига кириш кабели.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -11645,7 +11923,7 @@
       <c r="I66" s="5" t="n"/>
       <c r="J66" s="5" t="n"/>
     </row>
-    <row r="67" ht="40" customHeight="1">
+    <row r="67" ht="72" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
@@ -11656,7 +11934,8 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Коаксиальный кабель для телевизионной точки в зале.</t>
+          <t>Коаксиальный кабель для телевизионной точки в зале.
+Залдаги телевизион нуқта учун коаксиальный кабель.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -11684,7 +11963,7 @@
       <c r="I67" s="5" t="n"/>
       <c r="J67" s="5" t="n"/>
     </row>
-    <row r="68" ht="40" customHeight="1">
+    <row r="68" ht="72" customHeight="1">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
@@ -11695,7 +11974,8 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Гофра для защиты проводки в ремонтируемых комнатах.</t>
+          <t>Гофра для защиты проводки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда симларни ҳимоя қилиш учун гофра.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -11723,7 +12003,7 @@
       <c r="I68" s="5" t="n"/>
       <c r="J68" s="5" t="n"/>
     </row>
-    <row r="69" ht="40" customHeight="1">
+    <row r="69" ht="72" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
@@ -11734,7 +12014,8 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Гофра для защиты проводки в ремонтируемых комнатах.</t>
+          <t>Гофра для защиты проводки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда симларни ҳимоя қилиш учун гофра.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -11762,7 +12043,7 @@
       <c r="I69" s="5" t="n"/>
       <c r="J69" s="5" t="n"/>
     </row>
-    <row r="70" ht="40" customHeight="1">
+    <row r="70" ht="72" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
@@ -11773,7 +12054,8 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Щит для защитных аппаратов внутри прихожей.</t>
+          <t>Щит для защитных аппаратов внутри прихожей.
+Даҳлиз ичида ҳимоя аппаратлари учун щит.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -11801,7 +12083,7 @@
       <c r="I70" s="5" t="n"/>
       <c r="J70" s="5" t="n"/>
     </row>
-    <row r="71" ht="56" customHeight="1">
+    <row r="71" ht="88" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
@@ -11812,7 +12094,8 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Коробки для доступных соединений проводов над дверями комнат.</t>
+          <t>Коробки для доступных соединений проводов над дверями комнат.
+Хоналар эшиклари устида сим уланишларига кириш учун коробкалар.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -11840,837 +12123,1058 @@
       <c r="I71" s="5" t="n"/>
       <c r="J71" s="5" t="n"/>
     </row>
-    <row r="72" ht="40" customHeight="1">
+    <row r="72" ht="136" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
+          <t>Автомат 1P C16/C10</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Автоматы для защиты линий от перегрузки и короткого замыкания. Количество и номиналы подтвердит электрик.
+Линияларни ортиқча юк ва қисқа туташувдан ҳимоя қилиш учун автоматлар. Сони ва номиналини электрик тасдиқлайди.</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>1P C16/C10; 9 шт. предварительно, полюсность линий кондиционеров уточнить
+Общее</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="n"/>
+    </row>
+    <row r="73" ht="136" customHeight="1">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>DIN-рейка, гребёнка и маркировка</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Крепление и соединение аппаратов щита, подписи линий. Рейки обычно входят в корпус; отдельно проверить комплектацию.
+Щит аппаратларини маҳкамлаш ва улаш, линияларга ёзув. Рейкалар одатда корпусга киради; комплектни текшириш.</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>DIN-рейки, однофазная гребёнка, маркировка; комплектацию уточнить
+Общее</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="n"/>
+      <c r="J73" s="5" t="n"/>
+    </row>
+    <row r="74" ht="104" customHeight="1">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Вводной автомат 2P 40A C</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Вводной автомат для отключения питания квартиры; номинал согласовать с электриком.
+Квартира токини ўчириш учун кириш автомати; номиналини электрик билан келишиш.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>2P 40A, характеристика C; проектный ориентир
+Общее</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="n"/>
+      <c r="J74" s="5" t="n"/>
+    </row>
+    <row r="75" ht="104" customHeight="1">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Шина N на DIN-изоляторе</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Отдельная шина для нейтральных проводников в щите; разделение после УЗО подтвердит электрик.
+Щитда нейтрал симлар учун алоҳида шина; УЗОдан кейин ажратишни электрик тасдиқлайди.</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>N на DIN-изоляторе; количество групп уточнить
+Общее</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="n"/>
+      <c r="J75" s="5" t="n"/>
+    </row>
+    <row r="76" ht="104" customHeight="1">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Шина PE на DIN-изоляторе</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Отдельная шина для защитного заземления, не соединять с N после УЗО.
+Ҳимоя ерлаш симлари учун алоҳида шина, УЗОдан кейин N билан уламаслик.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>PE на DIN-изоляторе; наличие PE проверить
+Общее</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="n"/>
+      <c r="J76" s="5" t="n"/>
+    </row>
+    <row r="77" ht="72" customHeight="1">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>Провод ПВ-3 4 мм² PE</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Защитный провод для заземления электропроводки квартиры.</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Защитный провод для заземления электропроводки квартиры.
+Квартира электропроводкасини заземление қилиш учун ҳимоя сими.</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>ПВ-3 4 мм² PE
 Общее</t>
         </is>
       </c>
-      <c r="E72" s="4" t="n">
+      <c r="E77" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G77" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="I72" s="5" t="n"/>
-      <c r="J72" s="5" t="n"/>
-    </row>
-    <row r="73" ht="56" customHeight="1">
-      <c r="A73" s="2" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="I77" s="5" t="n"/>
+      <c r="J77" s="5" t="n"/>
+    </row>
+    <row r="78" ht="104" customHeight="1">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>RJ45 и TV механизмы</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>RJ45 для роутера на балконе и антенный разъём для телевизора в зале.
+Балкондаги роутер учун RJ45 ва Залдаги телевизор учун антенна улагичи.</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>1 RJ45 + 1 TV; рамки и совместимость серии уточнить
+Общее</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="n"/>
+      <c r="J78" s="5" t="n"/>
+    </row>
+    <row r="79" ht="104" customHeight="1">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Подрозетники 60 мм</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Подрозетники для установки розеток в ремонтируемых комнатах.</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>60 мм; на двойную розетку два подрозетника
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Установочные коробки розеток и выключателей на стенах без гипсокартона.
+Гипсокартонсиз деворларда розетка ва выключатель ўрнатиш учун коробкалар.</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Кирпич/бетон, 68×45 мм; 29 отверстий + 10% = 32 шт.
 Общее</t>
         </is>
       </c>
-      <c r="E73" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="n">
-        <v>69</v>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="5" t="n"/>
-    </row>
-    <row r="74" ht="40" customHeight="1">
-      <c r="A74" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="E79" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="n"/>
+      <c r="J79" s="5" t="n"/>
+    </row>
+    <row r="80" ht="104" customHeight="1">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Подрозетники для гипсокартона</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Установочные коробки розеток и выключателей на стенах с гипсокартоном по плану.
+Режа бўйича гипсокартонли деворларда розетка ва выключатель ўрнатиш учун коробкалар.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Для гипсокартона; 33 отверстия + 10% = 37 шт.
+Общее</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="n"/>
+      <c r="J80" s="5" t="n"/>
+    </row>
+    <row r="81" ht="88" customHeight="1">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Клеммы WAGO 221-413</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Клеммы для соединений в щите и коробках прихожей.</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>WAGO 221-413
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Клеммы для соединений в щите и коробках прихожей.
+Даҳлиз щити ва коробкаларидаги уланишлар учун клеммалар.</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Клеммы WAGO 221-413; оригинал по выбору владельца, серию и подлинность проверить
 Общее</t>
         </is>
       </c>
-      <c r="E74" s="4" t="n">
+      <c r="E81" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="n">
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="n"/>
-      <c r="J74" s="5" t="n"/>
-    </row>
-    <row r="75" ht="72" customHeight="1">
-      <c r="A75" s="2" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>RJ45 и TV механизмы</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Интернет-розетка для роутера на балконе и антенная розетка за ТВ в зале.</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>BS — RJ45 на балконе; TH — антенна, без RJ45; H1 — обычная розетка
-Общее</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>комплект</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t>комплект</t>
-        </is>
-      </c>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="5" t="n"/>
-    </row>
-    <row r="76" ht="56" customHeight="1">
-      <c r="A76" s="2" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="n"/>
+      <c r="J81" s="5" t="n"/>
+    </row>
+    <row r="82" ht="88" customHeight="1">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>УЗО 30 мА, черновик до решения электрика</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>УЗО для защиты от утечки тока, состав щита решает электрик.</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>УЗО для защиты от утечки тока, состав щита решает электрик.
+Ток сизишидан ҳимоя учун УЗО, щит таркибини электрик ҳал қилади.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>30 мА; состав щита согласовать
 Общее</t>
         </is>
       </c>
-      <c r="E76" s="4" t="n">
+      <c r="E82" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="n">
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I76" s="5" t="n"/>
-      <c r="J76" s="5" t="n"/>
-    </row>
-    <row r="77" ht="56" customHeight="1">
-      <c r="A77" s="2" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Остальные аппараты щита, шины и маркировка</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Аппараты и маркировка для сборки щита прихожей по решению электрика.</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>DB; состав решает электрик
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="n"/>
+      <c r="J82" s="5" t="n"/>
+    </row>
+    <row r="83" ht="88" customHeight="1">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Клеммы WAGO 221-415</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Клеммы для соединений в щите и коробках прихожей.
+Даҳлиз щити ва коробкаларидаги уланишлар учун клеммалар.</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Клеммы WAGO 221-415; оригинал по выбору владельца, серию и подлинность проверить
 Общее</t>
         </is>
       </c>
-      <c r="E77" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>комплект</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>комплект</t>
-        </is>
-      </c>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="5" t="n"/>
-    </row>
-    <row r="78" ht="40" customHeight="1">
-      <c r="A78" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Клеммы WAGO 221-415</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Клеммы для соединений в щите и коробках прихожей.</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>WAGO 221-415
-Общее</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="n">
+      <c r="E83" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="n">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I78" s="5" t="n"/>
-      <c r="J78" s="5" t="n"/>
-    </row>
-    <row r="79" ht="56" customHeight="1">
-      <c r="A79" s="2" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="n"/>
+      <c r="J83" s="5" t="n"/>
+    </row>
+    <row r="84" ht="72" customHeight="1">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>Временное питание и свет бригады</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Временное питание и освещение для безопасной работы бригады.</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Временное питание и освещение для безопасной работы бригады.
+Бригаданинг хавфсиз ишлаши учун вақтинча ток ва ёритиш.</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>DB; безопасную схему решает электрик
 Общее</t>
         </is>
       </c>
-      <c r="E79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="E84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>комплект</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G84" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>комплект</t>
         </is>
       </c>
-      <c r="I79" s="5" t="n"/>
-      <c r="J79" s="5" t="n"/>
-    </row>
-    <row r="80" ht="40" customHeight="1">
-      <c r="A80" s="2" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="I84" s="5" t="n"/>
+      <c r="J84" s="5" t="n"/>
+    </row>
+    <row r="85" ht="88" customHeight="1">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>UTP cat.5e</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Сетевой кабель от ввода до роутера на балконе; ТВ по Wi-Fi.</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Сетевой кабель от ввода до роутера на балконе; ТВ по Wi-Fi.
+Киришдан Балкондаги роутергача тармоқ кабели; телевизор Wi-Fi орқали.</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>UTP cat.5e
 Общее</t>
         </is>
       </c>
-      <c r="E80" s="4" t="n">
+      <c r="E85" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G85" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
-      <c r="I80" s="5" t="n"/>
-      <c r="J80" s="5" t="n"/>
-    </row>
-    <row r="81" ht="56" customHeight="1">
-      <c r="A81" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="I85" s="5" t="n"/>
+      <c r="J85" s="5" t="n"/>
+    </row>
+    <row r="86" ht="104" customHeight="1">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>Дюбель-гвоздь 6×60</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркасини маҳкамлаш учун дюбель-гвоздлар.</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Запас и округление</t>
         </is>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="E86" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>кг</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G86" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>кг</t>
         </is>
       </c>
-      <c r="I81" s="5" t="n"/>
-      <c r="J81" s="5" t="n"/>
-    </row>
-    <row r="82" ht="56" customHeight="1">
-      <c r="A82" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="I86" s="5" t="n"/>
+      <c r="J86" s="5" t="n"/>
+    </row>
+    <row r="87" ht="104" customHeight="1">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>Саморезы-семечки</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХни каркасга маҳкамлаш учун саморезлар.</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Запас и округление</t>
         </is>
       </c>
-      <c r="E82" s="3" t="n">
+      <c r="E87" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>кг</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G87" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>кг</t>
         </is>
       </c>
-      <c r="I82" s="5" t="n"/>
-      <c r="J82" s="5" t="n"/>
-    </row>
-    <row r="83" ht="56" customHeight="1">
-      <c r="A83" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="I87" s="5" t="n"/>
+      <c r="J87" s="5" t="n"/>
+    </row>
+    <row r="88" ht="104" customHeight="1">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>ПВХ панели потолочные и балкон</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.
+Ваннахона, Ошхона, Даҳлиз потолоклари ҳамда Балкон деворлари ва потолоки учун панеллар.</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Запас и округление</t>
         </is>
       </c>
-      <c r="E83" s="3" t="n">
+      <c r="E88" s="3" t="n">
         <v>6.05</v>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>шт. по 1 м²</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G88" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>шт. по 1 м²</t>
         </is>
       </c>
-      <c r="I83" s="5" t="n"/>
-      <c r="J83" s="5" t="n"/>
-    </row>
-    <row r="84" ht="56" customHeight="1">
-      <c r="A84" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="I88" s="5" t="n"/>
+      <c r="J88" s="5" t="n"/>
+    </row>
+    <row r="89" ht="104" customHeight="1">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Направляющие для ПВХ</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси направляющийлари.</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>UD 3 м; совместимость подтвердить
 Запас и округление</t>
         </is>
       </c>
-      <c r="E84" s="3" t="n">
+      <c r="E89" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>шт. 3 м</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G89" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>шт. 3 м</t>
         </is>
       </c>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="5" t="n"/>
-    </row>
-    <row r="85" ht="56" customHeight="1">
-      <c r="A85" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="I89" s="5" t="n"/>
+      <c r="J89" s="5" t="n"/>
+    </row>
+    <row r="90" ht="72" customHeight="1">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Профиль для ПВХ</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси профили.</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>CD 3 м; совместимость подтвердить
 Запас и округление</t>
         </is>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="E90" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>шт. 3 м</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G90" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>шт. 3 м</t>
         </is>
       </c>
-      <c r="I85" s="5" t="n"/>
-      <c r="J85" s="5" t="n"/>
-    </row>
-    <row r="86" ht="56" customHeight="1">
-      <c r="A86" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="I90" s="5" t="n"/>
+      <c r="J90" s="5" t="n"/>
+    </row>
+    <row r="91" ht="104" customHeight="1">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Пластиковые уголки</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ туташган жойларини ёпиш учун уголоклар.</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Длина 3 м
 Запас и округление</t>
         </is>
       </c>
-      <c r="E86" s="3" t="n">
+      <c r="E91" s="3" t="n">
         <v>0.89</v>
       </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="n">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="n"/>
-      <c r="J86" s="5" t="n"/>
-    </row>
-    <row r="87" ht="56" customHeight="1">
-      <c r="A87" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="5" t="n"/>
+    </row>
+    <row r="92" ht="72" customHeight="1">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Плиссе</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Плиссе на окна кухни, зала и наружное остекление балкона.</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Плиссе на окна кухни, зала и наружное остекление балкона.
+Ошхона, Зал деразалари ва Балконнинг ташқи ойналарига плиссе.</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Замерить каждую секцию окна
 Без распределения</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I87" s="5" t="n"/>
-      <c r="J87" s="5" t="n"/>
-    </row>
-    <row r="88" ht="72" customHeight="1">
-      <c r="A88" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="n"/>
+      <c r="J92" s="5" t="n"/>
+    </row>
+    <row r="93" ht="104" customHeight="1">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Защитная клетка для наружного блока</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Клетка для защиты наружного блока кондиционера под решёткой окна спальни.</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Клетка для защиты наружного блока кондиционера под решёткой окна спальни.
+Ётоқхона деразаси решёткаси остидаги ташқи кондиционер блокини ҳимоя қилиш учун клетка.</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Наружный блок под решёткой окна спальни; отдельный подрядчик
 Без распределения</t>
         </is>
       </c>
-      <c r="E88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="n"/>
-      <c r="J88" s="5" t="n"/>
-    </row>
-    <row r="89" ht="40" customHeight="1">
-      <c r="A89" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="E93" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="5" t="n"/>
+    </row>
+    <row r="94" ht="88" customHeight="1">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Краска стен</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Краска для стен зала, прихожей и окрашиваемых участков кухни.</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Краска для стен зала, прихожей и окрашиваемых участков кухни.
+Зал, Даҳлиз деворлари ва Ошхонанинг бўяладиган қисмлари учун краска.</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Без распределения</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>комплект</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>комплект</t>
         </is>
       </c>
-      <c r="I89" s="5" t="n"/>
-      <c r="J89" s="5" t="n"/>
-    </row>
-    <row r="90" ht="56" customHeight="1">
-      <c r="A90" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="I94" s="5" t="n"/>
+      <c r="J94" s="5" t="n"/>
+    </row>
+    <row r="95" ht="104" customHeight="1">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Краска POLARD UNIVERSAL 10 кг</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Кандидат краски для стен, пригодность и моющуюся стойкость ещё нужно проверить.</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Кандидат краски для стен, пригодность и моющуюся стойкость ещё нужно проверить.
+Деворлар учун краска варианти, яроқлилиги ва ювилишга чидамлилигини текшириш керак.</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Без распределения</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>ведро 10 кг</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>ведро 10 кг</t>
         </is>
       </c>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="5" t="n"/>
-    </row>
-    <row r="91" ht="56" customHeight="1">
-      <c r="A91" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="I95" s="5" t="n"/>
+      <c r="J95" s="5" t="n"/>
+    </row>
+    <row r="96" ht="88" customHeight="1">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Стяжка старая: мешки/вывоз</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Мешки и вывоз мусора после демонтажа старой стяжки.</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Мешки и вывоз мусора после демонтажа старой стяжки.
+Эски стяжкани бузгандан кейин чиқинди учун қоплар ва олиб чиқиш.</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Общее</t>
         </is>
       </c>
-      <c r="E91" s="4" t="n">
+      <c r="E96" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>мешок 50 кг эквивалент</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G96" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>мешок 50 кг эквивалент</t>
         </is>
       </c>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="5" t="n"/>
-    </row>
-    <row r="92" ht="56" customHeight="1">
-      <c r="A92" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="I96" s="5" t="n"/>
+      <c r="J96" s="5" t="n"/>
+    </row>
+    <row r="97" ht="104" customHeight="1">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Газовая плита напольная 50–60 см</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Устаревшая позиция: напольную газовую плиту не заказывать, выбрана панель.</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Устаревшая позиция: напольную газовую плиту не заказывать, выбрана панель.
+Эски позиция: полга қўйиладиган газ плитасини буюртма қилманг, панель танланган.</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Не заказывать
 Без распределения</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>комплект</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>уточнить</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>комплект</t>
         </is>
       </c>
-      <c r="I92" s="5" t="n"/>
-      <c r="J92" s="5" t="n"/>
+      <c r="I97" s="5" t="n"/>
+      <c r="J97" s="5" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J92"/>
+  <autoFilter ref="A1:J97"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/materialy/материалы-по-комнатам.xlsx
+++ b/materialy/материалы-по-комнатам.xlsx
@@ -41,9 +41,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Спальня'!$A$1:$J$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Спальня'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Спальня'!$A$1:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'На всю квартиру'!$A$1:$J$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'На всю квартиру'!$A$1:$J$92</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'На всю квартиру'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'На всю квартиру'!$A$1:$J$97</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'На всю квартиру'!$A$1:$J$92</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="0"/>
 </workbook>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
     </row>
@@ -1179,7 +1179,7 @@
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
     </row>
-    <row r="13" ht="72" customHeight="1">
+    <row r="13" ht="104" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -1190,13 +1190,13 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стенам прихожей.
-Даҳлиз деворларига гипсокартонни ёпиштириш учун клей.</t>
+          <t>Клей для облицовки стен ванной, кухни, прихожей и зала гипсокартоном.
+Ваннахона, Ошхона, Даҳлиз ва Зал деворларини гипсокартон билан қоплаш учун клей.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Knauf Perlfix, 30 кг</t>
+          <t>Knauf Perlfix, 30 кг; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="G13" s="4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
     </row>
-    <row r="15" ht="72" customHeight="1">
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -1268,13 +1268,13 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стен прихожей перед отделкой.
-Отделкадан олдин Даҳлиз деворларини текислаш учун листлар.</t>
+          <t>Листы для выравнивания стен прихожей и зала перед отделкой.
+Отделкадан олдин Даҳлиз ва Зал деворларини текислаш учун листлар.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>ГКЛ 12,5 мм, 1200×2500, один слой</t>
+          <t>ГКЛ 12,5 мм, 1200×2500, один слой; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="G15" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
     </row>
-    <row r="14" ht="72" customHeight="1">
+    <row r="14" ht="104" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -2377,13 +2377,13 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стенам ванной.
-Ваннахона деворларига гипсокартонни ёпиштириш учун клей.</t>
+          <t>Клей для облицовки стен ванной, кухни, прихожей и зала гипсокартоном.
+Ваннахона, Ошхона, Даҳлиз ва Зал деворларини гипсокартон билан қоплаш учун клей.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Knauf Perlfix, 30 кг</t>
+          <t>Knauf Perlfix, 30 кг; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
     </row>
-    <row r="17" ht="72" customHeight="1">
+    <row r="17" ht="120" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -2494,13 +2494,13 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стен ванной перед отделкой.
-Отделкадан олдин Ваннахона деворларини текислаш учун листлар.</t>
+          <t>Влагостойкие листы для выравнивания стен ванной и кухни перед отделкой.
+Отделкадан олдин Ваннахона ва Ошхона деворларини текислаш учун намга чидамли листлар.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ГКЛВ 12,5 мм, 1200×2500, два слоя со смещением швов</t>
+          <t>ГКЛВ 12,5 мм, 1200×2500, один или два слоя по стенам чертежа, со смещением швов; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
     </row>
-    <row r="14" ht="72" customHeight="1">
+    <row r="14" ht="104" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -4692,13 +4692,13 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стенам кухни.
-Ошхона деворларига гипсокартонни ёпиштириш учун клей.</t>
+          <t>Клей для облицовки стен ванной, кухни, прихожей и зала гипсокартоном.
+Ваннахона, Ошхона, Даҳлиз ва Зал деворларини гипсокартон билан қоплаш учун клей.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Knauf Perlfix, 30 кг</t>
+          <t>Knauf Perlfix, 30 кг; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -4798,7 +4798,7 @@
       <c r="I16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
     </row>
-    <row r="17" ht="72" customHeight="1">
+    <row r="17" ht="120" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -4809,13 +4809,13 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стен кухни перед отделкой.
-Отделкадан олдин Ошхона деворларини текислаш учун листлар.</t>
+          <t>Влагостойкие листы для выравнивания стен ванной и кухни перед отделкой.
+Отделкадан олдин Ваннахона ва Ошхона деворларини текислаш учун намга чидамли листлар.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ГКЛВ 12,5 мм, 1200×2500, два слоя со смещением швов</t>
+          <t>ГКЛВ 12,5 мм, 1200×2500, один или два слоя по стенам чертежа, со смещением швов; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="G17" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -4878,22 +4878,26 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Радиатор кухни, краны и байпас</t>
+          <t>Кран стиральной машины 1/2″</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Радиатор для отопления кухни под окном.
-Ошхонани иситиш учун дераза остида радиатор.</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
+          <t>Кран для перекрытия воды стиральной машине в кухне.
+Ошхонадаги стиральная машина сувини ёпиш учун кран.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1/2″, кухня K7</t>
+        </is>
+      </c>
       <c r="E19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G19" s="4" t="n">
@@ -4901,7 +4905,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I19" s="5" t="n"/>
@@ -4913,26 +4917,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Кран стиральной машины 1/2″</t>
+          <t>Радиатор кухни, краны и байпас</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Кран для перекрытия воды стиральной машине в кухне.
-Ошхонадаги стиральная машина сувини ёпиш учун кран.</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>1/2″, кухня K7</t>
-        </is>
-      </c>
+          <t>Радиатор для отопления кухни под окном.
+Ошхонани иситиш учун дераза остида радиатор.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="G20" s="4" t="n">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="I20" s="5" t="n"/>
@@ -5776,7 +5776,7 @@
       <c r="I42" s="5" t="n"/>
       <c r="J42" s="5" t="n"/>
     </row>
-    <row r="43" ht="136" customHeight="1">
+    <row r="43" ht="232" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>K5 560 + K7 600 + K8 400 + K10 475 = 2035 мм; столешница 2035×600×40; мойка 500×500; навесные шкафы 1110 + 425 мм, глубина 320, высота 720, низ 1450 мм; изготовление после замера готовых стен</t>
+          <t>K5 560 + K7 600 + K8 400 + K10 475 = 2035 мм; столешница 2035×600×40; мойка 500×500; навесные шкафы 1110 + 425 мм, глубина 320, высота 720, низ 1450 мм; изготовление после замера готовых стен; врезная мойка для тумбы 0,56 м, внутренняя ширина около 488 мм; чаша вместе с сифоном не шире 488 мм — передать мебельщику</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
@@ -6421,7 +6421,7 @@
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
     </row>
-    <row r="14" ht="72" customHeight="1">
+    <row r="14" ht="104" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -6432,13 +6432,13 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стене под ТВ в зале.
-Залда ТВ ортидаги деворга гипсокартонни ёпиштириш учун клей.</t>
+          <t>Клей для облицовки стен ванной, кухни, прихожей и зала гипсокартоном.
+Ваннахона, Ошхона, Даҳлиз ва Зал деворларини гипсокартон билан қоплаш учун клей.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Knauf Perlfix, 30 кг</t>
+          <t>Knauf Perlfix, 30 кг; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -6450,7 +6450,7 @@
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
     </row>
-    <row r="16" ht="72" customHeight="1">
+    <row r="16" ht="88" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -6510,13 +6510,13 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стены под ТВ в зале перед отделкой.
-Отделкадан олдин Залдаги ТВ деворини текислаш учун листлар.</t>
+          <t>Листы для выравнивания стен прихожей и зала перед отделкой.
+Отделкадан олдин Даҳлиз ва Зал деворларини текислаш учун листлар.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>ГКЛ 12,5 мм, 1200×2500, один слой</t>
+          <t>ГКЛ 12,5 мм, 1200×2500, один слой; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10813,7 +10813,7 @@
       <c r="I38" s="5" t="n"/>
       <c r="J38" s="5" t="n"/>
     </row>
-    <row r="39" ht="72" customHeight="1">
+    <row r="39" ht="104" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
@@ -10824,18 +10824,18 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стенам ванной.
-Ваннахона деворларига гипсокартонни ёпиштириш учун клей.</t>
+          <t>Клей для облицовки стен ванной, кухни, прихожей и зала гипсокартоном.
+Ваннахона, Ошхона, Даҳлиз ва Зал деворларини гипсокартон билан қоплаш учун клей.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Knauf Perlfix, 30 кг
+          <t>Knauf Perlfix, 30 кг; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса
 Запас и округление</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1.29</v>
+        <v>2.01</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -10853,81 +10853,81 @@
       <c r="I39" s="5" t="n"/>
       <c r="J39" s="5" t="n"/>
     </row>
-    <row r="40" ht="72" customHeight="1">
+    <row r="40" ht="120" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Клей монтажный Knauf Perlfix 30 кг</t>
+          <t>Саморезы ГКЛ 3,5×35</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стенам прихожей.
-Даҳлиз деворларига гипсокартонни ёпиштириш учун клей.</t>
+          <t>Саморезы для второго слоя гипсокартона ванной; крепление согласовать с изготовителем системы.
+Ваннахона гипсокартонининг иккинчи қатлами учун саморезлар; маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Knauf Perlfix, 30 кг
+          <t>3,5×35; крепление второго слоя согласовать
 Запас и округление</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.65</v>
+        <v>0.49</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>мешок 30 кг</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>мешок 30 кг</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="I40" s="5" t="n"/>
       <c r="J40" s="5" t="n"/>
     </row>
-    <row r="41" ht="72" customHeight="1">
+    <row r="41" ht="120" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Клей монтажный Knauf Perlfix 30 кг</t>
+          <t>Саморезы ГКЛ 3,5×35</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стенам кухни.
-Ошхона деворларига гипсокартонни ёпиштириш учун клей.</t>
+          <t>Саморезы для второго слоя гипсокартона кухни; крепление согласовать с изготовителем системы.
+Ошхона гипсокартонининг иккинчи қатлами учун саморезлар; маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Knauf Perlfix, 30 кг
+          <t>3,5×35; крепление второго слоя согласовать
 Запас и округление</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1.44</v>
+        <v>0.63</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>мешок 30 кг</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>мешок 30 кг</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="I41" s="5" t="n"/>
@@ -10939,67 +10939,67 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Клей монтажный Knauf Perlfix 30 кг</t>
+          <t>Серпянка 90 м</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Клей, чтобы приклеить гипсокартон к стене под ТВ в зале.
-Залда ТВ ортидаги деворга гипсокартонни ёпиштириш учун клей.</t>
+          <t>Серпянка для укрепления швов гипсокартона ванной.
+Ваннахона гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Knauf Perlfix, 30 кг
+          <t>Серпянка, рулон 90 м
 Запас и округление</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>мешок 30 кг</t>
+          <t>рулон 90 м</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>мешок 30 кг</t>
+          <t>рулон 90 м</t>
         </is>
       </c>
       <c r="I42" s="5" t="n"/>
       <c r="J42" s="5" t="n"/>
     </row>
-    <row r="43" ht="120" customHeight="1">
+    <row r="43" ht="72" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Саморезы ГКЛ 3,5×35</t>
+          <t>Серпянка 90 м</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для второго слоя гипсокартона ванной; крепление согласовать с изготовителем системы.
-Ваннахона гипсокартонининг иккинчи қатлами учун саморезлар; маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
+          <t>Серпянка для укрепления швов гипсокартона прихожей.
+Даҳлиз гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3,5×35; крепление второго слоя согласовать
+          <t>Серпянка, рулон 90 м
 Запас и округление</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>рулон 90 м</t>
         </is>
       </c>
       <c r="G43" s="4" t="n">
@@ -11007,39 +11007,39 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>рулон 90 м</t>
         </is>
       </c>
       <c r="I43" s="5" t="n"/>
       <c r="J43" s="5" t="n"/>
     </row>
-    <row r="44" ht="120" customHeight="1">
+    <row r="44" ht="72" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Саморезы ГКЛ 3,5×35</t>
+          <t>Серпянка 90 м</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для второго слоя гипсокартона кухни; крепление согласовать с изготовителем системы.
-Ошхона гипсокартонининг иккинчи қатлами учун саморезлар; маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
+          <t>Серпянка для укрепления швов гипсокартона кухни.
+Ошхона гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>3,5×35; крепление второго слоя согласовать
+          <t>Серпянка, рулон 90 м
 Запас и округление</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>рулон 90 м</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
@@ -11047,13 +11047,13 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>рулон 90 м</t>
         </is>
       </c>
       <c r="I44" s="5" t="n"/>
       <c r="J44" s="5" t="n"/>
     </row>
-    <row r="45" ht="72" customHeight="1">
+    <row r="45" ht="104" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
@@ -11064,8 +11064,8 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона ванной.
-Ваннахона гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
+          <t>Серпянка для укрепления швов гипсокартона на стене под ТВ в зале.
+Залда ТВ ортидаги девор гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11075,7 +11075,7 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -11093,121 +11093,120 @@
       <c r="I45" s="5" t="n"/>
       <c r="J45" s="5" t="n"/>
     </row>
-    <row r="46" ht="72" customHeight="1">
+    <row r="46" ht="104" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Серпянка 90 м</t>
+          <t>ГКЛ 12,5 мм 1200×2500</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона прихожей.
-Даҳлиз гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
+          <t>Листы для выравнивания стен прихожей и зала перед отделкой.
+Отделкадан олдин Даҳлиз ва Зал деворларини текислаш учун листлар.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Серпянка, рулон 90 м
+          <t>ГКЛ 12,5 мм, 1200×2500, один слой; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса
 Запас и округление</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I46" s="5" t="n"/>
       <c r="J46" s="5" t="n"/>
     </row>
-    <row r="47" ht="72" customHeight="1">
+    <row r="47" ht="136" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Серпянка 90 м</t>
+          <t>ГКЛВ 12,5 мм 1200×2500</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона кухни.
-Ошхона гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
+          <t>Влагостойкие листы для выравнивания стен ванной и кухни перед отделкой.
+Отделкадан олдин Ваннахона ва Ошхона деворларини текислаш учун намга чидамли листлар.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Серпянка, рулон 90 м
+          <t>ГКЛВ 12,5 мм, 1200×2500, один или два слоя по стенам чертежа, со смещением швов; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса
 Запас и округление</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.72</v>
+        <v>2.45</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I47" s="5" t="n"/>
       <c r="J47" s="5" t="n"/>
     </row>
-    <row r="48" ht="104" customHeight="1">
+    <row r="48" ht="72" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Серпянка 90 м</t>
+          <t>Труба PP-R Ø20 PN20</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона на стене под ТВ в зале.
-Залда ТВ ортидаги девор гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
+          <t>Трубы для подачи воды к сантехнике ванной и кухни.
+Ваннахона ва Ошхона сантехникасига сув келтириш учун трубалар.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Серпянка, рулон 90 м
-Запас и округление</t>
+          <t>Запас и округление</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I48" s="5" t="n"/>
@@ -11219,23 +11218,22 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ГКЛ 12,5 мм 1200×2500</t>
+          <t>Отвод канализационный Ø50</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стен прихожей перед отделкой.
-Отделкадан олдин Даҳлиз деворларини текислаш учун листлар.</t>
+          <t>Отводы для поворотов канализации ванной и кухни.
+Ваннахона ва Ошхона канализациясини буриш учун отводлар.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>ГКЛ 12,5 мм, 1200×2500, один слой
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>1.3</v>
+          <t>Без распределения</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -11243,7 +11241,7 @@
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -11253,29 +11251,28 @@
       <c r="I49" s="5" t="n"/>
       <c r="J49" s="5" t="n"/>
     </row>
-    <row r="50" ht="72" customHeight="1">
+    <row r="50" ht="88" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>ГКЛ 12,5 мм 1200×2500</t>
+          <t>Тройник PP-R Ø20</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стены под ТВ в зале перед отделкой.
-Отделкадан олдин Залдаги ТВ деворини текислаш учун листлар.</t>
+          <t>Тройники для ответвлений воды к сантехнике ванной и кухни.
+Ваннахона ва Ошхона сантехникасига сув тармоқлари учун тройниклар.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>ГКЛ 12,5 мм, 1200×2500, один слой
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>1.26</v>
+          <t>Без распределения</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -11283,7 +11280,7 @@
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -11299,23 +11296,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>ГКЛВ 12,5 мм 1200×2500</t>
+          <t>Тройник канализационный Ø50</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стен ванной перед отделкой.
-Отделкадан олдин Ваннахона деворларини текислаш учун листлар.</t>
+          <t>Тройники для объединения сливов ванной и кухни.
+Ваннахона ва Ошхона сливларини бирлаштириш учун тройниклар.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>ГКЛВ 12,5 мм, 1200×2500, два слоя со смещением швов
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>1.58</v>
+          <t>Без распределения</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -11323,7 +11319,7 @@
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -11339,23 +11335,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>ГКЛВ 12,5 мм 1200×2500</t>
+          <t>Угольник PP-R Ø20</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стен кухни перед отделкой.
-Отделкадан олдин Ошхона деворларини текислаш учун листлар.</t>
+          <t>Угольники для поворотов водопроводных труб ванной и кухни.
+Ваннахона ва Ошхона сув трубаларини буриш учун угольниклар.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>ГКЛВ 12,5 мм, 1200×2500, два слоя со смещением швов
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>1.87</v>
+          <t>Без распределения</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -11363,7 +11358,7 @@
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -11373,19 +11368,19 @@
       <c r="I52" s="5" t="n"/>
       <c r="J52" s="5" t="n"/>
     </row>
-    <row r="53" ht="72" customHeight="1">
+    <row r="53" ht="88" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Труба PP-R Ø20 PN20</t>
+          <t>Труба канализационная ПВХ Ø50</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Трубы для подачи воды к сантехнике ванной и кухни.
-Ваннахона ва Ошхона сантехникасига сув келтириш учун трубалар.</t>
+          <t>Трубы для отвода стоков ванной и кухни к стояку.
+Ваннахона ва Ошхона оқова сувини стоякка олиб бориш учун трубалар.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -11394,7 +11389,7 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>10.2</v>
+        <v>0.51</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -11402,7 +11397,7 @@
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -11418,13 +11413,13 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный Ø50</t>
+          <t>Переход PP-R с резьбой 20×½″</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Отводы для поворотов канализации ванной и кухни.
-Ваннахона ва Ошхона канализациясини буриш учун отводлар.</t>
+          <t>Переходы для соединения труб с резьбовой сантехникой.
+Трубаларни резьбали сантехникага улаш учун переходлар.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11451,40 +11446,40 @@
       <c r="I54" s="5" t="n"/>
       <c r="J54" s="5" t="n"/>
     </row>
-    <row r="55" ht="88" customHeight="1">
+    <row r="55" ht="72" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Тройник PP-R Ø20</t>
+          <t>Труба PP-R Ø20 PN20 для гигиенического душа</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Тройники для ответвлений воды к сантехнике ванной и кухни.
-Ваннахона ва Ошхона сантехникасига сув тармоқлари учун тройниклар.</t>
+          <t>Труба для подачи воды к гигиеническому душу туалета.
+Ҳожатхона гигиенический душига сув келтириш учун труба.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Без распределения</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>3</v>
+          <t>Запас и округление</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0.68</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I55" s="5" t="n"/>
@@ -11496,13 +11491,13 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный Ø50</t>
+          <t>Муфта канализационная Ø50</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Тройники для объединения сливов ванной и кухни.
-Ваннахона ва Ошхона сливларини бирлаштириш учун тройниклар.</t>
+          <t>Муфты для соединения участков канализации ванной и кухни.
+Ваннахона ва Ошхона канализация қисмларини улаш учун муфталар.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -11511,7 +11506,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -11519,7 +11514,7 @@
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -11535,13 +11530,13 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Угольник PP-R Ø20</t>
+          <t>Муфта PP-R Ø20</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Угольники для поворотов водопроводных труб ванной и кухни.
-Ваннахона ва Ошхона сув трубаларини буриш учун угольниклар.</t>
+          <t>Муфты для соединения водопроводных труб ванной и кухни.
+Ваннахона ва Ошхона сув трубаларини улаш учун муфталар.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -11550,7 +11545,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -11558,7 +11553,7 @@
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -11568,28 +11563,29 @@
       <c r="I57" s="5" t="n"/>
       <c r="J57" s="5" t="n"/>
     </row>
-    <row r="58" ht="88" customHeight="1">
+    <row r="58" ht="104" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Труба канализационная ПВХ Ø50</t>
+          <t>Кабель-канал 40×25 спальня AC</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Трубы для отвода стоков ванной и кухни к стояку.
-Ваннахона ва Ошхона оқова сувини стоякка олиб бориш учун трубалар.</t>
+          <t>Кабель-канал для отдельной линии кондиционера в готовой спальне.
+Тайёр Ётоқхонада кондиционернинг алоҳида линияси учун кабель-канал.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Запас и округление</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>0.51</v>
+          <t>40×25; QF9, спальня
+Общее</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -11597,7 +11593,7 @@
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -11613,34 +11609,35 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Переход PP-R с резьбой 20×½″</t>
+          <t>ВВГнг(А)-LS 3×2,5</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Переходы для соединения труб с резьбовой сантехникой.
-Трубаларни резьбали сантехникага улаш учун переходлар.</t>
+          <t>Кабель розеточной линии QF3 для зала, прихожей и балкона.
+Зал, Даҳлиз ва Балкон розеткалари QF3 линияси учун кабель.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Без распределения</t>
+          <t>ВВГнг(А)-LS 3×2,5; QF3
+Общее</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>4</v>
+        <v>97</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I59" s="5" t="n"/>
@@ -11652,22 +11649,23 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Труба PP-R Ø20 PN20 для гигиенического душа</t>
+          <t>ВВГнг(А)-LS 3×1,5</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Труба для подачи воды к гигиеническому душу туалета.
-Ҳожатхона гигиенический душига сув келтириш учун труба.</t>
+          <t>Кабель для линий освещения ремонтируемых комнат.
+Таъмирланадиган хоналар чироқлари линиялари учун кабель.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Запас и округление</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>0.68</v>
+          <t>ВВГнг(А)-LS 3×1,5; L1/L2
+Общее</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>103</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -11675,7 +11673,7 @@
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>2</v>
+        <v>103</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
@@ -11691,34 +11689,35 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Муфта канализационная Ø50</t>
+          <t>ВВГнг(А)-LS 3×6, ввод от счётчика до щита</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Муфты для соединения участков канализации ванной и кухни.
-Ваннахона ва Ошхона канализация қисмларини улаш учун муфталар.</t>
+          <t>Вводной кабель от счётчика на площадке к щиту в прихожей.
+Майдонча счётчигидан Даҳлиз щитига кириш кабели.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Без распределения</t>
+          <t>ВВГнг(А)-LS 3×6
+Общее</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I61" s="5" t="n"/>
@@ -11730,62 +11729,63 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Муфта PP-R Ø20</t>
+          <t>Коаксиал RG-6</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Муфты для соединения водопроводных труб ванной и кухни.
-Ваннахона ва Ошхона сув трубаларини улаш учун муфталар.</t>
+          <t>Коаксиальный кабель для телевизионной точки в зале.
+Залдаги телевизион нуқта учун коаксиальный кабель.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Без распределения</t>
+          <t>RG-6
+Общее</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I62" s="5" t="n"/>
       <c r="J62" s="5" t="n"/>
     </row>
-    <row r="63" ht="104" customHeight="1">
+    <row r="63" ht="72" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Кабель-канал 40×25 спальня AC</t>
+          <t>Гофра Ø16 мм</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Кабель-канал для отдельной линии кондиционера в готовой спальне.
-Тайёр Ётоқхонада кондиционернинг алоҳида линияси учун кабель-канал.</t>
+          <t>Гофра для защиты проводки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда симларни ҳимоя қилиш учун гофра.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>40×25; QF9, спальня
+          <t>Ø16 мм
 Общее</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -11809,23 +11809,23 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-LS 3×2,5</t>
+          <t>Гофра Ø20 мм</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Кабель розеточной линии QF3 для зала, прихожей и балкона.
-Зал, Даҳлиз ва Балкон розеткалари QF3 линияси учун кабель.</t>
+          <t>Гофра для защиты проводки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда симларни ҳимоя қилиш учун гофра.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-LS 3×2,5; QF3
+          <t>Ø20 мм
 Общее</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
@@ -11849,218 +11849,218 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-LS 3×1,5</t>
+          <t>Щит накладной IP41, 2×12 модулей</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Кабель для линий освещения ремонтируемых комнат.
-Таъмирланадиган хоналар чироқлари линиялари учун кабель.</t>
+          <t>Щит для защитных аппаратов внутри прихожей.
+Даҳлиз ичида ҳимоя аппаратлари учун щит.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-LS 3×1,5; L1/L2
+          <t>IP41, 2×12 модулей
 Общее</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I65" s="5" t="n"/>
       <c r="J65" s="5" t="n"/>
     </row>
-    <row r="66" ht="72" customHeight="1">
+    <row r="66" ht="88" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-LS 3×6, ввод от счётчика до щита</t>
+          <t>Распаячные коробки</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Вводной кабель от счётчика на площадке к щиту в прихожей.
-Майдонча счётчигидан Даҳлиз щитига кириш кабели.</t>
+          <t>Коробки для доступных соединений проводов над дверями комнат.
+Хоналар эшиклари устида сим уланишларига кириш учун коробкалар.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-LS 3×6
+          <t>Размер и защиту согласовать с электриком
 Общее</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I66" s="5" t="n"/>
       <c r="J66" s="5" t="n"/>
     </row>
-    <row r="67" ht="72" customHeight="1">
+    <row r="67" ht="136" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Коаксиал RG-6</t>
+          <t>Автомат 1P C16/C10</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Коаксиальный кабель для телевизионной точки в зале.
-Залдаги телевизион нуқта учун коаксиальный кабель.</t>
+          <t>Автоматы для защиты линий от перегрузки и короткого замыкания. Количество и номиналы подтвердит электрик.
+Линияларни ортиқча юк ва қисқа туташувдан ҳимоя қилиш учун автоматлар. Сони ва номиналини электрик тасдиқлайди.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>RG-6
+          <t>1P C16/C10; 9 шт. предварительно, полюсность линий кондиционеров уточнить
 Общее</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I67" s="5" t="n"/>
       <c r="J67" s="5" t="n"/>
     </row>
-    <row r="68" ht="72" customHeight="1">
+    <row r="68" ht="136" customHeight="1">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Гофра Ø16 мм</t>
+          <t>DIN-рейка, гребёнка и маркировка</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Гофра для защиты проводки в ремонтируемых комнатах.
-Таъмирланадиган хоналарда симларни ҳимоя қилиш учун гофра.</t>
+          <t>Крепление и соединение аппаратов щита, подписи линий. Рейки обычно входят в корпус; отдельно проверить комплектацию.
+Щит аппаратларини маҳкамлаш ва улаш, линияларга ёзув. Рейкалар одатда корпусга киради; комплектни текшириш.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Ø16 мм
+          <t>DIN-рейки, однофазная гребёнка, маркировка; комплектацию уточнить
 Общее</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="I68" s="5" t="n"/>
       <c r="J68" s="5" t="n"/>
     </row>
-    <row r="69" ht="72" customHeight="1">
+    <row r="69" ht="104" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Гофра Ø20 мм</t>
+          <t>Вводной автомат 2P 40A C</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Гофра для защиты проводки в ремонтируемых комнатах.
-Таъмирланадиган хоналарда симларни ҳимоя қилиш учун гофра.</t>
+          <t>Вводной автомат для отключения питания квартиры; номинал согласовать с электриком.
+Квартира токини ўчириш учун кириш автомати; номиналини электрик билан келишиш.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Ø20 мм
+          <t>2P 40A, характеристика C; проектный ориентир
 Общее</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I69" s="5" t="n"/>
       <c r="J69" s="5" t="n"/>
     </row>
-    <row r="70" ht="72" customHeight="1">
+    <row r="70" ht="104" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Щит накладной IP41, 2×12 модулей</t>
+          <t>Шина N на DIN-изоляторе</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Щит для защитных аппаратов внутри прихожей.
-Даҳлиз ичида ҳимоя аппаратлари учун щит.</t>
+          <t>Отдельная шина для нейтральных проводников в щите; разделение после УЗО подтвердит электрик.
+Щитда нейтрал симлар учун алоҳида шина; УЗОдан кейин ажратишни электрик тасдиқлайди.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>IP41, 2×12 модулей
+          <t>N на DIN-изоляторе; количество групп уточнить
 Общее</t>
         </is>
       </c>
@@ -12083,29 +12083,29 @@
       <c r="I70" s="5" t="n"/>
       <c r="J70" s="5" t="n"/>
     </row>
-    <row r="71" ht="88" customHeight="1">
+    <row r="71" ht="104" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Распаячные коробки</t>
+          <t>Шина PE на DIN-изоляторе</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Коробки для доступных соединений проводов над дверями комнат.
-Хоналар эшиклари устида сим уланишларига кириш учун коробкалар.</t>
+          <t>Отдельная шина для защитного заземления, не соединять с N после УЗО.
+Ҳимоя ерлаш симлари учун алоҳида шина, УЗОдан кейин N билан уламаслик.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Размер и защиту согласовать с электриком
+          <t>PE на DIN-изоляторе; наличие PE проверить
 Общее</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -12123,64 +12123,64 @@
       <c r="I71" s="5" t="n"/>
       <c r="J71" s="5" t="n"/>
     </row>
-    <row r="72" ht="136" customHeight="1">
+    <row r="72" ht="72" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Автомат 1P C16/C10</t>
+          <t>Провод ПВ-3 4 мм² PE</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Автоматы для защиты линий от перегрузки и короткого замыкания. Количество и номиналы подтвердит электрик.
-Линияларни ортиқча юк ва қисқа туташувдан ҳимоя қилиш учун автоматлар. Сони ва номиналини электрик тасдиқлайди.</t>
+          <t>Защитный провод для заземления электропроводки квартиры.
+Квартира электропроводкасини заземление қилиш учун ҳимоя сими.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>1P C16/C10; 9 шт. предварительно, полюсность линий кондиционеров уточнить
+          <t>ПВ-3 4 мм² PE
 Общее</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I72" s="5" t="n"/>
       <c r="J72" s="5" t="n"/>
     </row>
-    <row r="73" ht="136" customHeight="1">
+    <row r="73" ht="104" customHeight="1">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>DIN-рейка, гребёнка и маркировка</t>
+          <t>RJ45 и TV механизмы</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Крепление и соединение аппаратов щита, подписи линий. Рейки обычно входят в корпус; отдельно проверить комплектацию.
-Щит аппаратларини маҳкамлаш ва улаш, линияларга ёзув. Рейкалар одатда корпусга киради; комплектни текшириш.</t>
+          <t>RJ45 для роутера на балконе и антенный разъём для телевизора в зале.
+Балкондаги роутер учун RJ45 ва Залдаги телевизор учун антенна улагичи.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>DIN-рейки, однофазная гребёнка, маркировка; комплектацию уточнить
+          <t>1 RJ45 + 1 TV; рамки и совместимость серии уточнить
 Общее</t>
         </is>
       </c>
@@ -12209,23 +12209,23 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Вводной автомат 2P 40A C</t>
+          <t>Подрозетники 60 мм</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Вводной автомат для отключения питания квартиры; номинал согласовать с электриком.
-Квартира токини ўчириш учун кириш автомати; номиналини электрик билан келишиш.</t>
+          <t>Установочные коробки розеток и выключателей на стенах без гипсокартона.
+Гипсокартонсиз деворларда розетка ва выключатель ўрнатиш учун коробкалар.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>2P 40A, характеристика C; проектный ориентир
+          <t>Кирпич/бетон, 68×45 мм; 29 отверстий + 10% = 32 шт.
 Общее</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="G74" s="4" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
@@ -12249,23 +12249,23 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Шина N на DIN-изоляторе</t>
+          <t>Подрозетники для гипсокартона</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Отдельная шина для нейтральных проводников в щите; разделение после УЗО подтвердит электрик.
-Щитда нейтрал симлар учун алоҳида шина; УЗОдан кейин ажратишни электрик тасдиқлайди.</t>
+          <t>Установочные коробки розеток и выключателей на стенах с гипсокартоном по плану.
+Режа бўйича гипсокартонли деворларда розетка ва выключатель ўрнатиш учун коробкалар.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>N на DIN-изоляторе; количество групп уточнить
+          <t>Для гипсокартона; 33 отверстия + 10% = 37 шт.
 Общее</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         </is>
       </c>
       <c r="G75" s="4" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
@@ -12283,29 +12283,29 @@
       <c r="I75" s="5" t="n"/>
       <c r="J75" s="5" t="n"/>
     </row>
-    <row r="76" ht="104" customHeight="1">
+    <row r="76" ht="88" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Шина PE на DIN-изоляторе</t>
+          <t>Клеммы WAGO 221-413</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Отдельная шина для защитного заземления, не соединять с N после УЗО.
-Ҳимоя ерлаш симлари учун алоҳида шина, УЗОдан кейин N билан уламаслик.</t>
+          <t>Клеммы для соединений в щите и коробках прихожей.
+Даҳлиз щити ва коробкаларидаги уланишлар учун клеммалар.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>PE на DIN-изоляторе; наличие PE проверить
+          <t>Клеммы WAGO 221-413; оригинал по выбору владельца, серию и подлинность проверить
 Общее</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -12323,233 +12323,231 @@
       <c r="I76" s="5" t="n"/>
       <c r="J76" s="5" t="n"/>
     </row>
-    <row r="77" ht="72" customHeight="1">
+    <row r="77" ht="88" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Провод ПВ-3 4 мм² PE</t>
+          <t>УЗО 30 мА, черновик до решения электрика</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Защитный провод для заземления электропроводки квартиры.
-Квартира электропроводкасини заземление қилиш учун ҳимоя сими.</t>
+          <t>УЗО для защиты от утечки тока, состав щита решает электрик.
+Ток сизишидан ҳимоя учун УЗО, щит таркибини электрик ҳал қилади.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>ПВ-3 4 мм² PE
+          <t>30 мА; состав щита согласовать
 Общее</t>
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I77" s="5" t="n"/>
       <c r="J77" s="5" t="n"/>
     </row>
-    <row r="78" ht="104" customHeight="1">
+    <row r="78" ht="88" customHeight="1">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>RJ45 и TV механизмы</t>
+          <t>Клеммы WAGO 221-415</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>RJ45 для роутера на балконе и антенный разъём для телевизора в зале.
-Балкондаги роутер учун RJ45 ва Залдаги телевизор учун антенна улагичи.</t>
+          <t>Клеммы для соединений в щите и коробках прихожей.
+Даҳлиз щити ва коробкаларидаги уланишлар учун клеммалар.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1 RJ45 + 1 TV; рамки и совместимость серии уточнить
+          <t>Клеммы WAGO 221-415; оригинал по выбору владельца, серию и подлинность проверить
 Общее</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I78" s="5" t="n"/>
       <c r="J78" s="5" t="n"/>
     </row>
-    <row r="79" ht="104" customHeight="1">
+    <row r="79" ht="72" customHeight="1">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Подрозетники 60 мм</t>
+          <t>Временное питание и свет бригады</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Установочные коробки розеток и выключателей на стенах без гипсокартона.
-Гипсокартонсиз деворларда розетка ва выключатель ўрнатиш учун коробкалар.</t>
+          <t>Временное питание и освещение для безопасной работы бригады.
+Бригаданинг хавфсиз ишлаши учун вақтинча ток ва ёритиш.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Кирпич/бетон, 68×45 мм; 29 отверстий + 10% = 32 шт.
+          <t>DB; безопасную схему решает электрик
 Общее</t>
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="G79" s="4" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="I79" s="5" t="n"/>
       <c r="J79" s="5" t="n"/>
     </row>
-    <row r="80" ht="104" customHeight="1">
+    <row r="80" ht="88" customHeight="1">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Подрозетники для гипсокартона</t>
+          <t>UTP cat.5e</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Установочные коробки розеток и выключателей на стенах с гипсокартоном по плану.
-Режа бўйича гипсокартонли деворларда розетка ва выключатель ўрнатиш учун коробкалар.</t>
+          <t>Сетевой кабель от ввода до роутера на балконе; ТВ по Wi-Fi.
+Киришдан Балкондаги роутергача тармоқ кабели; телевизор Wi-Fi орқали.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Для гипсокартона; 33 отверстия + 10% = 37 шт.
+          <t>UTP cat.5e
 Общее</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G80" s="4" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I80" s="5" t="n"/>
       <c r="J80" s="5" t="n"/>
     </row>
-    <row r="81" ht="88" customHeight="1">
+    <row r="81" ht="104" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Клеммы WAGO 221-413</t>
+          <t>Дюбель-гвоздь 6×60</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Клеммы для соединений в щите и коробках прихожей.
-Даҳлиз щити ва коробкаларидаги уланишлар учун клеммалар.</t>
+          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркасини маҳкамлаш учун дюбель-гвоздлар.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Клеммы WAGO 221-413; оригинал по выбору владельца, серию и подлинность проверить
-Общее</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="n">
-        <v>30</v>
+          <t>Запас и округление</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>1.22</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G81" s="4" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="I81" s="5" t="n"/>
       <c r="J81" s="5" t="n"/>
     </row>
-    <row r="82" ht="88" customHeight="1">
+    <row r="82" ht="104" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>УЗО 30 мА, черновик до решения электрика</t>
+          <t>Саморезы-семечки</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>УЗО для защиты от утечки тока, состав щита решает электрик.
-Ток сизишидан ҳимоя учун УЗО, щит таркибини электрик ҳал қилади.</t>
+          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХни каркасга маҳкамлаш учун саморезлар.</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>30 мА; состав щита согласовать
-Общее</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="n">
-        <v>2</v>
+          <t>Запас и округление</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>1.22</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G82" s="4" t="n">
@@ -12557,127 +12555,126 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="I82" s="5" t="n"/>
       <c r="J82" s="5" t="n"/>
     </row>
-    <row r="83" ht="88" customHeight="1">
+    <row r="83" ht="104" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Клеммы WAGO 221-415</t>
+          <t>ПВХ панели потолочные и балкон</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Клеммы для соединений в щите и коробках прихожей.
-Даҳлиз щити ва коробкаларидаги уланишлар учун клеммалар.</t>
+          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.
+Ваннахона, Ошхона, Даҳлиз потолоклари ҳамда Балкон деворлари ва потолоки учун панеллар.</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Клеммы WAGO 221-415; оригинал по выбору владельца, серию и подлинность проверить
-Общее</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="n">
-        <v>10</v>
+          <t>Запас и округление</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>6.05</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>шт. по 1 м²</t>
         </is>
       </c>
       <c r="G83" s="4" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>шт. по 1 м²</t>
         </is>
       </c>
       <c r="I83" s="5" t="n"/>
       <c r="J83" s="5" t="n"/>
     </row>
-    <row r="84" ht="72" customHeight="1">
+    <row r="84" ht="104" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Временное питание и свет бригады</t>
+          <t>Направляющие для ПВХ</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Временное питание и освещение для безопасной работы бригады.
-Бригаданинг хавфсиз ишлаши учун вақтинча ток ва ёритиш.</t>
+          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси направляющийлари.</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>DB; безопасную схему решает электрик
-Общее</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="n">
-        <v>1</v>
+          <t>UD 3 м; совместимость подтвердить
+Запас и округление</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0.89</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="G84" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="I84" s="5" t="n"/>
       <c r="J84" s="5" t="n"/>
     </row>
-    <row r="85" ht="88" customHeight="1">
+    <row r="85" ht="72" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>UTP cat.5e</t>
+          <t>Профиль для ПВХ</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Сетевой кабель от ввода до роутера на балконе; ТВ по Wi-Fi.
-Киришдан Балкондаги роутергача тармоқ кабели; телевизор Wi-Fi орқали.</t>
+          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси профили.</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>UTP cat.5e
-Общее</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="n">
-        <v>11</v>
+          <t>CD 3 м; совместимость подтвердить
+Запас и округление</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0.89</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="G85" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="I85" s="5" t="n"/>
@@ -12689,73 +12686,79 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Дюбель-гвоздь 6×60</t>
+          <t>Пластиковые уголки</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.
-Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркасини маҳкамлаш учун дюбель-гвоздлар.</t>
+          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ туташган жойларини ёпиш учун уголоклар.</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Запас и округление</t>
+          <t>Длина 3 м
+Запас и округление</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G86" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I86" s="5" t="n"/>
       <c r="J86" s="5" t="n"/>
     </row>
-    <row r="87" ht="104" customHeight="1">
+    <row r="87" ht="72" customHeight="1">
       <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Саморезы-семечки</t>
+          <t>Плиссе</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.
-Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХни каркасга маҳкамлаш учун саморезлар.</t>
+          <t>Плиссе на окна кухни, зала и наружное остекление балкона.
+Ошхона, Зал деразалари ва Балконнинг ташқи ойналарига плиссе.</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Запас и округление</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>1.22</v>
+          <t>Замерить каждую секцию окна
+Без распределения</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="G87" s="4" t="n">
-        <v>2</v>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I87" s="5" t="n"/>
@@ -12767,177 +12770,183 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>ПВХ панели потолочные и балкон</t>
+          <t>Защитная клетка для наружного блока</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.
-Ваннахона, Ошхона, Даҳлиз потолоклари ҳамда Балкон деворлари ва потолоки учун панеллар.</t>
+          <t>Клетка для защиты наружного блока кондиционера под решёткой окна спальни.
+Ётоқхона деразаси решёткаси остидаги ташқи кондиционер блокини ҳимоя қилиш учун клетка.</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Запас и округление</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>6.05</v>
+          <t>Наружный блок под решёткой окна спальни; отдельный подрядчик
+Без распределения</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>шт. по 1 м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G88" s="4" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>шт. по 1 м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I88" s="5" t="n"/>
       <c r="J88" s="5" t="n"/>
     </row>
-    <row r="89" ht="104" customHeight="1">
+    <row r="89" ht="88" customHeight="1">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Направляющие для ПВХ</t>
+          <t>Краска стен</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.
-Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси направляющийлари.</t>
+          <t>Краска для стен зала, прихожей и окрашиваемых участков кухни.
+Зал, Даҳлиз деворлари ва Ошхонанинг бўяладиган қисмлари учун краска.</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>UD 3 м; совместимость подтвердить
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>0.89</v>
+          <t>Без распределения</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
-        </is>
-      </c>
-      <c r="G89" s="4" t="n">
-        <v>13</v>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="I89" s="5" t="n"/>
       <c r="J89" s="5" t="n"/>
     </row>
-    <row r="90" ht="72" customHeight="1">
+    <row r="90" ht="104" customHeight="1">
       <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Профиль для ПВХ</t>
+          <t>Краска POLARD UNIVERSAL 10 кг</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.
-Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси профили.</t>
+          <t>Кандидат краски для стен, пригодность и моющуюся стойкость ещё нужно проверить.
+Деворлар учун краска варианти, яроқлилиги ва ювилишга чидамлилигини текшириш керак.</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>CD 3 м; совместимость подтвердить
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>0.89</v>
+          <t>Без распределения</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
-        </is>
-      </c>
-      <c r="G90" s="4" t="n">
-        <v>13</v>
+          <t>ведро 10 кг</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
+          <t>ведро 10 кг</t>
         </is>
       </c>
       <c r="I90" s="5" t="n"/>
       <c r="J90" s="5" t="n"/>
     </row>
-    <row r="91" ht="104" customHeight="1">
+    <row r="91" ht="88" customHeight="1">
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Пластиковые уголки</t>
+          <t>Стяжка старая: мешки/вывоз</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.
-Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ туташган жойларини ёпиш учун уголоклар.</t>
+          <t>Мешки и вывоз мусора после демонтажа старой стяжки.
+Эски стяжкани бузгандан кейин чиқинди учун қоплар ва олиб чиқиш.</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Длина 3 м
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>0.89</v>
+          <t>Общее</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>67</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>мешок 50 кг эквивалент</t>
         </is>
       </c>
       <c r="G91" s="4" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>мешок 50 кг эквивалент</t>
         </is>
       </c>
       <c r="I91" s="5" t="n"/>
       <c r="J91" s="5" t="n"/>
     </row>
-    <row r="92" ht="72" customHeight="1">
+    <row r="92" ht="104" customHeight="1">
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Плиссе</t>
+          <t>Газовая плита напольная 50–60 см</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Плиссе на окна кухни, зала и наружное остекление балкона.
-Ошхона, Зал деразалари ва Балконнинг ташқи ойналарига плиссе.</t>
+          <t>Устаревшая позиция: напольную газовую плиту не заказывать, выбрана панель.
+Эски позиция: полга қўйиладиган газ плитасини буюртма қилманг, панель танланган.</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Замерить каждую секцию окна
+          <t>Не заказывать
 Без распределения</t>
         </is>
       </c>
@@ -12948,7 +12957,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -12958,223 +12967,14 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="I92" s="5" t="n"/>
       <c r="J92" s="5" t="n"/>
     </row>
-    <row r="93" ht="104" customHeight="1">
-      <c r="A93" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Защитная клетка для наружного блока</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Клетка для защиты наружного блока кондиционера под решёткой окна спальни.
-Ётоқхона деразаси решёткаси остидаги ташқи кондиционер блокини ҳимоя қилиш учун клетка.</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Наружный блок под решёткой окна спальни; отдельный подрядчик
-Без распределения</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G93" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="n"/>
-      <c r="J93" s="5" t="n"/>
-    </row>
-    <row r="94" ht="88" customHeight="1">
-      <c r="A94" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Краска стен</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Краска для стен зала, прихожей и окрашиваемых участков кухни.
-Зал, Даҳлиз деворлари ва Ошхонанинг бўяладиган қисмлари учун краска.</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Без распределения</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>комплект</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>комплект</t>
-        </is>
-      </c>
-      <c r="I94" s="5" t="n"/>
-      <c r="J94" s="5" t="n"/>
-    </row>
-    <row r="95" ht="104" customHeight="1">
-      <c r="A95" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Краска POLARD UNIVERSAL 10 кг</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Кандидат краски для стен, пригодность и моющуюся стойкость ещё нужно проверить.
-Деворлар учун краска варианти, яроқлилиги ва ювилишга чидамлилигини текшириш керак.</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Без распределения</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>ведро 10 кг</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>ведро 10 кг</t>
-        </is>
-      </c>
-      <c r="I95" s="5" t="n"/>
-      <c r="J95" s="5" t="n"/>
-    </row>
-    <row r="96" ht="88" customHeight="1">
-      <c r="A96" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Стяжка старая: мешки/вывоз</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Мешки и вывоз мусора после демонтажа старой стяжки.
-Эски стяжкани бузгандан кейин чиқинди учун қоплар ва олиб чиқиш.</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Общее</t>
-        </is>
-      </c>
-      <c r="E96" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>мешок 50 кг эквивалент</t>
-        </is>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>мешок 50 кг эквивалент</t>
-        </is>
-      </c>
-      <c r="I96" s="5" t="n"/>
-      <c r="J96" s="5" t="n"/>
-    </row>
-    <row r="97" ht="104" customHeight="1">
-      <c r="A97" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Газовая плита напольная 50–60 см</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Устаревшая позиция: напольную газовую плиту не заказывать, выбрана панель.
-Эски позиция: полга қўйиладиган газ плитасини буюртма қилманг, панель танланган.</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Не заказывать
-Без распределения</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>комплект</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>комплект</t>
-        </is>
-      </c>
-      <c r="I97" s="5" t="n"/>
-      <c r="J97" s="5" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J97"/>
+  <autoFilter ref="A1:J92"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/materialy/материалы-по-комнатам.xlsx
+++ b/materialy/материалы-по-комнатам.xlsx
@@ -41,9 +41,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Спальня'!$A$1:$J$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Спальня'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Спальня'!$A$1:$J$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'На всю квартиру'!$A$1:$J$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'На всю квартиру'!$A$1:$J$85</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'На всю квартиру'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'На всю квартиру'!$A$1:$J$92</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'На всю квартиру'!$A$1:$J$85</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="0"/>
 </workbook>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C9" s="2" t="inlineStr"/>
     </row>
@@ -1140,7 +1140,7 @@
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
     </row>
-    <row r="12" ht="72" customHeight="1">
+    <row r="12" ht="136" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
@@ -1151,8 +1151,8 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона прихожей.
-Даҳлиз гипсокартони чокларини ёпиш учун шпаклёвка.</t>
+          <t>Шпаклёвка для заделки швов гипсокартона ванной, кухни, прихожей и зала; общая закупка на квартиру.
+Ваннахона, Ошхона, Даҳлиз ва Зал гипсокартони чокларини тўлдириш учун шпаклёвка; квартира учун умумий харид.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
     </row>
-    <row r="14" ht="72" customHeight="1">
+    <row r="14" ht="136" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -1229,8 +1229,8 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона прихожей.
-Даҳлиз гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
+          <t>Серпянка для укрепления швов гипсокартона ванной, кухни, прихожей и зала; общая закупка на квартиру.
+Ваннахона, Ошхона, Даҳлиз ва Зал гипсокартони чокларини мустаҳкамлаш учун серпянка; квартира учун умумий харид.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
     </row>
-    <row r="13" ht="72" customHeight="1">
+    <row r="13" ht="136" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -2338,8 +2338,8 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона ванной.
-Ваннахона гипсокартони чокларини ёпиш учун шпаклёвка.</t>
+          <t>Шпаклёвка для заделки швов гипсокартона ванной, кухни, прихожей и зала; общая закупка на квартиру.
+Ваннахона, Ошхона, Даҳлиз ва Зал гипсокартони чокларини тўлдириш учун шпаклёвка; квартира учун умумий харид.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
     </row>
-    <row r="15" ht="120" customHeight="1">
+    <row r="15" ht="168" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -2416,8 +2416,8 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для второго слоя гипсокартона ванной; крепление согласовать с изготовителем системы.
-Ваннахона гипсокартонининг иккинчи қатлами учун саморезлар; маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
+          <t>Саморезы для второго слоя гипсокартона ванной и кухни; общая закупка на квартиру. Крепление согласовать с изготовителем системы.
+Ваннахона ва Ошхона гипсокартонининг иккинчи қатлами учун саморезлар; квартира учун умумий харид. Маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
     </row>
-    <row r="16" ht="72" customHeight="1">
+    <row r="16" ht="136" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -2455,8 +2455,8 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона ванной.
-Ваннахона гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
+          <t>Серпянка для укрепления швов гипсокартона ванной, кухни, прихожей и зала; общая закупка на квартиру.
+Ваннахона, Ошхона, Даҳлиз ва Зал гипсокартони чокларини мустаҳкамлаш учун серпянка; квартира учун умумий харид.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
     </row>
-    <row r="13" ht="72" customHeight="1">
+    <row r="13" ht="136" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -4653,8 +4653,8 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона кухни.
-Ошхона гипсокартони чокларини ёпиш учун шпаклёвка.</t>
+          <t>Шпаклёвка для заделки швов гипсокартона ванной, кухни, прихожей и зала; общая закупка на квартиру.
+Ваннахона, Ошхона, Даҳлиз ва Зал гипсокартони чокларини тўлдириш учун шпаклёвка; квартира учун умумий харид.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -4720,7 +4720,7 @@
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
     </row>
-    <row r="15" ht="120" customHeight="1">
+    <row r="15" ht="168" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -4731,8 +4731,8 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для второго слоя гипсокартона кухни; крепление согласовать с изготовителем системы.
-Ошхона гипсокартонининг иккинчи қатлами учун саморезлар; маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
+          <t>Саморезы для второго слоя гипсокартона ванной и кухни; общая закупка на квартиру. Крепление согласовать с изготовителем системы.
+Ваннахона ва Ошхона гипсокартонининг иккинчи қатлами учун саморезлар; квартира учун умумий харид. Маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       <c r="I15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
     </row>
-    <row r="16" ht="72" customHeight="1">
+    <row r="16" ht="136" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -4770,8 +4770,8 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона кухни.
-Ошхона гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
+          <t>Серпянка для укрепления швов гипсокартона ванной, кухни, прихожей и зала; общая закупка на квартиру.
+Ваннахона, Ошхона, Даҳлиз ва Зал гипсокартони чокларини мустаҳкамлаш учун серпянка; квартира учун умумий харид.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -6382,7 +6382,7 @@
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
     </row>
-    <row r="13" ht="104" customHeight="1">
+    <row r="13" ht="136" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -6393,8 +6393,8 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона на стене под ТВ в зале.
-Залда ТВ ортидаги девор гипсокартони чокларини ёпиш учун шпаклёвка.</t>
+          <t>Шпаклёвка для заделки швов гипсокартона ванной, кухни, прихожей и зала; общая закупка на квартиру.
+Ваннахона, Ошхона, Даҳлиз ва Зал гипсокартони чокларини тўлдириш учун шпаклёвка; квартира учун умумий харид.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -6460,7 +6460,7 @@
       <c r="I14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
     </row>
-    <row r="15" ht="104" customHeight="1">
+    <row r="15" ht="136" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -6471,8 +6471,8 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона на стене под ТВ в зале.
-Залда ТВ ортидаги девор гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
+          <t>Серпянка для укрепления швов гипсокартона ванной, кухни, прихожей и зала; общая закупка на квартиру.
+Ваннахона, Ошхона, Даҳлиз ва Зал гипсокартони чокларини мустаҳкамлаш учун серпянка; квартира учун умумий харид.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -9258,7 +9258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10653,7 +10653,7 @@
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
     </row>
-    <row r="35" ht="72" customHeight="1">
+    <row r="35" ht="136" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
@@ -10664,8 +10664,8 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона ванной.
-Ваннахона гипсокартони чокларини ёпиш учун шпаклёвка.</t>
+          <t>Шпаклёвка для заделки швов гипсокартона ванной, кухни, прихожей и зала; общая закупка на квартиру.
+Ваннахона, Ошхона, Даҳлиз ва Зал гипсокартони чокларини тўлдириш учун шпаклёвка; квартира учун умумий харид.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>0.79</v>
+        <v>0.2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -10693,73 +10693,73 @@
       <c r="I35" s="5" t="n"/>
       <c r="J35" s="5" t="n"/>
     </row>
-    <row r="36" ht="72" customHeight="1">
+    <row r="36" ht="104" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка швов Knauf Fugen 25 кг</t>
+          <t>Клей монтажный Knauf Perlfix 30 кг</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона прихожей.
-Даҳлиз гипсокартони чокларини ёпиш учун шпаклёвка.</t>
+          <t>Клей для облицовки стен ванной, кухни, прихожей и зала гипсокартоном.
+Ваннахона, Ошхона, Даҳлиз ва Зал деворларини гипсокартон билан қоплаш учун клей.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Knauf Fugen, 25 кг
+          <t>Knauf Perlfix, 30 кг; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса
 Запас и округление</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.83</v>
+        <v>2.01</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
+          <t>мешок 30 кг</t>
         </is>
       </c>
       <c r="G36" s="4" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
+          <t>мешок 30 кг</t>
         </is>
       </c>
       <c r="I36" s="5" t="n"/>
       <c r="J36" s="5" t="n"/>
     </row>
-    <row r="37" ht="72" customHeight="1">
+    <row r="37" ht="168" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка швов Knauf Fugen 25 кг</t>
+          <t>Саморезы ГКЛ 3,5×35</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона кухни.
-Ошхона гипсокартони чокларини ёпиш учун шпаклёвка.</t>
+          <t>Саморезы для второго слоя гипсокартона ванной и кухни; общая закупка на квартиру. Крепление согласовать с изготовителем системы.
+Ваннахона ва Ошхона гипсокартонининг иккинчи қатлами учун саморезлар; квартира учун умумий харид. Маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Knauf Fugen, 25 кг
+          <t>3,5×35; крепление второго слоя согласовать
 Запас и округление</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.75</v>
+        <v>0.12</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G37" s="4" t="n">
@@ -10767,39 +10767,39 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="I37" s="5" t="n"/>
       <c r="J37" s="5" t="n"/>
     </row>
-    <row r="38" ht="104" customHeight="1">
+    <row r="38" ht="136" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка швов Knauf Fugen 25 кг</t>
+          <t>Серпянка 90 м</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Шпаклёвка для заделки швов гипсокартона на стене под ТВ в зале.
-Залда ТВ ортидаги девор гипсокартони чокларини ёпиш учун шпаклёвка.</t>
+          <t>Серпянка для укрепления швов гипсокартона ванной, кухни, прихожей и зала; общая закупка на квартиру.
+Ваннахона, Ошхона, Даҳлиз ва Зал гипсокартони чокларини мустаҳкамлаш учун серпянка; квартира учун умумий харид.</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Knauf Fugen, 25 кг
+          <t>Серпянка, рулон 90 м
 Запас и округление</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.83</v>
+        <v>0.11</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
+          <t>рулон 90 м</t>
         </is>
       </c>
       <c r="G38" s="4" t="n">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
+          <t>рулон 90 м</t>
         </is>
       </c>
       <c r="I38" s="5" t="n"/>
@@ -10819,115 +10819,114 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Клей монтажный Knauf Perlfix 30 кг</t>
+          <t>ГКЛ 12,5 мм 1200×2500</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Клей для облицовки стен ванной, кухни, прихожей и зала гипсокартоном.
-Ваннахона, Ошхона, Даҳлиз ва Зал деворларини гипсокартон билан қоплаш учун клей.</t>
+          <t>Листы для выравнивания стен прихожей и зала перед отделкой.
+Отделкадан олдин Даҳлиз ва Зал деворларини текислаш учун листлар.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Knauf Perlfix, 30 кг; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса
+          <t>ГКЛ 12,5 мм, 1200×2500, один слой; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса
 Запас и округление</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2.01</v>
+        <v>1.56</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>мешок 30 кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G39" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>мешок 30 кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I39" s="5" t="n"/>
       <c r="J39" s="5" t="n"/>
     </row>
-    <row r="40" ht="120" customHeight="1">
+    <row r="40" ht="136" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Саморезы ГКЛ 3,5×35</t>
+          <t>ГКЛВ 12,5 мм 1200×2500</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для второго слоя гипсокартона ванной; крепление согласовать с изготовителем системы.
-Ваннахона гипсокартонининг иккинчи қатлами учун саморезлар; маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
+          <t>Влагостойкие листы для выравнивания стен ванной и кухни перед отделкой.
+Отделкадан олдин Ваннахона ва Ошхона деворларини текислаш учун намга чидамли листлар.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3,5×35; крепление второго слоя согласовать
+          <t>ГКЛВ 12,5 мм, 1200×2500, один или два слоя по стенам чертежа, со смещением швов; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса
 Запас и округление</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.49</v>
+        <v>2.45</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I40" s="5" t="n"/>
       <c r="J40" s="5" t="n"/>
     </row>
-    <row r="41" ht="120" customHeight="1">
+    <row r="41" ht="72" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Саморезы ГКЛ 3,5×35</t>
+          <t>Труба PP-R Ø20 PN20</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для второго слоя гипсокартона кухни; крепление согласовать с изготовителем системы.
-Ошхона гипсокартонининг иккинчи қатлами учун саморезлар; маҳкамлашни система ишлаб чиқарувчиси билан келишиш.</t>
+          <t>Трубы для подачи воды к сантехнике ванной и кухни.
+Ваннахона ва Ошхона сантехникасига сув келтириш учун трубалар.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>3,5×35; крепление второго слоя согласовать
-Запас и округление</t>
+          <t>Запас и округление</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.63</v>
+        <v>10.2</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I41" s="5" t="n"/>
@@ -10939,75 +10938,73 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Серпянка 90 м</t>
+          <t>Отвод канализационный Ø50</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона ванной.
-Ваннахона гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
+          <t>Отводы для поворотов канализации ванной и кухни.
+Ваннахона ва Ошхона канализациясини буриш учун отводлар.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Серпянка, рулон 90 м
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>0.77</v>
+          <t>Без распределения</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I42" s="5" t="n"/>
       <c r="J42" s="5" t="n"/>
     </row>
-    <row r="43" ht="72" customHeight="1">
+    <row r="43" ht="88" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Серпянка 90 м</t>
+          <t>Тройник PP-R Ø20</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона прихожей.
-Даҳлиз гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
+          <t>Тройники для ответвлений воды к сантехнике ванной и кухни.
+Ваннахона ва Ошхона сантехникасига сув тармоқлари учун тройниклар.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Серпянка, рулон 90 м
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>0.8100000000000001</v>
+          <t>Без распределения</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G43" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I43" s="5" t="n"/>
@@ -11019,143 +11016,139 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Серпянка 90 м</t>
+          <t>Тройник канализационный Ø50</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона кухни.
-Ошхона гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
+          <t>Тройники для объединения сливов ванной и кухни.
+Ваннахона ва Ошхона сливларини бирлаштириш учун тройниклар.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Серпянка, рулон 90 м
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>0.72</v>
+          <t>Без распределения</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G44" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I44" s="5" t="n"/>
       <c r="J44" s="5" t="n"/>
     </row>
-    <row r="45" ht="104" customHeight="1">
+    <row r="45" ht="72" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Серпянка 90 м</t>
+          <t>Угольник PP-R Ø20</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Серпянка для укрепления швов гипсокартона на стене под ТВ в зале.
-Залда ТВ ортидаги девор гипсокартони чокларини мустаҳкамлаш учун серпянка.</t>
+          <t>Угольники для поворотов водопроводных труб ванной и кухни.
+Ваннахона ва Ошхона сув трубаларини буриш учун угольниклар.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Серпянка, рулон 90 м
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>0.8100000000000001</v>
+          <t>Без распределения</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>рулон 90 м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I45" s="5" t="n"/>
       <c r="J45" s="5" t="n"/>
     </row>
-    <row r="46" ht="104" customHeight="1">
+    <row r="46" ht="88" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ГКЛ 12,5 мм 1200×2500</t>
+          <t>Труба канализационная ПВХ Ø50</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Листы для выравнивания стен прихожей и зала перед отделкой.
-Отделкадан олдин Даҳлиз ва Зал деворларини текислаш учун листлар.</t>
+          <t>Трубы для отвода стоков ванной и кухни к стояку.
+Ваннахона ва Ошхона оқова сувини стоякка олиб бориш учун трубалар.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>ГКЛ 12,5 мм, 1200×2500, один слой; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса
-Запас и округление</t>
+          <t>Запас и округление</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1.56</v>
+        <v>0.51</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G46" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I46" s="5" t="n"/>
       <c r="J46" s="5" t="n"/>
     </row>
-    <row r="47" ht="136" customHeight="1">
+    <row r="47" ht="72" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ГКЛВ 12,5 мм 1200×2500</t>
+          <t>Переход PP-R с резьбой 20×½″</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Влагостойкие листы для выравнивания стен ванной и кухни перед отделкой.
-Отделкадан олдин Ваннахона ва Ошхона деворларини текислаш учун намга чидамли листлар.</t>
+          <t>Переходы для соединения труб с резьбовой сантехникой.
+Трубаларни резьбали сантехникага улаш учун переходлар.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>ГКЛВ 12,5 мм, 1200×2500, один или два слоя по стенам чертежа, со смещением швов; одна закупка на всю квартиру, запас 10% один раз; в комнате указан расход без запаса
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>2.45</v>
+          <t>Без распределения</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>4</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -11163,7 +11156,7 @@
         </is>
       </c>
       <c r="G47" s="4" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -11179,13 +11172,13 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Труба PP-R Ø20 PN20</t>
+          <t>Труба PP-R Ø20 PN20 для гигиенического душа</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Трубы для подачи воды к сантехнике ванной и кухни.
-Ваннахона ва Ошхона сантехникасига сув келтириш учун трубалар.</t>
+          <t>Труба для подачи воды к гигиеническому душу туалета.
+Ҳожатхона гигиенический душига сув келтириш учун труба.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -11194,7 +11187,7 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>10.2</v>
+        <v>0.68</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -11202,7 +11195,7 @@
         </is>
       </c>
       <c r="G48" s="4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -11218,13 +11211,13 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Отвод канализационный Ø50</t>
+          <t>Муфта канализационная Ø50</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Отводы для поворотов канализации ванной и кухни.
-Ваннахона ва Ошхона канализациясини буриш учун отводлар.</t>
+          <t>Муфты для соединения участков канализации ванной и кухни.
+Ваннахона ва Ошхона канализация қисмларини улаш учун муфталар.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -11233,7 +11226,7 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -11241,7 +11234,7 @@
         </is>
       </c>
       <c r="G49" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -11251,19 +11244,19 @@
       <c r="I49" s="5" t="n"/>
       <c r="J49" s="5" t="n"/>
     </row>
-    <row r="50" ht="88" customHeight="1">
+    <row r="50" ht="72" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Тройник PP-R Ø20</t>
+          <t>Муфта PP-R Ø20</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Тройники для ответвлений воды к сантехнике ванной и кухни.
-Ваннахона ва Ошхона сантехникасига сув тармоқлари учун тройниклар.</t>
+          <t>Муфты для соединения водопроводных труб ванной и кухни.
+Ваннахона ва Ошхона сув трубаларини улаш учун муфталар.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -11272,7 +11265,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -11280,7 +11273,7 @@
         </is>
       </c>
       <c r="G50" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -11290,40 +11283,41 @@
       <c r="I50" s="5" t="n"/>
       <c r="J50" s="5" t="n"/>
     </row>
-    <row r="51" ht="72" customHeight="1">
+    <row r="51" ht="104" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Тройник канализационный Ø50</t>
+          <t>Кабель-канал 40×25 спальня AC</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Тройники для объединения сливов ванной и кухни.
-Ваннахона ва Ошхона сливларини бирлаштириш учун тройниклар.</t>
+          <t>Кабель-канал для отдельной линии кондиционера в готовой спальне.
+Тайёр Ётоқхонада кондиционернинг алоҳида линияси учун кабель-канал.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Без распределения</t>
+          <t>40×25; QF9, спальня
+Общее</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G51" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I51" s="5" t="n"/>
@@ -11335,61 +11329,63 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Угольник PP-R Ø20</t>
+          <t>ВВГнг(А)-LS 3×2,5</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Угольники для поворотов водопроводных труб ванной и кухни.
-Ваннахона ва Ошхона сув трубаларини буриш учун угольниклар.</t>
+          <t>Кабель розеточной линии QF3 для зала, прихожей и балкона.
+Зал, Даҳлиз ва Балкон розеткалари QF3 линияси учун кабель.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Без распределения</t>
+          <t>ВВГнг(А)-LS 3×2,5; QF3
+Общее</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G52" s="4" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I52" s="5" t="n"/>
       <c r="J52" s="5" t="n"/>
     </row>
-    <row r="53" ht="88" customHeight="1">
+    <row r="53" ht="72" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Труба канализационная ПВХ Ø50</t>
+          <t>ВВГнг(А)-LS 3×1,5</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Трубы для отвода стоков ванной и кухни к стояку.
-Ваннахона ва Ошхона оқова сувини стоякка олиб бориш учун трубалар.</t>
+          <t>Кабель для линий освещения ремонтируемых комнат.
+Таъмирланадиган хоналар чироқлари линиялари учун кабель.</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Запас и округление</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>0.51</v>
+          <t>ВВГнг(А)-LS 3×1,5; L1/L2
+Общее</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>103</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -11397,7 +11393,7 @@
         </is>
       </c>
       <c r="G53" s="4" t="n">
-        <v>4</v>
+        <v>103</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -11413,34 +11409,35 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Переход PP-R с резьбой 20×½″</t>
+          <t>ВВГнг(А)-LS 3×6, ввод от счётчика до щита</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Переходы для соединения труб с резьбовой сантехникой.
-Трубаларни резьбали сантехникага улаш учун переходлар.</t>
+          <t>Вводной кабель от счётчика на площадке к щиту в прихожей.
+Майдонча счётчигидан Даҳлиз щитига кириш кабели.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Без распределения</t>
+          <t>ВВГнг(А)-LS 3×6
+Общее</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G54" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I54" s="5" t="n"/>
@@ -11452,22 +11449,23 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Труба PP-R Ø20 PN20 для гигиенического душа</t>
+          <t>Коаксиал RG-6</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Труба для подачи воды к гигиеническому душу туалета.
-Ҳожатхона гигиенический душига сув келтириш учун труба.</t>
+          <t>Коаксиальный кабель для телевизионной точки в зале.
+Залдаги телевизион нуқта учун коаксиальный кабель.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Запас и округление</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>0.68</v>
+          <t>RG-6
+Общее</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -11475,7 +11473,7 @@
         </is>
       </c>
       <c r="G55" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -11491,34 +11489,35 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Муфта канализационная Ø50</t>
+          <t>Гофра Ø16 мм</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Муфты для соединения участков канализации ванной и кухни.
-Ваннахона ва Ошхона канализация қисмларини улаш учун муфталар.</t>
+          <t>Гофра для защиты проводки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда симларни ҳимоя қилиш учун гофра.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Без распределения</t>
+          <t>Ø16 мм
+Общее</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G56" s="4" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I56" s="5" t="n"/>
@@ -11530,314 +11529,315 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Муфта PP-R Ø20</t>
+          <t>Гофра Ø20 мм</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Муфты для соединения водопроводных труб ванной и кухни.
-Ваннахона ва Ошхона сув трубаларини улаш учун муфталар.</t>
+          <t>Гофра для защиты проводки в ремонтируемых комнатах.
+Таъмирланадиган хоналарда симларни ҳимоя қилиш учун гофра.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Без распределения</t>
+          <t>Ø20 мм
+Общее</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G57" s="4" t="n">
-        <v>2</v>
+        <v>147</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I57" s="5" t="n"/>
       <c r="J57" s="5" t="n"/>
     </row>
-    <row r="58" ht="104" customHeight="1">
+    <row r="58" ht="72" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Кабель-канал 40×25 спальня AC</t>
+          <t>Щит накладной IP41, 2×12 модулей</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Кабель-канал для отдельной линии кондиционера в готовой спальне.
-Тайёр Ётоқхонада кондиционернинг алоҳида линияси учун кабель-канал.</t>
+          <t>Щит для защитных аппаратов внутри прихожей.
+Даҳлиз ичида ҳимоя аппаратлари учун щит.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>40×25; QF9, спальня
+          <t>IP41, 2×12 модулей
 Общее</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G58" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I58" s="5" t="n"/>
       <c r="J58" s="5" t="n"/>
     </row>
-    <row r="59" ht="72" customHeight="1">
+    <row r="59" ht="88" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-LS 3×2,5</t>
+          <t>Распаячные коробки</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Кабель розеточной линии QF3 для зала, прихожей и балкона.
-Зал, Даҳлиз ва Балкон розеткалари QF3 линияси учун кабель.</t>
+          <t>Коробки для доступных соединений проводов над дверями комнат.
+Хоналар эшиклари устида сим уланишларига кириш учун коробкалар.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-LS 3×2,5; QF3
+          <t>Размер и защиту согласовать с электриком
 Общее</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G59" s="4" t="n">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I59" s="5" t="n"/>
       <c r="J59" s="5" t="n"/>
     </row>
-    <row r="60" ht="72" customHeight="1">
+    <row r="60" ht="136" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-LS 3×1,5</t>
+          <t>Автомат 1P C16/C10</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Кабель для линий освещения ремонтируемых комнат.
-Таъмирланадиган хоналар чироқлари линиялари учун кабель.</t>
+          <t>Автоматы для защиты линий от перегрузки и короткого замыкания. Количество и номиналы подтвердит электрик.
+Линияларни ортиқча юк ва қисқа туташувдан ҳимоя қилиш учун автоматлар. Сони ва номиналини электрик тасдиқлайди.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-LS 3×1,5; L1/L2
+          <t>1P C16/C10; 9 шт. предварительно, полюсность линий кондиционеров уточнить
 Общее</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G60" s="4" t="n">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I60" s="5" t="n"/>
       <c r="J60" s="5" t="n"/>
     </row>
-    <row r="61" ht="72" customHeight="1">
+    <row r="61" ht="136" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-LS 3×6, ввод от счётчика до щита</t>
+          <t>DIN-рейка, гребёнка и маркировка</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Вводной кабель от счётчика на площадке к щиту в прихожей.
-Майдонча счётчигидан Даҳлиз щитига кириш кабели.</t>
+          <t>Крепление и соединение аппаратов щита, подписи линий. Рейки обычно входят в корпус; отдельно проверить комплектацию.
+Щит аппаратларини маҳкамлаш ва улаш, линияларга ёзув. Рейкалар одатда корпусга киради; комплектни текшириш.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>ВВГнг(А)-LS 3×6
+          <t>DIN-рейки, однофазная гребёнка, маркировка; комплектацию уточнить
 Общее</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="G61" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="I61" s="5" t="n"/>
       <c r="J61" s="5" t="n"/>
     </row>
-    <row r="62" ht="72" customHeight="1">
+    <row r="62" ht="104" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Коаксиал RG-6</t>
+          <t>Вводной автомат 2P 40A C</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Коаксиальный кабель для телевизионной точки в зале.
-Залдаги телевизион нуқта учун коаксиальный кабель.</t>
+          <t>Вводной автомат для отключения питания квартиры; номинал согласовать с электриком.
+Квартира токини ўчириш учун кириш автомати; номиналини электрик билан келишиш.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>RG-6
+          <t>2P 40A, характеристика C; проектный ориентир
 Общее</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G62" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I62" s="5" t="n"/>
       <c r="J62" s="5" t="n"/>
     </row>
-    <row r="63" ht="72" customHeight="1">
+    <row r="63" ht="104" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Гофра Ø16 мм</t>
+          <t>Шина N на DIN-изоляторе</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Гофра для защиты проводки в ремонтируемых комнатах.
-Таъмирланадиган хоналарда симларни ҳимоя қилиш учун гофра.</t>
+          <t>Отдельная шина для нейтральных проводников в щите; разделение после УЗО подтвердит электрик.
+Щитда нейтрал симлар учун алоҳида шина; УЗОдан кейин ажратишни электрик тасдиқлайди.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Ø16 мм
+          <t>N на DIN-изоляторе; количество групп уточнить
 Общее</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G63" s="4" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I63" s="5" t="n"/>
       <c r="J63" s="5" t="n"/>
     </row>
-    <row r="64" ht="72" customHeight="1">
+    <row r="64" ht="104" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Гофра Ø20 мм</t>
+          <t>Шина PE на DIN-изоляторе</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Гофра для защиты проводки в ремонтируемых комнатах.
-Таъмирланадиган хоналарда симларни ҳимоя қилиш учун гофра.</t>
+          <t>Отдельная шина для защитного заземления, не соединять с N после УЗО.
+Ҳимоя ерлаш симлари учун алоҳида шина, УЗОдан кейин N билан уламаслик.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Ø20 мм
+          <t>PE на DIN-изоляторе; наличие PE проверить
 Общее</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G64" s="4" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I64" s="5" t="n"/>
@@ -11849,103 +11849,103 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Щит накладной IP41, 2×12 модулей</t>
+          <t>Провод ПВ-3 4 мм² PE</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Щит для защитных аппаратов внутри прихожей.
-Даҳлиз ичида ҳимоя аппаратлари учун щит.</t>
+          <t>Защитный провод для заземления электропроводки квартиры.
+Квартира электропроводкасини заземление қилиш учун ҳимоя сими.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>IP41, 2×12 модулей
+          <t>ПВ-3 4 мм² PE
 Общее</t>
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G65" s="4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I65" s="5" t="n"/>
       <c r="J65" s="5" t="n"/>
     </row>
-    <row r="66" ht="88" customHeight="1">
+    <row r="66" ht="104" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Распаячные коробки</t>
+          <t>RJ45 и TV механизмы</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Коробки для доступных соединений проводов над дверями комнат.
-Хоналар эшиклари устида сим уланишларига кириш учун коробкалар.</t>
+          <t>RJ45 для роутера на балконе и антенный разъём для телевизора в зале.
+Балкондаги роутер учун RJ45 ва Залдаги телевизор учун антенна улагичи.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Размер и защиту согласовать с электриком
+          <t>1 RJ45 + 1 TV; рамки и совместимость серии уточнить
 Общее</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="G66" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="I66" s="5" t="n"/>
       <c r="J66" s="5" t="n"/>
     </row>
-    <row r="67" ht="136" customHeight="1">
+    <row r="67" ht="104" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Автомат 1P C16/C10</t>
+          <t>Подрозетники 60 мм</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Автоматы для защиты линий от перегрузки и короткого замыкания. Количество и номиналы подтвердит электрик.
-Линияларни ортиқча юк ва қисқа туташувдан ҳимоя қилиш учун автоматлар. Сони ва номиналини электрик тасдиқлайди.</t>
+          <t>Установочные коробки розеток и выключателей на стенах без гипсокартона.
+Гипсокартонсиз деворларда розетка ва выключатель ўрнатиш учун коробкалар.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>1P C16/C10; 9 шт. предварительно, полюсность линий кондиционеров уточнить
+          <t>Кирпич/бетон, 68×45 мм; 29 отверстий + 10% = 32 шт.
 Общее</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         </is>
       </c>
       <c r="G67" s="4" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
@@ -11963,69 +11963,69 @@
       <c r="I67" s="5" t="n"/>
       <c r="J67" s="5" t="n"/>
     </row>
-    <row r="68" ht="136" customHeight="1">
+    <row r="68" ht="104" customHeight="1">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>DIN-рейка, гребёнка и маркировка</t>
+          <t>Подрозетники для гипсокартона</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Крепление и соединение аппаратов щита, подписи линий. Рейки обычно входят в корпус; отдельно проверить комплектацию.
-Щит аппаратларини маҳкамлаш ва улаш, линияларга ёзув. Рейкалар одатда корпусга киради; комплектни текшириш.</t>
+          <t>Установочные коробки розеток и выключателей на стенах с гипсокартоном по плану.
+Режа бўйича гипсокартонли деворларда розетка ва выключатель ўрнатиш учун коробкалар.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>DIN-рейки, однофазная гребёнка, маркировка; комплектацию уточнить
+          <t>Для гипсокартона; 33 отверстия + 10% = 37 шт.
 Общее</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G68" s="4" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I68" s="5" t="n"/>
       <c r="J68" s="5" t="n"/>
     </row>
-    <row r="69" ht="104" customHeight="1">
+    <row r="69" ht="88" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Вводной автомат 2P 40A C</t>
+          <t>Клеммы WAGO 221-413</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Вводной автомат для отключения питания квартиры; номинал согласовать с электриком.
-Квартира токини ўчириш учун кириш автомати; номиналини электрик билан келишиш.</t>
+          <t>Клеммы для соединений в щите и коробках прихожей.
+Даҳлиз щити ва коробкаларидаги уланишлар учун клеммалар.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>2P 40A, характеристика C; проектный ориентир
+          <t>Клеммы WAGO 221-413; оригинал по выбору владельца, серию и подлинность проверить
 Общее</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
@@ -12043,29 +12043,29 @@
       <c r="I69" s="5" t="n"/>
       <c r="J69" s="5" t="n"/>
     </row>
-    <row r="70" ht="104" customHeight="1">
+    <row r="70" ht="88" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Шина N на DIN-изоляторе</t>
+          <t>УЗО 30 мА, черновик до решения электрика</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Отдельная шина для нейтральных проводников в щите; разделение после УЗО подтвердит электрик.
-Щитда нейтрал симлар учун алоҳида шина; УЗОдан кейин ажратишни электрик тасдиқлайди.</t>
+          <t>УЗО для защиты от утечки тока, состав щита решает электрик.
+Ток сизишидан ҳимоя учун УЗО, щит таркибини электрик ҳал қилади.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>N на DIN-изоляторе; количество групп уточнить
+          <t>30 мА; состав щита согласовать
 Общее</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         </is>
       </c>
       <c r="G70" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
@@ -12083,29 +12083,29 @@
       <c r="I70" s="5" t="n"/>
       <c r="J70" s="5" t="n"/>
     </row>
-    <row r="71" ht="104" customHeight="1">
+    <row r="71" ht="88" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Шина PE на DIN-изоляторе</t>
+          <t>Клеммы WAGO 221-415</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Отдельная шина для защитного заземления, не соединять с N после УЗО.
-Ҳимоя ерлаш симлари учун алоҳида шина, УЗОдан кейин N билан уламаслик.</t>
+          <t>Клеммы для соединений в щите и коробках прихожей.
+Даҳлиз щити ва коробкаларидаги уланишлар учун клеммалар.</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>PE на DIN-изоляторе; наличие PE проверить
+          <t>Клеммы WAGO 221-415; оригинал по выбору владельца, серию и подлинность проверить
 Общее</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         </is>
       </c>
       <c r="G71" s="4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
@@ -12129,75 +12129,75 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Провод ПВ-3 4 мм² PE</t>
+          <t>Временное питание и свет бригады</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Защитный провод для заземления электропроводки квартиры.
-Квартира электропроводкасини заземление қилиш учун ҳимоя сими.</t>
+          <t>Временное питание и освещение для безопасной работы бригады.
+Бригаданинг хавфсиз ишлаши учун вақтинча ток ва ёритиш.</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>ПВ-3 4 мм² PE
+          <t>DB; безопасную схему решает электрик
 Общее</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="G72" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="I72" s="5" t="n"/>
       <c r="J72" s="5" t="n"/>
     </row>
-    <row r="73" ht="104" customHeight="1">
+    <row r="73" ht="88" customHeight="1">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>RJ45 и TV механизмы</t>
+          <t>UTP cat.5e</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>RJ45 для роутера на балконе и антенный разъём для телевизора в зале.
-Балкондаги роутер учун RJ45 ва Залдаги телевизор учун антенна улагичи.</t>
+          <t>Сетевой кабель от ввода до роутера на балконе; ТВ по Wi-Fi.
+Киришдан Балкондаги роутергача тармоқ кабели; телевизор Wi-Fi орқали.</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>1 RJ45 + 1 TV; рамки и совместимость серии уточнить
+          <t>UTP cat.5e
 Общее</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G73" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>м</t>
         </is>
       </c>
       <c r="I73" s="5" t="n"/>
@@ -12209,35 +12209,34 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Подрозетники 60 мм</t>
+          <t>Дюбель-гвоздь 6×60</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Установочные коробки розеток и выключателей на стенах без гипсокартона.
-Гипсокартонсиз деворларда розетка ва выключатель ўрнатиш учун коробкалар.</t>
+          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркасини маҳкамлаш учун дюбель-гвоздлар.</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Кирпич/бетон, 68×45 мм; 29 отверстий + 10% = 32 шт.
-Общее</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>32</v>
+          <t>Запас и округление</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>1.22</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G74" s="4" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="I74" s="5" t="n"/>
@@ -12249,235 +12248,237 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Подрозетники для гипсокартона</t>
+          <t>Саморезы-семечки</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Установочные коробки розеток и выключателей на стенах с гипсокартоном по плану.
-Режа бўйича гипсокартонли деворларда розетка ва выключатель ўрнатиш учун коробкалар.</t>
+          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХни каркасга маҳкамлаш учун саморезлар.</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Для гипсокартона; 33 отверстия + 10% = 37 шт.
-Общее</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>37</v>
+          <t>Запас и округление</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>1.22</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="G75" s="4" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="I75" s="5" t="n"/>
       <c r="J75" s="5" t="n"/>
     </row>
-    <row r="76" ht="88" customHeight="1">
+    <row r="76" ht="104" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Клеммы WAGO 221-413</t>
+          <t>ПВХ панели потолочные и балкон</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Клеммы для соединений в щите и коробках прихожей.
-Даҳлиз щити ва коробкаларидаги уланишлар учун клеммалар.</t>
+          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.
+Ваннахона, Ошхона, Даҳлиз потолоклари ҳамда Балкон деворлари ва потолоки учун панеллар.</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Клеммы WAGO 221-413; оригинал по выбору владельца, серию и подлинность проверить
-Общее</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="n">
-        <v>30</v>
+          <t>Запас и округление</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>6.05</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>шт. по 1 м²</t>
         </is>
       </c>
       <c r="G76" s="4" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>шт. по 1 м²</t>
         </is>
       </c>
       <c r="I76" s="5" t="n"/>
       <c r="J76" s="5" t="n"/>
     </row>
-    <row r="77" ht="88" customHeight="1">
+    <row r="77" ht="104" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>УЗО 30 мА, черновик до решения электрика</t>
+          <t>Направляющие для ПВХ</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>УЗО для защиты от утечки тока, состав щита решает электрик.
-Ток сизишидан ҳимоя учун УЗО, щит таркибини электрик ҳал қилади.</t>
+          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси направляющийлари.</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>30 мА; состав щита согласовать
-Общее</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="n">
-        <v>2</v>
+          <t>UD 3 м; совместимость подтвердить
+Запас и округление</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0.89</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="G77" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="I77" s="5" t="n"/>
       <c r="J77" s="5" t="n"/>
     </row>
-    <row r="78" ht="88" customHeight="1">
+    <row r="78" ht="72" customHeight="1">
       <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Клеммы WAGO 221-415</t>
+          <t>Профиль для ПВХ</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Клеммы для соединений в щите и коробках прихожей.
-Даҳлиз щити ва коробкаларидаги уланишлар учун клеммалар.</t>
+          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси профили.</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Клеммы WAGO 221-415; оригинал по выбору владельца, серию и подлинность проверить
-Общее</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>10</v>
+          <t>CD 3 м; совместимость подтвердить
+Запас и округление</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0.89</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="G78" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>шт. 3 м</t>
         </is>
       </c>
       <c r="I78" s="5" t="n"/>
       <c r="J78" s="5" t="n"/>
     </row>
-    <row r="79" ht="72" customHeight="1">
+    <row r="79" ht="104" customHeight="1">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Временное питание и свет бригады</t>
+          <t>Пластиковые уголки</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Временное питание и освещение для безопасной работы бригады.
-Бригаданинг хавфсиз ишлаши учун вақтинча ток ва ёритиш.</t>
+          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.
+Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ туташган жойларини ёпиш учун уголоклар.</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>DB; безопасную схему решает электрик
-Общее</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>1</v>
+          <t>Длина 3 м
+Запас и округление</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0.89</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G79" s="4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>комплект</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I79" s="5" t="n"/>
       <c r="J79" s="5" t="n"/>
     </row>
-    <row r="80" ht="88" customHeight="1">
+    <row r="80" ht="72" customHeight="1">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>UTP cat.5e</t>
+          <t>Плиссе</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Сетевой кабель от ввода до роутера на балконе; ТВ по Wi-Fi.
-Киришдан Балкондаги роутергача тармоқ кабели; телевизор Wi-Fi орқали.</t>
+          <t>Плиссе на окна кухни, зала и наружное остекление балкона.
+Ошхона, Зал деразалари ва Балконнинг ташқи ойналарига плиссе.</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>UTP cat.5e
-Общее</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>11</v>
+          <t>Замерить каждую секцию окна
+Без распределения</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="n">
-        <v>11</v>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I80" s="5" t="n"/>
@@ -12489,73 +12490,78 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Дюбель-гвоздь 6×60</t>
+          <t>Защитная клетка для наружного блока</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Дюбель-гвозди для крепления каркаса ПВХ в ванной, кухне, прихожей и на балконе.
-Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркасини маҳкамлаш учун дюбель-гвоздлар.</t>
+          <t>Клетка для защиты наружного блока кондиционера под решёткой окна спальни.
+Ётоқхона деразаси решёткаси остидаги ташқи кондиционер блокини ҳимоя қилиш учун клетка.</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Запас и округление</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>1.22</v>
+          <t>Наружный блок под решёткой окна спальни; отдельный подрядчик
+Без распределения</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G81" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="I81" s="5" t="n"/>
       <c r="J81" s="5" t="n"/>
     </row>
-    <row r="82" ht="104" customHeight="1">
+    <row r="82" ht="88" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Саморезы-семечки</t>
+          <t>Краска стен</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Саморезы для крепления ПВХ к каркасу в ванной, кухне, прихожей и на балконе.
-Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХни каркасга маҳкамлаш учун саморезлар.</t>
+          <t>Краска для стен зала, прихожей и окрашиваемых участков кухни.
+Зал, Даҳлиз деворлари ва Ошхонанинг бўяладиган қисмлари учун краска.</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Запас и округление</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>1.22</v>
+          <t>Без распределения</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="n">
-        <v>2</v>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="I82" s="5" t="n"/>
@@ -12567,414 +12573,128 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>ПВХ панели потолочные и балкон</t>
+          <t>Краска POLARD UNIVERSAL 10 кг</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Панели для потолков ванной, кухни, прихожей, а также стен и потолка балкона.
-Ваннахона, Ошхона, Даҳлиз потолоклари ҳамда Балкон деворлари ва потолоки учун панеллар.</t>
+          <t>Кандидат краски для стен, пригодность и моющуюся стойкость ещё нужно проверить.
+Деворлар учун краска варианти, яроқлилиги ва ювилишга чидамлилигини текшириш керак.</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Запас и округление</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>6.05</v>
+          <t>Без распределения</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>шт. по 1 м²</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="n">
-        <v>45</v>
+          <t>ведро 10 кг</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>шт. по 1 м²</t>
+          <t>ведро 10 кг</t>
         </is>
       </c>
       <c r="I83" s="5" t="n"/>
       <c r="J83" s="5" t="n"/>
     </row>
-    <row r="84" ht="104" customHeight="1">
+    <row r="84" ht="88" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Направляющие для ПВХ</t>
+          <t>Стяжка старая: мешки/вывоз</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Направляющие каркаса ПВХ в ванной, кухне, прихожей и на балконе.
-Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси направляющийлари.</t>
+          <t>Мешки и вывоз мусора после демонтажа старой стяжки.
+Эски стяжкани бузгандан кейин чиқинди учун қоплар ва олиб чиқиш.</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>UD 3 м; совместимость подтвердить
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>0.89</v>
+          <t>Общее</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>67</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
+          <t>мешок 50 кг эквивалент</t>
         </is>
       </c>
       <c r="G84" s="4" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
+          <t>мешок 50 кг эквивалент</t>
         </is>
       </c>
       <c r="I84" s="5" t="n"/>
       <c r="J84" s="5" t="n"/>
     </row>
-    <row r="85" ht="72" customHeight="1">
+    <row r="85" ht="104" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Профиль для ПВХ</t>
+          <t>Газовая плита напольная 50–60 см</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Профиль каркаса ПВХ в ванной, кухне, прихожей и на балконе.
-Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ каркаси профили.</t>
+          <t>Устаревшая позиция: напольную газовую плиту не заказывать, выбрана панель.
+Эски позиция: полга қўйиладиган газ плитасини буюртма қилманг, панель танланган.</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>CD 3 м; совместимость подтвердить
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>0.89</v>
+          <t>Не заказывать
+Без распределения</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
-        </is>
-      </c>
-      <c r="G85" s="4" t="n">
-        <v>13</v>
+          <t>комплект</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>уточнить</t>
+        </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>шт. 3 м</t>
+          <t>комплект</t>
         </is>
       </c>
       <c r="I85" s="5" t="n"/>
       <c r="J85" s="5" t="n"/>
     </row>
-    <row r="86" ht="104" customHeight="1">
-      <c r="A86" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Пластиковые уголки</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Уголки для закрытия стыков ПВХ в ванной, кухне, прихожей и на балконе.
-Ваннахона, Ошхона, Даҳлиз ва Балконда ПВХ туташган жойларини ёпиш учун уголоклар.</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Длина 3 м
-Запас и округление</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G86" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="n"/>
-      <c r="J86" s="5" t="n"/>
-    </row>
-    <row r="87" ht="72" customHeight="1">
-      <c r="A87" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Плиссе</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Плиссе на окна кухни, зала и наружное остекление балкона.
-Ошхона, Зал деразалари ва Балконнинг ташқи ойналарига плиссе.</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Замерить каждую секцию окна
-Без распределения</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I87" s="5" t="n"/>
-      <c r="J87" s="5" t="n"/>
-    </row>
-    <row r="88" ht="104" customHeight="1">
-      <c r="A88" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Защитная клетка для наружного блока</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Клетка для защиты наружного блока кондиционера под решёткой окна спальни.
-Ётоқхона деразаси решёткаси остидаги ташқи кондиционер блокини ҳимоя қилиш учун клетка.</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Наружный блок под решёткой окна спальни; отдельный подрядчик
-Без распределения</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G88" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="n"/>
-      <c r="J88" s="5" t="n"/>
-    </row>
-    <row r="89" ht="88" customHeight="1">
-      <c r="A89" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Краска стен</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Краска для стен зала, прихожей и окрашиваемых участков кухни.
-Зал, Даҳлиз деворлари ва Ошхонанинг бўяладиган қисмлари учун краска.</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Без распределения</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>комплект</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>комплект</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="n"/>
-      <c r="J89" s="5" t="n"/>
-    </row>
-    <row r="90" ht="104" customHeight="1">
-      <c r="A90" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Краска POLARD UNIVERSAL 10 кг</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Кандидат краски для стен, пригодность и моющуюся стойкость ещё нужно проверить.
-Деворлар учун краска варианти, яроқлилиги ва ювилишга чидамлилигини текшириш керак.</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Без распределения</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>ведро 10 кг</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>ведро 10 кг</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="5" t="n"/>
-    </row>
-    <row r="91" ht="88" customHeight="1">
-      <c r="A91" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Стяжка старая: мешки/вывоз</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Мешки и вывоз мусора после демонтажа старой стяжки.
-Эски стяжкани бузгандан кейин чиқинди учун қоплар ва олиб чиқиш.</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Общее</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>мешок 50 кг эквивалент</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="n">
-        <v>67</v>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>мешок 50 кг эквивалент</t>
-        </is>
-      </c>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="5" t="n"/>
-    </row>
-    <row r="92" ht="104" customHeight="1">
-      <c r="A92" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Газовая плита напольная 50–60 см</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Устаревшая позиция: напольную газовую плиту не заказывать, выбрана панель.
-Эски позиция: полга қўйиладиган газ плитасини буюртма қилманг, панель танланган.</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Не заказывать
-Без распределения</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>комплект</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>комплект</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="n"/>
-      <c r="J92" s="5" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J92"/>
+  <autoFilter ref="A1:J85"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
